--- a/docs/downloads/2026-10-06/bursa-report-2026-10-06.xlsx
+++ b/docs/downloads/2026-10-06/bursa-report-2026-10-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-06" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-06'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-06'!$A$1:$M$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -78,13 +78,13 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -543,39 +543,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.38</v>
+        <v>0.075</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.027</v>
+        <v>0.1538</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>29337200</v>
+        <v>120139200</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="H2" t="n">
-        <v>70.89</v>
+        <v>17.7</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.344</v>
+        <v>0.204</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.215</v>
+        <v>0.425</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -588,40 +588,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>SLGC Berhad</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.245</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>8560400</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H3" t="n">
-        <v>16.25</v>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0.424</v>
-      </c>
+        <v>50575500</v>
+      </c>
+      <c r="G3" s="5" t="n"/>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
     </row>
@@ -633,39 +624,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0.0526</v>
+        <v>0.155</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>5174100</v>
+        <v>19144500</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="H4" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
+        <v>83.98999999999999</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.092</v>
+        <v>0.107</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.083</v>
+        <v>0.09</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,39 +669,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.32</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1175900</v>
+        <v>17948200</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.04</v>
+        <v>0.39</v>
       </c>
       <c r="H5" t="n">
-        <v>62.15</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
+        <v>76.48</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.482</v>
+        <v>0.258</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.476</v>
+        <v>0.238</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,39 +714,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>-0.008199999999999999</v>
+        <v>0.495</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>-0.0198</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>863700</v>
+        <v>8893300</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.03</v>
+        <v>0.34</v>
       </c>
       <c r="H6" t="n">
-        <v>71.92</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
+        <v>56.48</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.572</v>
+        <v>0.48</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.499</v>
+        <v>0.475</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,39 +759,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.775</v>
+        <v>0.84</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.0473</v>
+        <v>0.006</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>666700</v>
+        <v>8728000</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.54</v>
+        <v>1.26</v>
       </c>
       <c r="H7" t="n">
-        <v>68.06</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
+        <v>72.51000000000001</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.781</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.773</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,39 +804,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0143</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>KEYASIC</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E8" s="10" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="E8" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>552900</v>
+        <v>8449900</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.11</v>
+        <v>0.98</v>
       </c>
       <c r="H8" t="n">
-        <v>62.72</v>
+        <v>53.68</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.9</v>
+        <v>0.063</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.858</v>
+        <v>0.058</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -858,45 +849,2610 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0183</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>SALUTE</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.525</v>
+        <v>0.12</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.05</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>518800</v>
+        <v>8222700</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.48</v>
+        <v>1.12</v>
       </c>
       <c r="H9" t="n">
-        <v>21.71</v>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
+        <v>53.87</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.608</v>
+        <v>0.116</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.63</v>
+        <v>0.109</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>4723</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>JAKS</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>7545800</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H10" t="n">
+        <v>60.35</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>7215</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NIHSIN</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>7426500</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H11" t="n">
+        <v>70.89</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>-0.008199999999999999</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>7203700</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H12" t="n">
+        <v>71.92</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7020</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ASTEEL</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0.1579</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>7066700</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H13" t="n">
+        <v>64.31</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0.0307</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>6578600</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H14" t="n">
+        <v>66.83</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.08109999999999999</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>4888700</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H15" t="n">
+        <v>70.77</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5260</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>OWG</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>4106300</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="H16" t="n">
+        <v>69.03</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>L&amp;G</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>-0.0488</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>4099200</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H17" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0258</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AGMO</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0.0339</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>4021700</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="H18" t="n">
+        <v>61.78</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>3277000</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H19" t="n">
+        <v>42.38</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>1.337</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.1136</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H20" t="n">
+        <v>78.47</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>2335200</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>75.17</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>2031700</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H22" t="n">
+        <v>44.76</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>2.097</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>2.075</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5078</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>M&amp;G</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>1923300</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>1900700</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H24" t="n">
+        <v>53.69</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>1795700</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H25" t="n">
+        <v>67.61</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>1721600</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H26" t="n">
+        <v>53.15</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>7113</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TOPGLOV</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>1720400</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H27" t="n">
+        <v>61.97</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>1687400</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H28" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>1626500</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H29" t="n">
+        <v>47.05</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>2.218</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0251</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SFPTECH</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>-0.0169</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1551800</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H30" t="n">
+        <v>55.52</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>1478900</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H31" t="n">
+        <v>61.93</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>1.769</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>1.602</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>1416500</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H32" t="n">
+        <v>56.71</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0.0702</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>1317500</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H33" t="n">
+        <v>85.55</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1307300</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H34" t="n">
+        <v>69.31999999999999</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0024</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>JAG</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>1275300</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>57.94</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1651</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MRCB</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>-0.0172</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1181200</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H36" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MFGROUP</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>1178300</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H37" t="n">
+        <v>45.51</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>1154800</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H38" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>5.673</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>5.279</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>5315</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SKYWLD</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>1111200</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H39" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0262</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SUNVIEW</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>1081200</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H40" t="n">
+        <v>68.66</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0.0173</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>1073500</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H41" t="n">
+        <v>52.81</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>3.585</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>2.624</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>1056400</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H42" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>1.142</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0.0103</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>1045400</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H43" t="n">
+        <v>62.27</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>2.752</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>2.569</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0.0265</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>981400</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H44" t="n">
+        <v>67.51000000000001</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0.0365</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>968100</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>68.97</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>2.038</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0249</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>LGMS</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>963900</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>69.91</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>865600</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H47" t="n">
+        <v>64.69</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>812600</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H48" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>805000</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H49" t="n">
+        <v>62.49</v>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>4.889</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>4.612</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>804000</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H50" t="n">
+        <v>54</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>2.571</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>2.476</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>776600</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H51" t="n">
+        <v>62.98</v>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>2.584</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>763600</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H52" t="n">
+        <v>63.32</v>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>2.977</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>-0.0089</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>758500</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H53" t="n">
+        <v>63.68</v>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>747500</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H54" t="n">
+        <v>62.06</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>713900</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H55" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>670300</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H56" t="n">
+        <v>67.26000000000001</v>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>657300</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H57" t="n">
+        <v>48.73</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>2.681</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>651200</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H58" t="n">
+        <v>33.99</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>1.918</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>2.042</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0.0296</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>650500</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H59" t="n">
+        <v>74.79000000000001</v>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>641700</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H60" t="n">
+        <v>43.15</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>10.097</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>10.249</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>605600</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H61" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>-0.009300000000000001</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>571200</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H62" t="n">
+        <v>51.34</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>561400</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H63" t="n">
+        <v>51.28</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>3.036</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0466</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SRKKAI</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>-0.0091</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>559900</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H64" t="n">
+        <v>56.01</v>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0.0153</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>547600</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H65" t="n">
+        <v>71.98</v>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>2.909</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>2.761</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>521300</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H66" t="n">
+        <v>48.67</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>7.755</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:M66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-06/bursa-report-2026-10-06.xlsx
+++ b/docs/downloads/2026-10-06/bursa-report-2026-10-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-06" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-06'!$A$1:$M$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-06'!$A$1:$M$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -83,8 +83,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>0.1538</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>120139200</v>
+        <v>144184500</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="H2" t="n">
         <v>17.7</v>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>50575500</v>
+        <v>56670900</v>
       </c>
       <c r="G3" s="5" t="n"/>
       <c r="I3" s="6" t="inlineStr">
@@ -624,39 +624,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>0</v>
+        <v>0.315</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>19144500</v>
+        <v>22147100</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>3.35</v>
+        <v>0.48</v>
       </c>
       <c r="H4" t="n">
-        <v>83.98999999999999</v>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
+        <v>73.81</v>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.107</v>
+        <v>0.258</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.09</v>
+        <v>0.238</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -669,39 +669,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.32</v>
+        <v>0.155</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>17948200</v>
+        <v>21189700</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.39</v>
+        <v>3.71</v>
       </c>
       <c r="H5" t="n">
-        <v>76.48</v>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
+        <v>83.98999999999999</v>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.258</v>
+        <v>0.107</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.238</v>
+        <v>0.09</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,27 +723,27 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>-0.0198</v>
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>8893300</v>
+        <v>12913100</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.34</v>
+        <v>0.49</v>
       </c>
       <c r="H6" t="n">
-        <v>56.48</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
+        <v>58.53</v>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.48</v>
+        <v>0.481</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0.475</v>
@@ -759,39 +759,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0183</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SALUTE</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.84</v>
+        <v>0.115</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.006</v>
+        <v>0.0455</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>8728000</v>
+        <v>11105200</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="H7" t="n">
-        <v>72.51000000000001</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.3</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.781</v>
+        <v>0.115</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.773</v>
+        <v>0.109</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -804,39 +804,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0143</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KEYASIC</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>0</v>
+        <v>0.845</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.012</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8449900</v>
+        <v>10885300</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.98</v>
+        <v>1.58</v>
       </c>
       <c r="H8" t="n">
-        <v>53.68</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.41</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.063</v>
+        <v>0.781</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.058</v>
+        <v>0.773</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -849,39 +849,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0183</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SALUTE</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.12</v>
+        <v>0.84</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0307</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8222700</v>
+        <v>9774000</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.12</v>
+        <v>0.79</v>
       </c>
       <c r="H9" t="n">
-        <v>53.87</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.83</v>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.116</v>
+        <v>0.756</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.109</v>
+        <v>0.704</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -894,28 +894,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0143</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>KEYASIC</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>0.0294</v>
+        <v>0.065</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>7545800</v>
+        <v>9114200</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.12</v>
+        <v>1.06</v>
       </c>
       <c r="H10" t="n">
-        <v>60.35</v>
+        <v>53.68</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.162</v>
+        <v>0.063</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.127</v>
+        <v>0.058</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -939,39 +939,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0</v>
+        <v>0.115</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.2105</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7426500</v>
+        <v>8831600</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.17</v>
+        <v>5.88</v>
       </c>
       <c r="H11" t="n">
-        <v>70.89</v>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
+        <v>66.62</v>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.347</v>
+        <v>0.093</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.221</v>
+        <v>0.083</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -984,39 +984,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>-0.008199999999999999</v>
+        <v>0.18</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7203700</v>
+        <v>8723500</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.28</v>
+        <v>0.13</v>
       </c>
       <c r="H12" t="n">
-        <v>71.92</v>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.14</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.572</v>
+        <v>0.163</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.499</v>
+        <v>0.127</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1029,39 +1029,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>0.1579</v>
+        <v>0.605</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>7066700</v>
+        <v>8295300</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>4.7</v>
+        <v>0.32</v>
       </c>
       <c r="H13" t="n">
-        <v>64.31</v>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
+        <v>71.92</v>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.093</v>
+        <v>0.572</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.083</v>
+        <v>0.499</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1074,39 +1074,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>0.0307</v>
+        <v>0.375</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6578600</v>
+        <v>7458500</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.53</v>
+        <v>0.18</v>
       </c>
       <c r="H14" t="n">
-        <v>66.83</v>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
+        <v>68.56999999999999</v>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.756</v>
+        <v>0.347</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.704</v>
+        <v>0.221</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1119,39 +1119,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0.08109999999999999</v>
+        <v>0.635</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4888700</v>
+        <v>6938300</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>3.95</v>
+        <v>0.38</v>
       </c>
       <c r="H15" t="n">
-        <v>70.77</v>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.505</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1164,39 +1164,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OWG</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.21</v>
+        <v>0.785</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.05</v>
+        <v>0.0608</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4106300</v>
+        <v>6059500</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>17.29</v>
+        <v>4.9</v>
       </c>
       <c r="H16" t="n">
-        <v>69.03</v>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
+        <v>69.20999999999999</v>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.184</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.188</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1209,39 +1209,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>-0.0488</v>
+        <v>1.18</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>4099200</v>
+        <v>5997700</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.17</v>
+        <v>2.06</v>
       </c>
       <c r="H17" t="n">
-        <v>51.26</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.17</v>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.196</v>
+        <v>0.959</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.182</v>
+        <v>0.83</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1254,39 +1254,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0258</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AGMO</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>0.0339</v>
+        <v>0.395</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4021700</v>
+        <v>5458800</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>9.34</v>
+        <v>0.49</v>
       </c>
       <c r="H18" t="n">
-        <v>61.78</v>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.38</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.278</v>
+        <v>0.405</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.305</v>
+        <v>0.411</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1299,28 +1299,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>0</v>
+        <v>0.195</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>-0.0488</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3277000</v>
+        <v>4545600</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
       <c r="H19" t="n">
-        <v>42.38</v>
+        <v>51.26</v>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.337</v>
+        <v>0.196</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1.305</v>
+        <v>0.182</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1344,39 +1344,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.735</v>
+        <v>0.37</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.1136</v>
+        <v>0.0137</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2500000</v>
+        <v>4470400</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>1.09</v>
+        <v>0.57</v>
       </c>
       <c r="H20" t="n">
-        <v>78.47</v>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
+        <v>67.61</v>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.55</v>
+        <v>0.342</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.442</v>
+        <v>0.321</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1389,39 +1389,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>OWG</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>-0.0167</v>
+        <v>0.21</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.05</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2335200</v>
+        <v>4467900</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.8</v>
+        <v>18.81</v>
       </c>
       <c r="H21" t="n">
-        <v>75.17</v>
-      </c>
-      <c r="I21" s="9" t="inlineStr">
+        <v>69.03</v>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.959</v>
+        <v>0.184</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.83</v>
+        <v>0.188</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1434,28 +1434,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>0.0148</v>
+        <v>0.11</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2031700</v>
+        <v>4385300</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.11</v>
+        <v>0.64</v>
       </c>
       <c r="H22" t="n">
-        <v>44.76</v>
+        <v>41.61</v>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.097</v>
+        <v>0.117</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>2.075</v>
+        <v>0.123</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1479,39 +1479,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0258</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>AGMO</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
         <v>0.305</v>
       </c>
-      <c r="E23" s="8" t="n">
-        <v>0</v>
+      <c r="E23" s="3" t="n">
+        <v>0.0339</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1923300</v>
+        <v>4188200</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.1</v>
+        <v>9.73</v>
       </c>
       <c r="H23" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.78</v>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.303</v>
+        <v>0.278</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.294</v>
+        <v>0.305</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1524,39 +1524,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>0</v>
+        <v>0.65</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0.1404</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1900700</v>
+        <v>4115600</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.18</v>
+        <v>1.28</v>
       </c>
       <c r="H24" t="n">
-        <v>53.69</v>
-      </c>
-      <c r="I24" s="9" t="inlineStr">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.608</v>
+        <v>0.468</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.609</v>
+        <v>0.428</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1569,39 +1569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.37</v>
+        <v>0.78</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.0137</v>
+        <v>0.1818</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1795700</v>
+        <v>4007800</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.23</v>
+        <v>1.75</v>
       </c>
       <c r="H25" t="n">
-        <v>67.61</v>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
+        <v>80.67</v>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.342</v>
+        <v>0.555</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.321</v>
+        <v>0.443</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1614,39 +1614,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.78</v>
+        <v>0.305</v>
       </c>
       <c r="E26" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1721600</v>
+        <v>3924400</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="H26" t="n">
-        <v>53.15</v>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.3</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.775</v>
+        <v>0.303</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.775</v>
+        <v>0.294</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1659,28 +1659,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>0</v>
+        <v>1.3</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1720400</v>
+        <v>3820600</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.04</v>
+        <v>0.32</v>
       </c>
       <c r="H27" t="n">
-        <v>61.97</v>
+        <v>45.24</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.747</v>
+        <v>1.339</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.696</v>
+        <v>1.305</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1704,39 +1704,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.0108</v>
+        <v>0.0064</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1687400</v>
+        <v>3089900</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="H28" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.83</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.901</v>
+        <v>0.747</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.858</v>
+        <v>0.696</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1749,39 +1749,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>0.0278</v>
+        <v>0.615</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1626500</v>
+        <v>3075900</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="H29" t="n">
-        <v>47.05</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.69</v>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2.26</v>
+        <v>0.608</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>2.218</v>
+        <v>0.609</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1794,39 +1794,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>-0.0169</v>
+        <v>0.78</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1551800</v>
+        <v>2838100</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="H30" t="n">
-        <v>55.52</v>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
+        <v>53.15</v>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.273</v>
+        <v>0.775</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.306</v>
+        <v>0.775</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1839,28 +1839,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.0109</v>
+        <v>0.0148</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1478900</v>
+        <v>2813400</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="H31" t="n">
-        <v>61.93</v>
+        <v>44.76</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.769</v>
+        <v>2.097</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1.602</v>
+        <v>2.075</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1884,39 +1884,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.715</v>
+        <v>1.86</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0164</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1416500</v>
+        <v>2681200</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="H32" t="n">
-        <v>56.71</v>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.63</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.6870000000000001</v>
+        <v>1.769</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.672</v>
+        <v>1.602</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1929,39 +1929,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.61</v>
+        <v>0.375</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0.0702</v>
+        <v>0.0274</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1317500</v>
+        <v>2632400</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="H33" t="n">
-        <v>85.55</v>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.94</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.464</v>
+        <v>0.367</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.427</v>
+        <v>0.368</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1974,39 +1974,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.735</v>
+        <v>5.67</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.0068</v>
+        <v>0.0235</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1307300</v>
+        <v>2586700</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="H34" t="n">
-        <v>69.31999999999999</v>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.77</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.659</v>
+        <v>5.668</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.595</v>
+        <v>5.278</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2019,39 +2019,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.375</v>
+        <v>0.44</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0.0274</v>
+        <v>0.0115</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1275300</v>
+        <v>2561900</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="H35" t="n">
-        <v>57.94</v>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.17</v>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.367</v>
+        <v>0.397</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.368</v>
+        <v>0.337</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2064,39 +2064,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>-0.0172</v>
+        <v>2.94</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1181200</v>
+        <v>2502700</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.17</v>
+        <v>0.78</v>
       </c>
       <c r="H36" t="n">
-        <v>37.25</v>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.2</v>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.294</v>
+        <v>2.541</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.309</v>
+        <v>2.079</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2109,28 +2109,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>0</v>
+        <v>2.21</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0.0231</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1178300</v>
+        <v>2472000</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1.24</v>
+        <v>0.17</v>
       </c>
       <c r="H37" t="n">
-        <v>45.51</v>
+        <v>46.26</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.261</v>
+        <v>2.259</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.265</v>
+        <v>2.218</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2154,39 +2154,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>5.72</v>
+        <v>2.92</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.0325</v>
+        <v>0.0069</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1154800</v>
+        <v>2330200</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="H38" t="n">
-        <v>54.47</v>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.88</v>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>5.673</v>
+        <v>2.751</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>5.279</v>
+        <v>2.569</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2199,39 +2199,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SKYWLD</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>0.0519</v>
+        <v>0.375</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>-0.026</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1111200</v>
+        <v>2192400</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>1.88</v>
+        <v>0.25</v>
       </c>
       <c r="H39" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.29000000000001</v>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.391</v>
+        <v>0.345</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.397</v>
+        <v>0.317</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2244,39 +2244,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.405</v>
+        <v>10.02</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.0125</v>
+        <v>0.002</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1081200</v>
+        <v>2164500</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="H40" t="n">
-        <v>68.66</v>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.51</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.383</v>
+        <v>10.095</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.374</v>
+        <v>10.249</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2289,39 +2289,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>3.52</v>
+        <v>0.405</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.0173</v>
+        <v>0.0125</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1073500</v>
+        <v>2040800</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="H41" t="n">
-        <v>52.81</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.66</v>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>3.585</v>
+        <v>0.383</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>2.624</v>
+        <v>0.374</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2334,39 +2334,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>0</v>
+        <v>0.93</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0.0054</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1056400</v>
+        <v>1987000</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.26</v>
+        <v>0.39</v>
       </c>
       <c r="H42" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
+        <v>64</v>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.142</v>
+        <v>0.901</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>1.05</v>
+        <v>0.858</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2379,39 +2379,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>2.93</v>
+        <v>0.55</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.0103</v>
+        <v>0.068</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1045400</v>
+        <v>1962300</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.11</v>
+        <v>4.48</v>
       </c>
       <c r="H43" t="n">
-        <v>62.27</v>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
+        <v>71.17</v>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>2.752</v>
+        <v>0.506</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2.569</v>
+        <v>0.5</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2424,39 +2424,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.58</v>
+        <v>5.01</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>0.0265</v>
+        <v>0.004</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>981400</v>
+        <v>1949100</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
       <c r="H44" t="n">
-        <v>67.51000000000001</v>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
+        <v>61.61</v>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.53</v>
+        <v>4.887</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.484</v>
+        <v>4.611</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2469,39 +2469,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>2.27</v>
+        <v>0.72</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.0365</v>
+        <v>0.0141</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>968100</v>
+        <v>1916800</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.5</v>
+        <v>0.26</v>
       </c>
       <c r="H45" t="n">
-        <v>68.97</v>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
+        <v>57.56</v>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2.038</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1.929</v>
+        <v>0.673</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2514,39 +2514,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.545</v>
+        <v>2.61</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.0583</v>
+        <v>0.0156</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>963900</v>
+        <v>1915600</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>2.2</v>
+        <v>0.11</v>
       </c>
       <c r="H46" t="n">
-        <v>69.91</v>
-      </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.75</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.506</v>
+        <v>2.572</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.5</v>
+        <v>2.477</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2559,39 +2559,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.83</v>
+        <v>0.735</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.0247</v>
+        <v>0.0068</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>865600</v>
+        <v>1897500</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.32</v>
+        <v>0.19</v>
       </c>
       <c r="H47" t="n">
-        <v>64.69</v>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
+        <v>69.31999999999999</v>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.771</v>
+        <v>0.659</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.746</v>
+        <v>0.595</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2604,39 +2604,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1.38</v>
+        <v>0.58</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.0222</v>
+        <v>0.0265</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>812600</v>
+        <v>1802000</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="H48" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
+        <v>67.51000000000001</v>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.187</v>
+        <v>0.53</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.971</v>
+        <v>0.484</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2649,39 +2649,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>5.03</v>
+        <v>1.21</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>0.008</v>
+        <v>0.0083</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>805000</v>
+        <v>1795000</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.03</v>
+        <v>0.44</v>
       </c>
       <c r="H49" t="n">
-        <v>62.49</v>
-      </c>
-      <c r="I49" s="9" t="inlineStr">
+        <v>66.92</v>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>4.889</v>
+        <v>1.143</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>4.612</v>
+        <v>1.05</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2694,28 +2694,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>0.0117</v>
+        <v>1.07</v>
+      </c>
+      <c r="E50" s="9" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>804000</v>
+        <v>1759400</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="H50" t="n">
-        <v>54</v>
+        <v>51.34</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2.571</v>
+        <v>1.068</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>2.476</v>
+        <v>1.03</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2739,39 +2739,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2.69</v>
+        <v>0.49</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.0151</v>
+        <v>0.0208</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>776600</v>
+        <v>1676100</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.14</v>
+        <v>0.04</v>
       </c>
       <c r="H51" t="n">
-        <v>62.98</v>
-      </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.31</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.584</v>
+        <v>0.574</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2.56</v>
+        <v>0.78</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2784,39 +2784,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>0.0127</v>
+        <v>0.285</v>
+      </c>
+      <c r="E52" s="9" t="n">
+        <v>-0.0339</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>763600</v>
+        <v>1671800</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="H52" t="n">
-        <v>63.32</v>
-      </c>
-      <c r="I52" s="9" t="inlineStr">
+        <v>53.39</v>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>2.977</v>
+        <v>0.272</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>2.785</v>
+        <v>0.306</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2829,39 +2829,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>-0.0089</v>
+        <v>0.24</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>758500</v>
+        <v>1671500</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.05</v>
+        <v>1.62</v>
       </c>
       <c r="H53" t="n">
-        <v>63.68</v>
-      </c>
-      <c r="I53" s="9" t="inlineStr">
+        <v>71.56</v>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.511</v>
+        <v>0.213</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.428</v>
+        <v>0.203</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2874,28 +2874,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.85</v>
+        <v>3.48</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>0.0241</v>
+        <v>0.0058</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>747500</v>
+        <v>1603400</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="H54" t="n">
-        <v>62.06</v>
+        <v>51.97</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>3.581</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.746</v>
+        <v>2.623</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2919,39 +2919,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5277</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>FPGROUP</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>-0.0076</v>
+        <v>0.43</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0.0238</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>713900</v>
+        <v>1590600</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.22</v>
+        <v>1.6</v>
       </c>
       <c r="H55" t="n">
-        <v>65.25</v>
-      </c>
-      <c r="I55" s="9" t="inlineStr">
+        <v>59.94</v>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.64</v>
+        <v>0.409</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.607</v>
+        <v>0.417</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2964,39 +2964,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>0</v>
+        <v>2.64</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0.0076</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>670300</v>
+        <v>1544600</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.04</v>
+        <v>0.43</v>
       </c>
       <c r="H56" t="n">
-        <v>67.26000000000001</v>
-      </c>
-      <c r="I56" s="9" t="inlineStr">
+        <v>64.56</v>
+      </c>
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>2.565</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.505</v>
+        <v>2.23</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3009,39 +3009,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>0.0073</v>
+        <v>0.865</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>657300</v>
+        <v>1520300</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H57" t="n">
-        <v>48.73</v>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.41</v>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2.785</v>
+        <v>0.868</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2.681</v>
+        <v>0.87</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3054,28 +3054,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>-0.0054</v>
+        <v>1.76</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0.0173</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>651200</v>
+        <v>1398500</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.15</v>
+        <v>0.28</v>
       </c>
       <c r="H58" t="n">
-        <v>33.99</v>
+        <v>49.91</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.918</v>
+        <v>1.754</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>2.042</v>
+        <v>1.784</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3099,39 +3099,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.695</v>
+        <v>2.68</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>0.0296</v>
+        <v>0.0113</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>650500</v>
+        <v>1382300</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="H59" t="n">
-        <v>74.79000000000001</v>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
+        <v>62.16</v>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.612</v>
+        <v>2.583</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.518</v>
+        <v>2.56</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3144,28 +3144,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>SKYWLD</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>10.04</v>
+        <v>0.405</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>0.004</v>
+        <v>0.0519</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>641700</v>
+        <v>1369400</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.05</v>
+        <v>2.32</v>
       </c>
       <c r="H60" t="n">
-        <v>43.15</v>
+        <v>60.2</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>10.097</v>
+        <v>0.391</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>10.249</v>
+        <v>0.397</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3189,28 +3189,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.285</v>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>605600</v>
+        <v>1362600</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="H61" t="n">
-        <v>38.24</v>
+        <v>37.25</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.608</v>
+        <v>0.294</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.649</v>
+        <v>0.309</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3234,39 +3234,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>-0.009300000000000001</v>
+        <v>0.23</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>571200</v>
+        <v>1358800</v>
       </c>
       <c r="G62" s="5" t="n">
         <v>0.05</v>
       </c>
       <c r="H62" t="n">
-        <v>51.34</v>
-      </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>31.25</v>
+      </c>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.068</v>
+        <v>0.258</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1.03</v>
+        <v>0.311</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3279,39 +3279,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>-0.0033</v>
+        <v>0.55</v>
+      </c>
+      <c r="E63" s="9" t="n">
+        <v>-0.0179</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>561400</v>
+        <v>1340500</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.19</v>
+        <v>0.08</v>
       </c>
       <c r="H63" t="n">
-        <v>51.28</v>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.4</v>
+      </c>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>2.98</v>
+        <v>0.511</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>3.036</v>
+        <v>0.428</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3324,39 +3324,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0466</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SRKKAI</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>-0.0091</v>
+        <v>0.34</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0.0149</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>559900</v>
+        <v>1318900</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.54</v>
+        <v>0.25</v>
       </c>
       <c r="H64" t="n">
-        <v>56.01</v>
-      </c>
-      <c r="I64" s="9" t="inlineStr">
+        <v>58.44</v>
+      </c>
+      <c r="I64" s="10" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.527</v>
+        <v>0.323</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.533</v>
+        <v>0.338</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3369,39 +3369,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>0.0153</v>
+        <v>0.805</v>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>547600</v>
+        <v>1294100</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="H65" t="n">
-        <v>71.98</v>
-      </c>
-      <c r="I65" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.65</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2.909</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>2.761</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3414,45 +3414,1708 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>7.74</v>
+        <v>2.29</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>0.0013</v>
+        <v>0.0457</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>521300</v>
+        <v>1280500</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.04</v>
+        <v>0.66</v>
       </c>
       <c r="H66" t="n">
-        <v>48.67</v>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.77</v>
+      </c>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>7.77</v>
+        <v>2.04</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>7.755</v>
+        <v>1.93</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>5216</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>NEXG</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0.0345</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>1274000</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H67" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0.0309</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>1270400</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H68" t="n">
+        <v>65.43000000000001</v>
+      </c>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="7" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MFGROUP</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>1178300</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H69" t="n">
+        <v>45.51</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0373</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>VERDANT</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E70" s="9" t="n">
+        <v>-0.0182</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>1153100</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H70" t="n">
+        <v>66.38</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="7" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>1141100</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H71" t="n">
+        <v>62.06</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0353</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>WESTRVR</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>1125200</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H72" t="n">
+        <v>71.67</v>
+      </c>
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>1077600</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H73" t="n">
+        <v>63.73</v>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>5.054</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>1064800</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H74" t="n">
+        <v>74.22</v>
+      </c>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>1038900</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H75" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>5.598</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>5.736</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>1038000</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H76" t="n">
+        <v>78.03</v>
+      </c>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E77" s="9" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>1005200</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H77" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0469</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>GTA</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>1005000</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H78" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="K78" s="2" t="n"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E79" s="9" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>967900</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H79" t="n">
+        <v>77.17</v>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>1.055</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>955500</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H80" t="n">
+        <v>67.72</v>
+      </c>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="7" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>955500</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H81" t="n">
+        <v>48.87</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>1.322</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>954600</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H82" t="n">
+        <v>63.32</v>
+      </c>
+      <c r="I82" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>2.977</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>UEMS</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>914500</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H83" t="n">
+        <v>34.36</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0.008199999999999999</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>869500</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H84" t="n">
+        <v>60.55</v>
+      </c>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>825900</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H85" t="n">
+        <v>70.94</v>
+      </c>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>2.905</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="7" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>823900</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H86" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="7" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="E87" s="9" t="n">
+        <v>-0.0066</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>784700</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H87" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>3.036</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>781500</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H88" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>1.322</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="7" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="E89" s="9" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>779500</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H89" t="n">
+        <v>35.32</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>4.776</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>4.916</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="7" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="E90" s="9" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>768900</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H90" t="n">
+        <v>33.99</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>1.918</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>2.042</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="7" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="E91" s="9" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>761900</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H91" t="n">
+        <v>25.91</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>7.747</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>8.164</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>758100</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H92" t="n">
+        <v>49.71</v>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>2.786</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>2.681</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E93" s="9" t="n">
+        <v>-0.0152</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>754900</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H93" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="I93" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="7" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E94" s="9" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>729800</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H94" t="n">
+        <v>63.04</v>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="7" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>684100</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H95" t="n">
+        <v>49.21</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>7.771</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>7.755</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="7" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0259</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>668100</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H96" t="n">
+        <v>46</v>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="7" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0466</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>SRKKAI</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>602800</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H97" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="I97" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="7" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>585600</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H98" t="n">
+        <v>40.58</v>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>4.402</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>4.476</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="7" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E99" s="9" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>584900</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H99" t="n">
+        <v>53.44</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="7" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0273</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>VLB</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E100" s="9" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>554300</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H100" t="n">
+        <v>61.19</v>
+      </c>
+      <c r="I100" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="7" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5264</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>MALAKOF</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0.0199</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>552500</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H101" t="n">
+        <v>42.06</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>532800</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H102" t="n">
+        <v>69.54000000000001</v>
+      </c>
+      <c r="I102" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>3.868</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="7" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="E103" s="9" t="n">
+        <v>-0.0219</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>520100</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H103" t="n">
+        <v>73.92</v>
+      </c>
+      <c r="I103" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>2.572</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>1.953</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M66"/>
+  <autoFilter ref="A1:M103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-06/bursa-report-2026-10-06.xlsx
+++ b/docs/downloads/2026-10-06/bursa-report-2026-10-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-06" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-06'!$A$1:$M$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-06'!$A$1:$M$132</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M103"/>
+  <dimension ref="A1:M132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.1538</v>
+        <v>0.2308</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>144184500</v>
+        <v>328977900</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.29</v>
+        <v>0.67</v>
       </c>
       <c r="H2" t="n">
-        <v>17.7</v>
+        <v>19.11</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.204</v>
+        <v>0.205</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.425</v>
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.245</v>
+        <v>0.25</v>
       </c>
       <c r="E3" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>56670900</v>
+        <v>62343100</v>
       </c>
       <c r="G3" s="5" t="n"/>
       <c r="I3" s="6" t="inlineStr">
@@ -639,10 +639,10 @@
         <v>-0.0156</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>22147100</v>
+        <v>30023500</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.48</v>
+        <v>0.65</v>
       </c>
       <c r="H4" t="n">
         <v>73.81</v>
@@ -684,10 +684,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>21189700</v>
+        <v>21608200</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>3.71</v>
+        <v>3.78</v>
       </c>
       <c r="H5" t="n">
         <v>83.98999999999999</v>
@@ -714,39 +714,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0183</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>SALUTE</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>-0.009899999999999999</v>
+        <v>0.115</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>12913100</v>
+        <v>14568700</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.49</v>
+        <v>1.98</v>
       </c>
       <c r="H6" t="n">
-        <v>58.53</v>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.3</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.481</v>
+        <v>0.115</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.475</v>
+        <v>0.109</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -759,39 +759,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0183</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SALUTE</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.0455</v>
+        <v>0.82</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>-0.018</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>11105200</v>
+        <v>14143500</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1.51</v>
+        <v>2.05</v>
       </c>
       <c r="H7" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.78</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.115</v>
+        <v>0.779</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.109</v>
+        <v>0.773</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -804,28 +804,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0.012</v>
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10885300</v>
+        <v>13439000</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.58</v>
+        <v>0.51</v>
       </c>
       <c r="H8" t="n">
-        <v>73.41</v>
+        <v>58.53</v>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.781</v>
+        <v>0.481</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.773</v>
+        <v>0.475</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -864,10 +864,10 @@
         <v>0.0307</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9774000</v>
+        <v>10490900</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="H9" t="n">
         <v>66.83</v>
@@ -894,39 +894,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0143</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KEYASIC</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>0</v>
+        <v>0.605</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9114200</v>
+        <v>10353000</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.06</v>
+        <v>0.4</v>
       </c>
       <c r="H10" t="n">
-        <v>53.68</v>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.92</v>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.063</v>
+        <v>0.572</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.058</v>
+        <v>0.499</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -948,19 +948,19 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.115</v>
+        <v>0.12</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.2105</v>
+        <v>0.2632</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8831600</v>
+        <v>9962000</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>5.88</v>
+        <v>6.63</v>
       </c>
       <c r="H11" t="n">
-        <v>66.62</v>
+        <v>68.64</v>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0.083</v>
@@ -984,28 +984,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0143</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>KEYASIC</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>0.0588</v>
+        <v>0.06</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>8723500</v>
+        <v>9924200</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.13</v>
+        <v>1.15</v>
       </c>
       <c r="H12" t="n">
-        <v>62.14</v>
+        <v>47.86</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.163</v>
+        <v>0.063</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.127</v>
+        <v>0.058</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1029,39 +1029,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>-0.008199999999999999</v>
+        <v>0.175</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0.0294</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>8295300</v>
+        <v>9354600</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.32</v>
+        <v>0.14</v>
       </c>
       <c r="H13" t="n">
-        <v>71.92</v>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.35</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.572</v>
+        <v>0.162</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.499</v>
+        <v>0.127</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1074,28 +1074,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.375</v>
+        <v>0.63</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>-0.0132</v>
+        <v>-0.0156</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>7458500</v>
+        <v>8085800</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.18</v>
+        <v>0.44</v>
       </c>
       <c r="H14" t="n">
-        <v>68.56999999999999</v>
+        <v>64.97</v>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.347</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.221</v>
+        <v>0.505</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1119,28 +1119,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.38</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6938300</v>
+        <v>7984000</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.38</v>
+        <v>0.19</v>
       </c>
       <c r="H15" t="n">
-        <v>66.09999999999999</v>
+        <v>70.89</v>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.347</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.505</v>
+        <v>0.221</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1164,28 +1164,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>0.0608</v>
+        <v>1.18</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>6059500</v>
+        <v>6809700</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>4.9</v>
+        <v>2.33</v>
       </c>
       <c r="H16" t="n">
-        <v>69.20999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.959</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1209,28 +1209,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>-0.0167</v>
+        <v>0.8</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0.08109999999999999</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5997700</v>
+        <v>6407700</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>2.06</v>
+        <v>5.18</v>
       </c>
       <c r="H17" t="n">
-        <v>75.17</v>
+        <v>70.77</v>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.959</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.83</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1254,39 +1254,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>0</v>
+        <v>0.645</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0.1316</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5458800</v>
+        <v>6121900</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.49</v>
+        <v>1.9</v>
       </c>
       <c r="H18" t="n">
-        <v>38.38</v>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>87.37</v>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.405</v>
+        <v>0.467</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.411</v>
+        <v>0.428</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1299,28 +1299,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.195</v>
+        <v>0.11</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>-0.0488</v>
+        <v>-0.0435</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4545600</v>
+        <v>5943000</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.19</v>
+        <v>0.86</v>
       </c>
       <c r="H19" t="n">
-        <v>51.26</v>
+        <v>41.61</v>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.196</v>
+        <v>0.117</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.182</v>
+        <v>0.123</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1344,28 +1344,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.37</v>
+        <v>0.76</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.0137</v>
+        <v>0.1515</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4470400</v>
+        <v>5938300</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.57</v>
+        <v>2.59</v>
       </c>
       <c r="H20" t="n">
-        <v>67.61</v>
+        <v>79.75</v>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.342</v>
+        <v>0.553</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.321</v>
+        <v>0.443</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1389,40 +1389,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>OWG</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0.05</v>
+        <v>0.005</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>4467900</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>18.81</v>
-      </c>
-      <c r="H21" t="n">
-        <v>69.03</v>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>0.188</v>
-      </c>
+        <v>5710000</v>
+      </c>
+      <c r="G21" s="5" t="n"/>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
     </row>
@@ -1434,28 +1425,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>-0.0435</v>
+        <v>0.305</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4385300</v>
+        <v>5545400</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.64</v>
+        <v>0.28</v>
       </c>
       <c r="H22" t="n">
-        <v>41.61</v>
+        <v>53.3</v>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
@@ -1463,10 +1454,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.117</v>
+        <v>0.303</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.123</v>
+        <v>0.294</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1479,39 +1470,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0258</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AGMO</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>0.0339</v>
+        <v>0.395</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4188200</v>
+        <v>5473400</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>9.73</v>
+        <v>0.49</v>
       </c>
       <c r="H23" t="n">
-        <v>61.78</v>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.38</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.278</v>
+        <v>0.405</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.305</v>
+        <v>0.411</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1524,28 +1515,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>0.1404</v>
+        <v>0.365</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4115600</v>
+        <v>5291900</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1.28</v>
+        <v>0.68</v>
       </c>
       <c r="H24" t="n">
-        <v>87.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
@@ -1553,10 +1544,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.468</v>
+        <v>0.342</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.428</v>
+        <v>0.321</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1569,28 +1560,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
         <v>0.78</v>
       </c>
-      <c r="E25" s="3" t="n">
-        <v>0.1818</v>
+      <c r="E25" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4007800</v>
+        <v>5197100</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1.75</v>
+        <v>0.37</v>
       </c>
       <c r="H25" t="n">
-        <v>80.67</v>
+        <v>53.15</v>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
@@ -1598,10 +1589,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.555</v>
+        <v>0.775</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.443</v>
+        <v>0.775</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1614,28 +1605,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>0</v>
+        <v>0.195</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>-0.0488</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3924400</v>
+        <v>4845000</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="H26" t="n">
-        <v>53.3</v>
+        <v>51.26</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
@@ -1643,10 +1634,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.303</v>
+        <v>0.196</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.294</v>
+        <v>0.182</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1659,39 +1650,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1.3</v>
+        <v>0.41</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.0156</v>
+        <v>0.025</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3820600</v>
+        <v>4773800</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.32</v>
+        <v>0.42</v>
       </c>
       <c r="H27" t="n">
-        <v>45.24</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.7</v>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.339</v>
+        <v>0.383</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1.305</v>
+        <v>0.374</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1704,28 +1695,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.79</v>
+        <v>1.31</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.0064</v>
+        <v>0.0234</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3089900</v>
+        <v>4717900</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.06</v>
+        <v>0.39</v>
       </c>
       <c r="H28" t="n">
-        <v>62.83</v>
+        <v>46.57</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
@@ -1733,10 +1724,10 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.747</v>
+        <v>1.34</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.696</v>
+        <v>1.305</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1749,28 +1740,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>OWG</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>0</v>
+        <v>0.205</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0.025</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3075900</v>
+        <v>4611000</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.3</v>
+        <v>19.42</v>
       </c>
       <c r="H29" t="n">
-        <v>53.69</v>
+        <v>66.73</v>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
@@ -1778,10 +1769,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.608</v>
+        <v>0.184</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.609</v>
+        <v>0.188</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1794,28 +1785,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0258</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>AGMO</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>0</v>
+        <v>0.3</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2838100</v>
+        <v>4523600</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.2</v>
+        <v>10.51</v>
       </c>
       <c r="H30" t="n">
-        <v>53.15</v>
+        <v>59.88</v>
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
@@ -1823,10 +1814,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.775</v>
+        <v>0.277</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.775</v>
+        <v>0.305</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1839,39 +1830,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>0.0148</v>
+        <v>0.615</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2813400</v>
+        <v>4402400</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.15</v>
+        <v>0.43</v>
       </c>
       <c r="H31" t="n">
-        <v>44.76</v>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.69</v>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2.097</v>
+        <v>0.608</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>2.075</v>
+        <v>0.609</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1884,39 +1875,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1.86</v>
+        <v>0.725</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>0.0164</v>
+        <v>0.0211</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2681200</v>
+        <v>4251800</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.11</v>
+        <v>0.58</v>
       </c>
       <c r="H32" t="n">
-        <v>62.63</v>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.38</v>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.769</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1.602</v>
+        <v>0.673</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1929,28 +1920,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>0.0274</v>
+        <v>1.83</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2632400</v>
+        <v>4057100</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="H33" t="n">
-        <v>57.94</v>
+        <v>60.45</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1958,10 +1949,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.367</v>
+        <v>1.767</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.368</v>
+        <v>1.601</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1974,28 +1965,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>0.0235</v>
+        <v>0.785</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2586700</v>
+        <v>4012300</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="H34" t="n">
-        <v>52.77</v>
+        <v>61.97</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
@@ -2003,10 +1994,10 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>5.668</v>
+        <v>0.747</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>5.278</v>
+        <v>0.696</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2019,28 +2010,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.44</v>
+        <v>0.59</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0.0115</v>
+        <v>0.0442</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2561900</v>
+        <v>3794400</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.12</v>
+        <v>0.8</v>
       </c>
       <c r="H35" t="n">
-        <v>66.17</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
@@ -2048,10 +2039,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.397</v>
+        <v>0.531</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.337</v>
+        <v>0.484</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2064,39 +2055,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2.94</v>
+        <v>5.61</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.0068</v>
+        <v>0.0126</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>2502700</v>
+        <v>3680000</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.78</v>
+        <v>0.26</v>
       </c>
       <c r="H36" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.56</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>2.541</v>
+        <v>5.663</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>2.079</v>
+        <v>5.276</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2109,28 +2100,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0.0231</v>
+        <v>0.0197</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>2472000</v>
+        <v>3473800</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H37" t="n">
-        <v>46.26</v>
+        <v>46.25</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2138,10 +2129,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>2.259</v>
+        <v>2.098</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2.218</v>
+        <v>2.075</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2154,40 +2145,33 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>EVOCOM</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>0.0069</v>
+        <v>0.11</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>2330200</v>
+        <v>3293600</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H38" t="n">
-        <v>61.88</v>
-      </c>
-      <c r="I38" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>2.751</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>2.569</v>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
     </row>
@@ -2199,28 +2183,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>-0.026</v>
+        <v>0.155</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>2192400</v>
+        <v>3273600</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.25</v>
+        <v>0.93</v>
       </c>
       <c r="H39" t="n">
-        <v>68.29000000000001</v>
+        <v>52.53</v>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
@@ -2228,10 +2212,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.345</v>
+        <v>0.153</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.317</v>
+        <v>0.151</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2244,39 +2228,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>0.002</v>
+        <v>0.725</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>2164500</v>
+        <v>3222000</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="H40" t="n">
-        <v>41.51</v>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.34</v>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>10.095</v>
+        <v>0.658</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>10.249</v>
+        <v>0.595</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2289,39 +2273,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.405</v>
+        <v>2.19</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.0125</v>
+        <v>0.0139</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2040800</v>
+        <v>3100100</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="H41" t="n">
-        <v>68.66</v>
-      </c>
-      <c r="I41" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.59</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.383</v>
+        <v>2.258</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.374</v>
+        <v>2.218</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2334,28 +2318,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>0.0054</v>
+        <v>0.865</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1987000</v>
+        <v>3054800</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.39</v>
+        <v>0.16</v>
       </c>
       <c r="H42" t="n">
-        <v>64</v>
+        <v>46.41</v>
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
@@ -2363,10 +2347,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.901</v>
+        <v>0.868</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.858</v>
+        <v>0.87</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2379,28 +2363,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.55</v>
+        <v>2.92</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.068</v>
+        <v>0.0069</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1962300</v>
+        <v>3002100</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>4.48</v>
+        <v>0.32</v>
       </c>
       <c r="H43" t="n">
-        <v>71.17</v>
+        <v>61.88</v>
       </c>
       <c r="I43" s="10" t="inlineStr">
         <is>
@@ -2408,10 +2392,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.506</v>
+        <v>2.751</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.5</v>
+        <v>2.569</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2424,39 +2408,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>5.01</v>
+        <v>10.02</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1949100</v>
+        <v>2947300</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="H44" t="n">
-        <v>61.61</v>
-      </c>
-      <c r="I44" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.51</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>4.887</v>
+        <v>10.095</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>4.611</v>
+        <v>10.249</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2469,28 +2453,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.72</v>
+        <v>5.01</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.0141</v>
+        <v>0.004</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1916800</v>
+        <v>2935900</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.26</v>
+        <v>0.12</v>
       </c>
       <c r="H45" t="n">
-        <v>57.56</v>
+        <v>61.61</v>
       </c>
       <c r="I45" s="10" t="inlineStr">
         <is>
@@ -2498,10 +2482,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6870000000000001</v>
+        <v>4.887</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.673</v>
+        <v>4.611</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2514,28 +2498,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>2.61</v>
+        <v>0.375</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.0156</v>
+        <v>0.0274</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1915600</v>
+        <v>2907900</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.11</v>
+        <v>0.44</v>
       </c>
       <c r="H46" t="n">
-        <v>54.75</v>
+        <v>57.94</v>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
@@ -2543,10 +2527,10 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2.572</v>
+        <v>0.367</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2.477</v>
+        <v>0.368</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2559,39 +2543,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.735</v>
+        <v>2.51</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.0068</v>
+        <v>0.008</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1897500</v>
+        <v>2854300</v>
       </c>
       <c r="G47" s="5" t="n">
         <v>0.19</v>
       </c>
       <c r="H47" t="n">
-        <v>69.31999999999999</v>
-      </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.67</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.659</v>
+        <v>2.458</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.595</v>
+        <v>2.333</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2604,28 +2588,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>0.0265</v>
+        <v>2.9</v>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1802000</v>
+        <v>2829000</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.38</v>
+        <v>0.88</v>
       </c>
       <c r="H48" t="n">
-        <v>67.51000000000001</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
@@ -2633,10 +2617,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.53</v>
+        <v>2.537</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.484</v>
+        <v>2.079</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2649,39 +2633,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>0.0083</v>
+        <v>0.805</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1795000</v>
+        <v>2814000</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.44</v>
+        <v>0.18</v>
       </c>
       <c r="H49" t="n">
-        <v>66.92</v>
-      </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.65</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.143</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1.05</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2694,28 +2678,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E50" s="9" t="n">
-        <v>-0.009300000000000001</v>
+        <v>5.74</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0.061</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1759400</v>
+        <v>2746000</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.15</v>
+        <v>0.82</v>
       </c>
       <c r="H50" t="n">
-        <v>51.34</v>
+        <v>52.68</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2723,10 +2707,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.068</v>
+        <v>5.611</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1.03</v>
+        <v>5.739</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2739,28 +2723,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.49</v>
+        <v>2.59</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.0208</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1676100</v>
+        <v>2678500</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="H51" t="n">
-        <v>27.31</v>
+        <v>53.23</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
@@ -2768,10 +2752,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.574</v>
+        <v>2.57</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.78</v>
+        <v>2.476</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2784,28 +2768,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E52" s="9" t="n">
-        <v>-0.0339</v>
+        <v>0.435</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1671800</v>
+        <v>2665500</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="H52" t="n">
-        <v>53.39</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="I52" s="10" t="inlineStr">
         <is>
@@ -2813,10 +2797,10 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.272</v>
+        <v>0.397</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.306</v>
+        <v>0.337</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2829,39 +2813,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CENSOF</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>0.0213</v>
+        <v>1.07</v>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1671500</v>
+        <v>2615400</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>1.62</v>
+        <v>0.23</v>
       </c>
       <c r="H53" t="n">
-        <v>71.56</v>
-      </c>
-      <c r="I53" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.34</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.213</v>
+        <v>1.068</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.203</v>
+        <v>1.03</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2874,39 +2858,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>0.0058</v>
+        <v>0.38</v>
+      </c>
+      <c r="E54" s="9" t="n">
+        <v>-0.013</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1603400</v>
+        <v>2518900</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.13</v>
+        <v>0.29</v>
       </c>
       <c r="H54" t="n">
-        <v>51.97</v>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.59</v>
+      </c>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>3.581</v>
+        <v>0.346</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>2.623</v>
+        <v>0.317</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2919,28 +2903,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FPGROUP</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.43</v>
+        <v>0.55</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>0.0238</v>
+        <v>0.068</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1590600</v>
+        <v>2325600</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>1.6</v>
+        <v>5.32</v>
       </c>
       <c r="H55" t="n">
-        <v>59.94</v>
+        <v>71.17</v>
       </c>
       <c r="I55" s="10" t="inlineStr">
         <is>
@@ -2948,10 +2932,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.409</v>
+        <v>0.506</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.417</v>
+        <v>0.5</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2973,19 +2957,19 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0.0076</v>
+        <v>0.0267</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1544600</v>
+        <v>2290800</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="H56" t="n">
-        <v>64.56</v>
+        <v>67.58</v>
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
@@ -2993,10 +2977,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>2.565</v>
+        <v>2.57</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2.23</v>
+        <v>2.231</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3009,28 +2993,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E57" s="9" t="n">
-        <v>-0.005699999999999999</v>
+        <v>2.69</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0.0151</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1520300</v>
+        <v>2283400</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.08</v>
+        <v>0.43</v>
       </c>
       <c r="H57" t="n">
-        <v>46.41</v>
+        <v>62.98</v>
       </c>
       <c r="I57" s="10" t="inlineStr">
         <is>
@@ -3038,10 +3022,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.868</v>
+        <v>2.584</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.87</v>
+        <v>2.56</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3054,39 +3038,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1.76</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>0.0173</v>
+        <v>0.0108</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1398500</v>
+        <v>2176800</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.28</v>
+        <v>0.43</v>
       </c>
       <c r="H58" t="n">
-        <v>49.91</v>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.2</v>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.754</v>
+        <v>0.901</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1.784</v>
+        <v>0.858</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3099,39 +3083,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>2.68</v>
+        <v>0.49</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>0.0113</v>
+        <v>0.0208</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1382300</v>
+        <v>2123800</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.26</v>
+        <v>0.05</v>
       </c>
       <c r="H59" t="n">
-        <v>62.16</v>
-      </c>
-      <c r="I59" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.31</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2.583</v>
+        <v>0.574</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>2.56</v>
+        <v>0.78</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3144,39 +3128,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SKYWLD</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.405</v>
+        <v>0.34</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>0.0519</v>
+        <v>0.0149</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1369400</v>
+        <v>2106500</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>2.32</v>
+        <v>0.4</v>
       </c>
       <c r="H60" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.44</v>
+      </c>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.391</v>
+        <v>0.323</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.397</v>
+        <v>0.338</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3189,28 +3173,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E61" s="9" t="n">
-        <v>-0.0172</v>
+        <v>3.5</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0.0116</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1362600</v>
+        <v>2102500</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="H61" t="n">
-        <v>37.25</v>
+        <v>52.39</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
@@ -3218,10 +3202,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.294</v>
+        <v>3.583</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.309</v>
+        <v>2.623</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3234,28 +3218,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>0.0222</v>
+        <v>1.2</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1358800</v>
+        <v>2088300</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.05</v>
+        <v>0.51</v>
       </c>
       <c r="H62" t="n">
-        <v>31.25</v>
+        <v>65.7</v>
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
@@ -3263,10 +3247,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.258</v>
+        <v>1.142</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.311</v>
+        <v>1.05</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3279,28 +3263,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E63" s="9" t="n">
-        <v>-0.0179</v>
+        <v>0.705</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0.0444</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1340500</v>
+        <v>2028800</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.08</v>
+        <v>0.97</v>
       </c>
       <c r="H63" t="n">
-        <v>62.4</v>
+        <v>75.86</v>
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
@@ -3308,10 +3292,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.511</v>
+        <v>0.613</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.428</v>
+        <v>0.518</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3324,28 +3308,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.34</v>
+        <v>0.82</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0.0149</v>
+        <v>0.0123</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1318900</v>
+        <v>1959000</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.25</v>
+        <v>0.72</v>
       </c>
       <c r="H64" t="n">
-        <v>58.44</v>
+        <v>63.12</v>
       </c>
       <c r="I64" s="10" t="inlineStr">
         <is>
@@ -3353,10 +3337,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.323</v>
+        <v>0.77</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.338</v>
+        <v>0.746</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3369,39 +3353,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E65" s="9" t="n">
-        <v>-0.0062</v>
+        <v>0.235</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1294100</v>
+        <v>1928400</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.08</v>
+        <v>1.87</v>
       </c>
       <c r="H65" t="n">
-        <v>46.65</v>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.45999999999999</v>
+      </c>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.213</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.203</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3414,39 +3398,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>0.0457</v>
+        <v>0.96</v>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>-0.0052</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1280500</v>
+        <v>1830700</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.66</v>
+        <v>0.46</v>
       </c>
       <c r="H66" t="n">
-        <v>69.77</v>
-      </c>
-      <c r="I66" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.04</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>2.04</v>
+        <v>1.013</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1.93</v>
+        <v>1.076</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3459,28 +3443,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>0.0345</v>
+        <v>0.29</v>
+      </c>
+      <c r="E67" s="9" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1274000</v>
+        <v>1823600</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
       <c r="H67" t="n">
-        <v>54.5</v>
+        <v>55.52</v>
       </c>
       <c r="I67" s="10" t="inlineStr">
         <is>
@@ -3488,10 +3472,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.29</v>
+        <v>0.273</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.279</v>
+        <v>0.306</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3504,28 +3488,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.835</v>
+        <v>2.27</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.0309</v>
+        <v>0.0365</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1270400</v>
+        <v>1778800</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.47</v>
+        <v>0.91</v>
       </c>
       <c r="H68" t="n">
-        <v>65.43000000000001</v>
+        <v>68.97</v>
       </c>
       <c r="I68" s="10" t="inlineStr">
         <is>
@@ -3533,10 +3517,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.772</v>
+        <v>2.038</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.746</v>
+        <v>1.929</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3549,28 +3533,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>SKYWLD</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E69" s="8" t="n">
-        <v>0</v>
+        <v>0.405</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0.0519</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1178300</v>
+        <v>1769600</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>1.24</v>
+        <v>2.99</v>
       </c>
       <c r="H69" t="n">
-        <v>45.51</v>
+        <v>60.2</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
@@ -3578,10 +3562,10 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.261</v>
+        <v>0.391</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.265</v>
+        <v>0.397</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3594,39 +3578,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.27</v>
+        <v>0.555</v>
       </c>
       <c r="E70" s="9" t="n">
-        <v>-0.0182</v>
+        <v>-0.0089</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1153100</v>
+        <v>1751600</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.31</v>
+        <v>0.11</v>
       </c>
       <c r="H70" t="n">
-        <v>66.38</v>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.68</v>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.243</v>
+        <v>0.511</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.215</v>
+        <v>0.428</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3639,28 +3623,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.85</v>
+        <v>1.77</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.0241</v>
+        <v>0.0231</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1141100</v>
+        <v>1745300</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="H71" t="n">
-        <v>62.06</v>
+        <v>51.22</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
@@ -3668,10 +3652,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>1.755</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.746</v>
+        <v>1.784</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3684,28 +3668,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.455</v>
+        <v>0.785</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>0.0225</v>
+        <v>0.0261</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1125200</v>
+        <v>1732900</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="H72" t="n">
-        <v>71.67</v>
+        <v>68.98</v>
       </c>
       <c r="I72" s="10" t="inlineStr">
         <is>
@@ -3713,10 +3697,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4</v>
+        <v>0.713</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.359</v>
+        <v>0.637</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3729,39 +3713,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>5.25</v>
+        <v>3.02</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>0.0135</v>
+        <v>0.0033</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1077600</v>
+        <v>1670300</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.23</v>
+        <v>0.57</v>
       </c>
       <c r="H73" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="I73" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.17</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>5.03</v>
+        <v>2.982</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>5.054</v>
+        <v>3.036</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3774,39 +3758,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.505</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>0.0222</v>
+        <v>0.0202</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1064800</v>
+        <v>1654800</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.51</v>
+        <v>0.24</v>
       </c>
       <c r="H74" t="n">
-        <v>74.22</v>
-      </c>
-      <c r="I74" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.63</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.612</v>
+        <v>0.537</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.518</v>
+        <v>0.577</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3819,28 +3803,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>0.0351</v>
+        <v>4.68</v>
+      </c>
+      <c r="E75" s="9" t="n">
+        <v>-0.0064</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1038900</v>
+        <v>1637800</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.31</v>
+        <v>0.1</v>
       </c>
       <c r="H75" t="n">
-        <v>49.32</v>
+        <v>34.48</v>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
@@ -3848,10 +3832,10 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>5.598</v>
+        <v>4.775</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>5.736</v>
+        <v>4.916</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3864,28 +3848,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5277</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>FPGROUP</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>1.37</v>
+        <v>0.425</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>0.0148</v>
+        <v>0.0119</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1038000</v>
+        <v>1628100</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.35</v>
+        <v>1.64</v>
       </c>
       <c r="H76" t="n">
-        <v>78.03</v>
+        <v>58.08</v>
       </c>
       <c r="I76" s="10" t="inlineStr">
         <is>
@@ -3893,10 +3877,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.186</v>
+        <v>0.408</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.971</v>
+        <v>0.417</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3909,39 +3893,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>1618700</v>
+      </c>
+      <c r="G77" s="5" t="n">
         <v>0.57</v>
       </c>
-      <c r="E77" s="9" t="n">
-        <v>-0.008699999999999999</v>
-      </c>
-      <c r="F77" s="4" t="n">
-        <v>1005200</v>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>0.18</v>
-      </c>
       <c r="H77" t="n">
-        <v>35.28</v>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.67</v>
+      </c>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.607</v>
+        <v>0.4</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.649</v>
+        <v>0.359</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3954,28 +3938,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E78" s="8" t="n">
-        <v>0</v>
+        <v>0.845</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0.0181</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1005000</v>
+        <v>1612600</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.06</v>
+        <v>0.52</v>
       </c>
       <c r="H78" t="n">
-        <v>18.18</v>
+        <v>61.19</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
@@ -3983,9 +3967,11 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="K78" s="2" t="n"/>
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>0.746</v>
+      </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
     </row>
@@ -3997,28 +3983,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E79" s="9" t="n">
-        <v>-0.008500000000000001</v>
+        <v>1.35</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>967900</v>
+        <v>1550600</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.08</v>
+        <v>0.52</v>
       </c>
       <c r="H79" t="n">
-        <v>77.17</v>
+        <v>77.02</v>
       </c>
       <c r="I79" s="10" t="inlineStr">
         <is>
@@ -4026,10 +4012,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.055</v>
+        <v>1.184</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.895</v>
+        <v>0.97</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4042,39 +4028,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.775</v>
+        <v>1.26</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.0131</v>
+        <v>0.0413</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>955500</v>
+        <v>1544700</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.14</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>67.72</v>
-      </c>
-      <c r="I80" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.6</v>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.712</v>
+        <v>1.265</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.637</v>
+        <v>1.322</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4087,28 +4073,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>0.0496</v>
+        <v>1.84</v>
+      </c>
+      <c r="E81" s="9" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>955500</v>
+        <v>1455800</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.62</v>
+        <v>0.33</v>
       </c>
       <c r="H81" t="n">
-        <v>48.87</v>
+        <v>32.95</v>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
@@ -4116,10 +4102,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.266</v>
+        <v>1.917</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1.322</v>
+        <v>2.042</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4132,39 +4118,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>0.0127</v>
+        <v>1.63</v>
+      </c>
+      <c r="E82" s="9" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>954600</v>
+        <v>1416700</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="H82" t="n">
-        <v>63.32</v>
-      </c>
-      <c r="I82" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.28</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>2.977</v>
+        <v>1.689</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>2.785</v>
+        <v>1.805</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4177,39 +4163,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.51</v>
+        <v>0.235</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>0.0303</v>
+        <v>0.0444</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>914500</v>
+        <v>1381000</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="H83" t="n">
-        <v>34.36</v>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.19</v>
+      </c>
+      <c r="I83" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.537</v>
+        <v>0.258</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.577</v>
+        <v>0.311</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4222,39 +4208,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.285</v>
+      </c>
+      <c r="E84" s="9" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>869500</v>
+        <v>1377400</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="H84" t="n">
-        <v>60.55</v>
-      </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.25</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.582</v>
+        <v>0.294</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.578</v>
+        <v>0.309</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4267,28 +4253,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>3.28</v>
+        <v>0.295</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>0.0031</v>
+        <v>0.0172</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>825900</v>
+        <v>1375100</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.27</v>
+        <v>0.09</v>
       </c>
       <c r="H85" t="n">
-        <v>70.94</v>
+        <v>52.96</v>
       </c>
       <c r="I85" s="10" t="inlineStr">
         <is>
@@ -4296,10 +4282,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>2.905</v>
+        <v>0.29</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>2.76</v>
+        <v>0.278</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4312,28 +4298,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0396</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>ADNEX</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E86" s="8" t="n">
-        <v>0</v>
+        <v>0.445</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0.023</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>823900</v>
+        <v>1338000</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.13</v>
+        <v>2.92</v>
       </c>
       <c r="H86" t="n">
-        <v>68.36</v>
+        <v>62.16</v>
       </c>
       <c r="I86" s="10" t="inlineStr">
         <is>
@@ -4341,10 +4327,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.778</v>
+        <v>0.424</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.76</v>
+        <v>0.418</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4357,39 +4343,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="E87" s="9" t="n">
-        <v>-0.0066</v>
+        <v>3.16</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0.0032</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>784700</v>
+        <v>1327900</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="H87" t="n">
-        <v>50.32</v>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.18</v>
+      </c>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>2.979</v>
+        <v>2.974</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>3.036</v>
+        <v>2.785</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4402,39 +4388,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E88" s="8" t="n">
-        <v>0</v>
+        <v>5.24</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.0116</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>781500</v>
+        <v>1320100</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="H88" t="n">
-        <v>30.34</v>
-      </c>
-      <c r="I88" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.31</v>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.322</v>
+        <v>5.029</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1.316</v>
+        <v>5.054</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4447,39 +4433,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>4.69</v>
+        <v>1.16</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>-0.0042</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>779500</v>
+        <v>1317700</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="H89" t="n">
-        <v>35.32</v>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.17</v>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>4.776</v>
+        <v>1.055</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>4.916</v>
+        <v>0.895</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4492,28 +4478,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>1.85</v>
+        <v>0.27</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>-0.0054</v>
+        <v>-0.0182</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>768900</v>
+        <v>1315000</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.17</v>
+        <v>0.35</v>
       </c>
       <c r="H90" t="n">
-        <v>33.99</v>
+        <v>66.38</v>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
@@ -4521,10 +4507,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.918</v>
+        <v>0.243</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>2.042</v>
+        <v>0.215</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4537,39 +4523,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>7.44</v>
+        <v>0.445</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>-0.0027</v>
+        <v>-0.022</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>761900</v>
+        <v>1310100</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.08</v>
+        <v>0.21</v>
       </c>
       <c r="H91" t="n">
-        <v>25.91</v>
-      </c>
-      <c r="I91" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.49</v>
+      </c>
+      <c r="I91" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>7.747</v>
+        <v>0.415</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>8.164</v>
+        <v>0.408</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4582,28 +4568,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>0.011</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E92" s="9" t="n">
+        <v>-0.0261</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>758100</v>
+        <v>1263200</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="H92" t="n">
-        <v>49.71</v>
+        <v>33.3</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
@@ -4611,10 +4597,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>2.786</v>
+        <v>0.606</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>2.681</v>
+        <v>0.649</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4627,39 +4613,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E93" s="9" t="n">
-        <v>-0.0152</v>
+        <v>2.75</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0.0073</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>754900</v>
+        <v>1225600</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.23</v>
+        <v>0.09</v>
       </c>
       <c r="H93" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="I93" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.73</v>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.639</v>
+        <v>2.785</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.607</v>
+        <v>2.681</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4672,40 +4658,33 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E94" s="9" t="n">
-        <v>-0.0098</v>
+        <v>0.225</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>729800</v>
+        <v>1203700</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H94" t="n">
-        <v>63.04</v>
+        <v>0.03</v>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J94" s="2" t="n">
-        <v>0.956</v>
-      </c>
-      <c r="K94" s="2" t="n">
-        <v>0.803</v>
-      </c>
+      <c r="J94" s="2" t="n"/>
+      <c r="K94" s="2" t="n"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
     </row>
@@ -4717,28 +4696,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>7.75</v>
+        <v>0.485</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>0.0026</v>
+        <v>0.0211</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>684100</v>
+        <v>1195600</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.06</v>
+        <v>0.37</v>
       </c>
       <c r="H95" t="n">
-        <v>49.21</v>
+        <v>64.33</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4746,10 +4725,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>7.771</v>
+        <v>0.461</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>7.755</v>
+        <v>0.417</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4762,28 +4741,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="E96" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>668100</v>
+        <v>1178300</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.11</v>
+        <v>1.24</v>
       </c>
       <c r="H96" t="n">
-        <v>46</v>
+        <v>45.51</v>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
@@ -4791,10 +4770,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.519</v>
+        <v>0.261</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.531</v>
+        <v>0.265</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4807,28 +4786,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0466</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SRKKAI</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E97" s="8" t="n">
-        <v>0</v>
+        <v>0.255</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>0.02</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>602800</v>
+        <v>1133100</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.58</v>
+        <v>0.44</v>
       </c>
       <c r="H97" t="n">
-        <v>58.09</v>
+        <v>49.14</v>
       </c>
       <c r="I97" s="10" t="inlineStr">
         <is>
@@ -4836,10 +4815,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.527</v>
+        <v>0.254</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.533</v>
+        <v>0.264</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4852,28 +4831,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="E98" s="3" t="n">
-        <v>0.0121</v>
+        <v>0.275</v>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>585600</v>
+        <v>1082500</v>
       </c>
       <c r="G98" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H98" t="n">
-        <v>40.58</v>
+        <v>18.18</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
@@ -4881,11 +4860,9 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>4.402</v>
-      </c>
-      <c r="K98" s="2" t="n">
-        <v>4.476</v>
-      </c>
+        <v>0.295</v>
+      </c>
+      <c r="K98" s="2" t="n"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
     </row>
@@ -4897,39 +4874,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1.17</v>
+        <v>0.27</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0182</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>584900</v>
+        <v>1064500</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.06</v>
+        <v>0.51</v>
       </c>
       <c r="H99" t="n">
-        <v>53.44</v>
-      </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.44</v>
+      </c>
+      <c r="I99" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.158</v>
+        <v>0.251</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1.113</v>
+        <v>0.256</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4942,28 +4919,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E100" s="9" t="n">
-        <v>-0.0051</v>
+        <v>3.28</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0.0031</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>554300</v>
+        <v>1035300</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="H100" t="n">
-        <v>61.19</v>
+        <v>70.94</v>
       </c>
       <c r="I100" s="10" t="inlineStr">
         <is>
@@ -4971,10 +4948,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.922</v>
+        <v>2.905</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0.838</v>
+        <v>2.76</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4987,28 +4964,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E101" s="3" t="n">
-        <v>0.0199</v>
+        <v>1.16</v>
+      </c>
+      <c r="E101" s="9" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>552500</v>
+        <v>1008500</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="H101" t="n">
-        <v>42.06</v>
+        <v>51.81</v>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
@@ -5016,10 +4993,10 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.791</v>
+        <v>1.157</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.805</v>
+        <v>1.113</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5032,28 +5009,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="E102" s="3" t="n">
-        <v>0.0119</v>
+        <v>0.485</v>
+      </c>
+      <c r="E102" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>532800</v>
+        <v>1007700</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.06</v>
+        <v>0.52</v>
       </c>
       <c r="H102" t="n">
-        <v>69.54000000000001</v>
+        <v>61.65</v>
       </c>
       <c r="I102" s="10" t="inlineStr">
         <is>
@@ -5061,10 +5038,10 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>3.868</v>
+        <v>0.456</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>3.37</v>
+        <v>0.46</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5077,45 +5054,1350 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>IFCAMSC</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="E103" s="9" t="n">
-        <v>-0.0219</v>
+        <v>0.205</v>
+      </c>
+      <c r="E103" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>520100</v>
+        <v>1004500</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.14</v>
+        <v>1.9</v>
       </c>
       <c r="H103" t="n">
-        <v>73.92</v>
-      </c>
-      <c r="I103" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.37</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>2.572</v>
+        <v>0.205</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>1.953</v>
+        <v>0.215</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>989600</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H104" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>7.497</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>7.768</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="7" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>982700</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H105" t="n">
+        <v>42.98</v>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>4.407</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>4.477</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="7" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E106" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>947700</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H106" t="n">
+        <v>59.45</v>
+      </c>
+      <c r="I106" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="7" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>0466</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SRKKAI</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E107" s="9" t="n">
+        <v>-0.0182</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>947700</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H107" t="n">
+        <v>54.08</v>
+      </c>
+      <c r="I107" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="7" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="E108" s="9" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>914700</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H108" t="n">
+        <v>26.21</v>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>7.748</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>8.164999999999999</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="7" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>5264</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>MALAKOF</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0.0265</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>891300</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H109" t="n">
+        <v>43.76</v>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="7" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>889000</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H110" t="n">
+        <v>48.67</v>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>7.755</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="7" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E111" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>862100</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H111" t="n">
+        <v>64.81</v>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="7" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>852900</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H112" t="n">
+        <v>69.08</v>
+      </c>
+      <c r="I112" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>3.866</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="7" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E113" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>836500</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H113" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="I113" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="7" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E114" s="9" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>785200</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H114" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="I114" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="7" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>781700</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H115" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>1.323</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="7" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>780700</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H116" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="I116" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>6.977</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>6.657</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="7" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>RANHILL</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>712200</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H117" t="n">
+        <v>70.67</v>
+      </c>
+      <c r="I117" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>3.106</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>2.679</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="7" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0259</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E118" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>691400</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H118" t="n">
+        <v>46</v>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="7" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>688000</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H119" t="n">
+        <v>64.66</v>
+      </c>
+      <c r="I119" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="7" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E120" s="9" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>681700</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H120" t="n">
+        <v>61.73</v>
+      </c>
+      <c r="I120" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>1.272</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>1.176</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="7" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>0273</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>VLB</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E121" s="9" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>634800</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H121" t="n">
+        <v>61.19</v>
+      </c>
+      <c r="I121" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="7" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>626300</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H122" t="n">
+        <v>58.31</v>
+      </c>
+      <c r="I122" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>5.271</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>5.297</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="7" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="E123" s="9" t="n">
+        <v>-0.0188</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>625500</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H123" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="I123" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>2.573</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>1.953</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="7" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>593900</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H124" t="n">
+        <v>62.23</v>
+      </c>
+      <c r="I124" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>3.837</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>3.519</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="7" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>580200</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H125" t="n">
+        <v>47.85</v>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>1.161</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="7" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E126" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>572100</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="I126" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>13.086</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>13.646</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="7" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>0325</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E127" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="4" t="n">
+        <v>571300</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H127" t="n">
+        <v>60.29</v>
+      </c>
+      <c r="I127" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="7" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>566000</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H128" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>1.962</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="7" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v>531300</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H129" t="n">
+        <v>45.23</v>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>2.052</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="7" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>IOICORP</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F130" s="4" t="n">
+        <v>524800</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H130" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>4.705</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>4.617</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="7" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E131" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="4" t="n">
+        <v>510000</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H131" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="I131" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="7" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0291</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>CHB</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>504000</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H132" t="n">
+        <v>74.48</v>
+      </c>
+      <c r="I132" s="10" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>2.335</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M103"/>
+  <autoFilter ref="A1:M132"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-06/bursa-report-2026-10-06.xlsx
+++ b/docs/downloads/2026-10-06/bursa-report-2026-10-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-06" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-06'!$A$1:$M$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-06'!$A$1:$M$162</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -83,8 +83,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M132"/>
+  <dimension ref="A1:M162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.2308</v>
+        <v>0.3846</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>328977900</v>
+        <v>432901600</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
       <c r="H2" t="n">
-        <v>19.11</v>
+        <v>21.77</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.205</v>
+        <v>0.206</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.425</v>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>62343100</v>
+        <v>63672300</v>
       </c>
       <c r="G3" s="5" t="n"/>
       <c r="I3" s="6" t="inlineStr">
@@ -633,21 +633,21 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>-0.0156</v>
+        <v>0.32</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>30023500</v>
+        <v>30284600</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H4" t="n">
-        <v>73.81</v>
-      </c>
-      <c r="I4" s="10" t="inlineStr">
+        <v>76.48</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -684,15 +684,15 @@
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>21608200</v>
+        <v>21816000</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="H5" t="n">
         <v>83.98999999999999</v>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -714,39 +714,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0183</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SALUTE</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.0455</v>
+        <v>0.155</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>-0.06059999999999999</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>14568700</v>
+        <v>16148900</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>1.98</v>
+        <v>0.4</v>
       </c>
       <c r="H6" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.89</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.115</v>
+        <v>0.159</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.109</v>
+        <v>0.147</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -759,39 +759,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0183</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SALUTE</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>-0.018</v>
+        <v>0.115</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>14143500</v>
+        <v>16143100</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>64.78</v>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.3</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.779</v>
+        <v>0.115</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.773</v>
+        <v>0.109</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -804,39 +804,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>-0.009899999999999999</v>
+        <v>0.605</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>13439000</v>
+        <v>15594500</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.51</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="n">
-        <v>58.53</v>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
+        <v>71.92</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.481</v>
+        <v>0.572</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.475</v>
+        <v>0.499</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -849,39 +849,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0.0307</v>
+        <v>0.5</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>10490900</v>
+        <v>15557100</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.85</v>
+        <v>0.59</v>
       </c>
       <c r="H9" t="n">
-        <v>66.83</v>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
+        <v>58.53</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.756</v>
+        <v>0.481</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.704</v>
+        <v>0.475</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -894,39 +894,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>-0.008199999999999999</v>
+        <v>0.82</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>-0.018</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10353000</v>
+        <v>15033400</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.4</v>
+        <v>2.18</v>
       </c>
       <c r="H10" t="n">
-        <v>71.92</v>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
+        <v>64.78</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.572</v>
+        <v>0.779</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.499</v>
+        <v>0.773</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -948,27 +948,27 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.12</v>
+        <v>0.115</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.2632</v>
+        <v>0.2105</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>9962000</v>
+        <v>11746100</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>6.63</v>
+        <v>7.81</v>
       </c>
       <c r="H11" t="n">
-        <v>68.64</v>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
+        <v>66.62</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.094</v>
+        <v>0.093</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0.083</v>
@@ -984,39 +984,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0143</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KEYASIC</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>-0.07690000000000001</v>
+        <v>0.84</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.0307</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>9924200</v>
+        <v>11645800</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>47.86</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.83</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.063</v>
+        <v>0.756</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.058</v>
+        <v>0.704</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1029,28 +1029,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0143</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>KEYASIC</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>0.0294</v>
+        <v>0.065</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>9354600</v>
+        <v>9995300</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.14</v>
+        <v>1.16</v>
       </c>
       <c r="H13" t="n">
-        <v>60.35</v>
+        <v>53.68</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.162</v>
+        <v>0.063</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.127</v>
+        <v>0.058</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1074,39 +1074,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>-0.0156</v>
+        <v>0.38</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>8085800</v>
+        <v>9970300</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.44</v>
+        <v>0.23</v>
       </c>
       <c r="H14" t="n">
-        <v>64.97</v>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
+        <v>70.89</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.347</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.505</v>
+        <v>0.221</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1119,39 +1119,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>0</v>
+        <v>0.175</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.0294</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>7984000</v>
+        <v>9666500</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="H15" t="n">
-        <v>70.89</v>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.35</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.347</v>
+        <v>0.162</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.221</v>
+        <v>0.127</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1164,39 +1164,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>-0.0167</v>
+        <v>0.63</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>6809700</v>
+        <v>9038300</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>2.33</v>
+        <v>0.49</v>
       </c>
       <c r="H16" t="n">
-        <v>75.17</v>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
+        <v>64.97</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.959</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.83</v>
+        <v>0.505</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1209,40 +1209,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>0.08109999999999999</v>
+        <v>0.005</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>6407700</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="H17" t="n">
-        <v>70.77</v>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>0.6909999999999999</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>0.6830000000000001</v>
-      </c>
+        <v>8712000</v>
+      </c>
+      <c r="G17" s="5" t="n"/>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
     </row>
@@ -1254,39 +1245,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>0.1316</v>
+        <v>0.11</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>-0.0435</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>6121900</v>
+        <v>8337900</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>1.9</v>
+        <v>1.21</v>
       </c>
       <c r="H18" t="n">
-        <v>87.37</v>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.61</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.467</v>
+        <v>0.117</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.428</v>
+        <v>0.123</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1299,39 +1290,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>-0.0435</v>
+        <v>0.6</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0.0619</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5943000</v>
+        <v>7416600</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.86</v>
+        <v>1.57</v>
       </c>
       <c r="H19" t="n">
-        <v>41.61</v>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.69</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.117</v>
+        <v>0.532</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.123</v>
+        <v>0.484</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1344,39 +1335,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>0.1515</v>
+        <v>0.065</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5938300</v>
+        <v>7300500</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>2.59</v>
+        <v>0.92</v>
       </c>
       <c r="H20" t="n">
-        <v>79.75</v>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.553</v>
+        <v>0.073</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.443</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1389,31 +1380,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>0</v>
+        <v>0.785</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.0608</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5710000</v>
-      </c>
-      <c r="G21" s="5" t="n"/>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="n"/>
-      <c r="K21" s="2" t="n"/>
+        <v>7053100</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>69.20999999999999</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0.6830000000000001</v>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
     </row>
@@ -1425,39 +1425,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>0</v>
+        <v>1.17</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>5545400</v>
+        <v>7009900</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.28</v>
+        <v>2.4</v>
       </c>
       <c r="H22" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.78</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.303</v>
+        <v>0.958</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.294</v>
+        <v>0.829</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1470,28 +1470,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.395</v>
+        <v>0.305</v>
       </c>
       <c r="E23" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5473400</v>
+        <v>6808900</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.49</v>
+        <v>0.35</v>
       </c>
       <c r="H23" t="n">
-        <v>38.38</v>
+        <v>53.3</v>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.405</v>
+        <v>0.303</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.411</v>
+        <v>0.294</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1515,39 +1515,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>0</v>
+        <v>0.775</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0.1742</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5291900</v>
+        <v>6610500</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.68</v>
+        <v>2.88</v>
       </c>
       <c r="H24" t="n">
-        <v>66</v>
-      </c>
-      <c r="I24" s="10" t="inlineStr">
+        <v>80.45</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.342</v>
+        <v>0.554</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.321</v>
+        <v>0.443</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1560,39 +1560,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>0</v>
+        <v>0.64</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.1228</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5197100</v>
+        <v>6575600</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.37</v>
+        <v>2.04</v>
       </c>
       <c r="H25" t="n">
-        <v>53.15</v>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
+        <v>87.14</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.775</v>
+        <v>0.467</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.775</v>
+        <v>0.428</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1605,28 +1605,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0065</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>EFORCE</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>-0.0488</v>
+        <v>0.17</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4845000</v>
+        <v>6528900</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.21</v>
+        <v>0.84</v>
       </c>
       <c r="H26" t="n">
-        <v>51.26</v>
+        <v>41.86</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>0.196</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.182</v>
+        <v>0.177</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1650,39 +1650,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>0.025</v>
+        <v>0.78</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4773800</v>
+        <v>6397000</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="H27" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
+        <v>53.15</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.383</v>
+        <v>0.775</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.374</v>
+        <v>0.775</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1695,39 +1695,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>0.0234</v>
+        <v>0.295</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4717900</v>
+        <v>5859900</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.39</v>
+        <v>2.49</v>
       </c>
       <c r="H28" t="n">
-        <v>46.57</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.23</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.34</v>
+        <v>0.295</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1.305</v>
+        <v>0.296</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1740,39 +1740,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>OWG</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>0.025</v>
+        <v>0.785</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4611000</v>
+        <v>5759300</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>19.42</v>
+        <v>0.12</v>
       </c>
       <c r="H29" t="n">
-        <v>66.73</v>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.97</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.184</v>
+        <v>0.747</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.188</v>
+        <v>0.696</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1785,39 +1785,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0258</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AGMO</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>0.0169</v>
+        <v>1.83</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4523600</v>
+        <v>5748000</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>10.51</v>
+        <v>0.25</v>
       </c>
       <c r="H30" t="n">
-        <v>59.88</v>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.45</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.277</v>
+        <v>1.767</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.305</v>
+        <v>1.601</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1830,39 +1830,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>0</v>
+        <v>0.405</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0.0125</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4402400</v>
+        <v>5506400</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="H31" t="n">
-        <v>53.69</v>
-      </c>
-      <c r="I31" s="10" t="inlineStr">
+        <v>68.66</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.608</v>
+        <v>0.383</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.609</v>
+        <v>0.374</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1875,39 +1875,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>0.0211</v>
+        <v>0.39</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4251800</v>
+        <v>5487400</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.58</v>
+        <v>0.49</v>
       </c>
       <c r="H32" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.79</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.404</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.673</v>
+        <v>0.411</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1920,39 +1920,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1.83</v>
+        <v>0.365</v>
       </c>
       <c r="E33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4057100</v>
+        <v>5424900</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.17</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>60.45</v>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.767</v>
+        <v>0.342</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1.601</v>
+        <v>0.321</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1965,39 +1965,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>0</v>
+        <v>0.61</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4012300</v>
+        <v>5330400</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.08</v>
+        <v>0.52</v>
       </c>
       <c r="H34" t="n">
-        <v>61.97</v>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.03</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.747</v>
+        <v>0.608</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.696</v>
+        <v>0.609</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2010,39 +2010,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0.0442</v>
+        <v>0.0625</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3794400</v>
+        <v>5243600</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.8</v>
+        <v>1.51</v>
       </c>
       <c r="H35" t="n">
-        <v>69.18000000000001</v>
-      </c>
-      <c r="I35" s="10" t="inlineStr">
+        <v>68.5</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.531</v>
+        <v>0.455</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.484</v>
+        <v>0.444</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2055,28 +2055,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>5.61</v>
+        <v>1.29</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.0126</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>3680000</v>
+        <v>5104300</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.26</v>
+        <v>0.42</v>
       </c>
       <c r="H36" t="n">
-        <v>50.56</v>
+        <v>43.84</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>5.663</v>
+        <v>1.338</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>5.276</v>
+        <v>1.305</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2100,28 +2100,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>0.0197</v>
+        <v>0.195</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>-0.0488</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>3473800</v>
+        <v>4962400</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="H37" t="n">
-        <v>46.25</v>
+        <v>51.26</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>2.098</v>
+        <v>0.196</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2.075</v>
+        <v>0.182</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2145,33 +2145,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EVOCOM</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>-0.039</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>3293600</v>
+        <v>4860100</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>65.28</v>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0.316</v>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
     </row>
@@ -2183,39 +2190,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.155</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E39" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>3273600</v>
+        <v>4709700</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.93</v>
+        <v>0.31</v>
       </c>
       <c r="H39" t="n">
-        <v>52.53</v>
-      </c>
-      <c r="I39" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.21</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.153</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.151</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2228,39 +2235,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>OWG</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>-0.0068</v>
+        <v>0.205</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0.025</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>3222000</v>
+        <v>4668300</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.33</v>
+        <v>19.66</v>
       </c>
       <c r="H40" t="n">
-        <v>67.34</v>
-      </c>
-      <c r="I40" s="10" t="inlineStr">
+        <v>66.73</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.658</v>
+        <v>0.184</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.595</v>
+        <v>0.188</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2273,39 +2280,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2.19</v>
+        <v>0.725</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.0139</v>
+        <v>0.0211</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>3100100</v>
+        <v>4648700</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.21</v>
+        <v>0.63</v>
       </c>
       <c r="H41" t="n">
-        <v>44.59</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.38</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.258</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>2.218</v>
+        <v>0.673</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2318,39 +2325,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0258</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>AGMO</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.3</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>3054800</v>
+        <v>4597800</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.16</v>
+        <v>10.68</v>
       </c>
       <c r="H42" t="n">
-        <v>46.41</v>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
+        <v>59.88</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.868</v>
+        <v>0.277</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.87</v>
+        <v>0.305</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2363,39 +2370,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>0.0069</v>
+        <v>0.865</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>3002100</v>
+        <v>4571800</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="H43" t="n">
-        <v>61.88</v>
-      </c>
-      <c r="I43" s="10" t="inlineStr">
+        <v>46.41</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>2.751</v>
+        <v>0.868</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2.569</v>
+        <v>0.87</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2408,39 +2415,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>0.002</v>
+        <v>0.155</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2947300</v>
+        <v>4510500</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="H44" t="n">
-        <v>41.51</v>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.33</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>10.095</v>
+        <v>0.156</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>10.249</v>
+        <v>0.158</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2453,39 +2460,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>5.01</v>
+        <v>0.44</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.004</v>
+        <v>0.0115</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2935900</v>
+        <v>4503800</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="H45" t="n">
-        <v>61.61</v>
-      </c>
-      <c r="I45" s="10" t="inlineStr">
+        <v>66.17</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>4.887</v>
+        <v>0.397</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>4.611</v>
+        <v>0.337</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2507,19 +2514,19 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.375</v>
+        <v>0.37</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.0274</v>
+        <v>0.0137</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2907900</v>
+        <v>4482600</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.44</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>57.94</v>
+        <v>53.59</v>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
@@ -2530,7 +2537,7 @@
         <v>0.367</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2543,28 +2550,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>2.51</v>
+        <v>5.63</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.008</v>
+        <v>0.0162</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>2854300</v>
+        <v>4461900</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.19</v>
+        <v>0.32</v>
       </c>
       <c r="H47" t="n">
-        <v>59.67</v>
+        <v>51.32</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
@@ -2572,10 +2579,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2.458</v>
+        <v>5.664</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2.333</v>
+        <v>5.277</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2588,40 +2595,33 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>EVOCOM</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E48" s="9" t="n">
-        <v>-0.0068</v>
+        <v>0.11</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2829000</v>
+        <v>4390300</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="H48" t="n">
-        <v>76.15000000000001</v>
-      </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>2.537</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>2.079</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n"/>
+      <c r="K48" s="2" t="n"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
     </row>
@@ -2633,39 +2633,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E49" s="9" t="n">
-        <v>-0.0062</v>
+        <v>5.01</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0.004</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>2814000</v>
+        <v>4048700</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="H49" t="n">
-        <v>46.65</v>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.61</v>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.8090000000000001</v>
+        <v>4.887</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.8070000000000001</v>
+        <v>4.611</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2678,28 +2678,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>5.74</v>
+        <v>2.5</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>0.061</v>
+        <v>0.004</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>2746000</v>
+        <v>3984800</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.82</v>
+        <v>0.27</v>
       </c>
       <c r="H50" t="n">
-        <v>52.68</v>
+        <v>58.67</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>5.611</v>
+        <v>2.457</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>5.739</v>
+        <v>2.333</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2723,28 +2723,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2.59</v>
+        <v>2.07</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0197</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>2678500</v>
+        <v>3906800</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="H51" t="n">
-        <v>53.23</v>
+        <v>46.25</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.57</v>
+        <v>2.098</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2.476</v>
+        <v>2.075</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2768,39 +2768,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E52" s="8" t="n">
-        <v>0</v>
+        <v>10.04</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0.004</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2665500</v>
+        <v>3904300</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.13</v>
+        <v>0.33</v>
       </c>
       <c r="H52" t="n">
-        <v>65.20999999999999</v>
-      </c>
-      <c r="I52" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.15</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.397</v>
+        <v>10.097</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.337</v>
+        <v>10.249</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2813,39 +2813,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E53" s="9" t="n">
-        <v>-0.009300000000000001</v>
+        <v>2.89</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>-0.0034</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2615400</v>
+        <v>3877700</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="H53" t="n">
-        <v>51.34</v>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.43</v>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.068</v>
+        <v>2.748</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>1.03</v>
+        <v>2.569</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2858,39 +2858,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E54" s="9" t="n">
-        <v>-0.013</v>
+        <v>0.155</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2518900</v>
+        <v>3853100</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.29</v>
+        <v>1.1</v>
       </c>
       <c r="H54" t="n">
-        <v>71.59</v>
-      </c>
-      <c r="I54" s="10" t="inlineStr">
+        <v>52.53</v>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.346</v>
+        <v>0.153</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.317</v>
+        <v>0.151</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2903,39 +2903,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>0.068</v>
+        <v>0.54</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>2325600</v>
+        <v>3667800</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>5.32</v>
+        <v>0.23</v>
       </c>
       <c r="H55" t="n">
-        <v>71.17</v>
-      </c>
-      <c r="I55" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.98</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.506</v>
+        <v>0.51</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.5</v>
+        <v>0.428</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2948,39 +2948,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2.69</v>
+        <v>0.505</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0.0267</v>
+        <v>0.0202</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>2290800</v>
+        <v>3553000</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.64</v>
+        <v>0.52</v>
       </c>
       <c r="H56" t="n">
-        <v>67.58</v>
-      </c>
-      <c r="I56" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.63</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>2.57</v>
+        <v>0.537</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2.231</v>
+        <v>0.577</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2993,39 +2993,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>2.69</v>
+        <v>2.21</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0.0151</v>
+        <v>0.0231</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2283400</v>
+        <v>3402300</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.43</v>
+        <v>0.23</v>
       </c>
       <c r="H57" t="n">
-        <v>62.98</v>
-      </c>
-      <c r="I57" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.26</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2.584</v>
+        <v>2.259</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2.56</v>
+        <v>2.218</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3038,39 +3038,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>0.0108</v>
+        <v>0.72</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>2176800</v>
+        <v>3327900</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.43</v>
+        <v>0.34</v>
       </c>
       <c r="H58" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="I58" s="10" t="inlineStr">
+        <v>66.04000000000001</v>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.901</v>
+        <v>0.657</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.858</v>
+        <v>0.595</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3083,28 +3083,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.49</v>
+        <v>5.73</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>0.0208</v>
+        <v>0.0591</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2123800</v>
+        <v>3235600</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.05</v>
+        <v>0.96</v>
       </c>
       <c r="H59" t="n">
-        <v>27.31</v>
+        <v>52.46</v>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.574</v>
+        <v>5.61</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.78</v>
+        <v>5.739</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3128,39 +3128,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>0.0149</v>
+        <v>1.06</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>2106500</v>
+        <v>3164200</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="H60" t="n">
-        <v>58.44</v>
-      </c>
-      <c r="I60" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.69</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.323</v>
+        <v>1.067</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.338</v>
+        <v>1.03</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3173,28 +3173,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>0.0116</v>
+        <v>0.0117</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>2102500</v>
+        <v>3000000</v>
       </c>
       <c r="G61" s="5" t="n">
         <v>0.17</v>
       </c>
       <c r="H61" t="n">
-        <v>52.39</v>
+        <v>54</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>3.583</v>
+        <v>2.571</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>2.623</v>
+        <v>2.476</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3227,27 +3227,27 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>0</v>
+        <v>1.19</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>2088300</v>
+        <v>2956500</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.51</v>
+        <v>0.73</v>
       </c>
       <c r="H62" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="I62" s="10" t="inlineStr">
+        <v>63.36</v>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.142</v>
+        <v>1.141</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>1.05</v>
@@ -3263,39 +3263,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>0.0444</v>
+        <v>2.88</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>2028800</v>
+        <v>2949800</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="H63" t="n">
-        <v>75.86</v>
-      </c>
-      <c r="I63" s="10" t="inlineStr">
+        <v>74.61</v>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.613</v>
+        <v>2.535</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.518</v>
+        <v>2.078</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3308,39 +3308,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.82</v>
+        <v>3.57</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0.0123</v>
+        <v>0.0318</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1959000</v>
+        <v>2928600</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.72</v>
+        <v>0.24</v>
       </c>
       <c r="H64" t="n">
-        <v>63.12</v>
-      </c>
-      <c r="I64" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.82</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.77</v>
+        <v>3.59</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.746</v>
+        <v>2.625</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3353,39 +3353,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CENSOF</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E65" s="8" t="n">
-        <v>0</v>
+        <v>2.69</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0.0267</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1928400</v>
+        <v>2841300</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>1.87</v>
+        <v>0.79</v>
       </c>
       <c r="H65" t="n">
-        <v>69.45999999999999</v>
-      </c>
-      <c r="I65" s="10" t="inlineStr">
+        <v>67.58</v>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.213</v>
+        <v>2.57</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.203</v>
+        <v>2.231</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3398,39 +3398,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E66" s="9" t="n">
-        <v>-0.0052</v>
+        <v>2.67</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0.0075</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1830700</v>
+        <v>2580500</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="H66" t="n">
-        <v>28.04</v>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.32</v>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.013</v>
+        <v>2.582</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1.076</v>
+        <v>2.56</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3443,39 +3443,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E67" s="9" t="n">
-        <v>-0.0169</v>
+        <v>0.49</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1823600</v>
+        <v>2547300</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H67" t="n">
-        <v>55.52</v>
-      </c>
-      <c r="I67" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.31</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.273</v>
+        <v>0.574</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.306</v>
+        <v>0.78</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3488,39 +3488,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>2.27</v>
+        <v>0.545</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.0365</v>
+        <v>0.0583</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1778800</v>
+        <v>2506900</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.91</v>
+        <v>5.73</v>
       </c>
       <c r="H68" t="n">
-        <v>68.97</v>
-      </c>
-      <c r="I68" s="10" t="inlineStr">
+        <v>69.91</v>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2.038</v>
+        <v>0.506</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1.929</v>
+        <v>0.5</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3533,39 +3533,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SKYWLD</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.405</v>
+        <v>0.7</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>0.0519</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1769600</v>
+        <v>2500100</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>2.99</v>
+        <v>1.19</v>
       </c>
       <c r="H69" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.34</v>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.391</v>
+        <v>0.613</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.397</v>
+        <v>0.518</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3578,39 +3578,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E70" s="9" t="n">
-        <v>-0.0089</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1751600</v>
+        <v>2453300</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.11</v>
+        <v>0.9</v>
       </c>
       <c r="H70" t="n">
-        <v>63.68</v>
-      </c>
-      <c r="I70" s="10" t="inlineStr">
+        <v>61.41</v>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.511</v>
+        <v>0.769</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.428</v>
+        <v>0.745</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3623,39 +3623,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>0.0231</v>
+        <v>0.925</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1745300</v>
+        <v>2363400</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="H71" t="n">
-        <v>51.22</v>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.72</v>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.755</v>
+        <v>0.9</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1.784</v>
+        <v>0.858</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3683,15 +3683,15 @@
         <v>0.0261</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1732900</v>
+        <v>2322400</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="H72" t="n">
         <v>68.98</v>
       </c>
-      <c r="I72" s="10" t="inlineStr">
+      <c r="I72" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -3713,28 +3713,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>3.02</v>
+        <v>1.76</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>0.0033</v>
+        <v>0.0173</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1670300</v>
+        <v>2272100</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.57</v>
+        <v>0.45</v>
       </c>
       <c r="H73" t="n">
-        <v>53.17</v>
+        <v>49.91</v>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>2.982</v>
+        <v>1.754</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>3.036</v>
+        <v>1.784</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3758,28 +3758,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>0.0202</v>
+        <v>0.965</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1654800</v>
+        <v>2184500</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.24</v>
+        <v>0.55</v>
       </c>
       <c r="H74" t="n">
-        <v>31.63</v>
+        <v>28.95</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.537</v>
+        <v>1.013</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.577</v>
+        <v>1.076</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3803,39 +3803,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="E75" s="9" t="n">
-        <v>-0.0064</v>
+        <v>0.34</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0.0149</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1637800</v>
+        <v>2146600</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.1</v>
+        <v>0.41</v>
       </c>
       <c r="H75" t="n">
-        <v>34.48</v>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.44</v>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>4.775</v>
+        <v>0.323</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>4.916</v>
+        <v>0.338</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3848,39 +3848,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FPGROUP</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>0.0119</v>
+        <v>4.69</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1628100</v>
+        <v>2031000</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1.64</v>
+        <v>0.12</v>
       </c>
       <c r="H76" t="n">
-        <v>58.08</v>
-      </c>
-      <c r="I76" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.32</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.408</v>
+        <v>4.776</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.417</v>
+        <v>4.916</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3893,39 +3893,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>0.0225</v>
+        <v>1.16</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1618700</v>
+        <v>2026300</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.57</v>
+        <v>0.17</v>
       </c>
       <c r="H77" t="n">
-        <v>71.67</v>
-      </c>
-      <c r="I77" s="10" t="inlineStr">
+        <v>77.17</v>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.4</v>
+        <v>1.055</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.359</v>
+        <v>0.895</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3938,39 +3938,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.845</v>
+        <v>2.27</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>0.0181</v>
+        <v>0.0365</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1612600</v>
+        <v>1994600</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.52</v>
+        <v>1.02</v>
       </c>
       <c r="H78" t="n">
-        <v>61.19</v>
-      </c>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.97</v>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.8139999999999999</v>
+        <v>2.038</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.746</v>
+        <v>1.929</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3983,39 +3983,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E79" s="8" t="n">
-        <v>0</v>
+        <v>0.615</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0.008199999999999999</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1550600</v>
+        <v>1956400</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.52</v>
+        <v>0.65</v>
       </c>
       <c r="H79" t="n">
-        <v>77.02</v>
-      </c>
-      <c r="I79" s="10" t="inlineStr">
+        <v>58.38</v>
+      </c>
+      <c r="I79" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.184</v>
+        <v>0.612</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.97</v>
+        <v>0.596</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4028,39 +4028,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>1.26</v>
+        <v>0.24</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.0413</v>
+        <v>0.0213</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1544700</v>
+        <v>1946500</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>1</v>
+        <v>1.89</v>
       </c>
       <c r="H80" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.56</v>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.265</v>
+        <v>0.213</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>1.322</v>
+        <v>0.203</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4073,39 +4073,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="E81" s="9" t="n">
-        <v>-0.0108</v>
+        <v>0.445</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>-0.022</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1455800</v>
+        <v>1915700</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="H81" t="n">
-        <v>32.95</v>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.49</v>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.917</v>
+        <v>0.415</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2.042</v>
+        <v>0.408</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4118,39 +4118,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5277</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>FPGROUP</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E82" s="9" t="n">
-        <v>-0.0061</v>
+        <v>0.43</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0.0238</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1416700</v>
+        <v>1909000</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.21</v>
+        <v>1.93</v>
       </c>
       <c r="H82" t="n">
-        <v>37.28</v>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.94</v>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.689</v>
+        <v>0.409</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1.805</v>
+        <v>0.417</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4163,39 +4163,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>0.0444</v>
+        <v>0.285</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>-0.0339</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1381000</v>
+        <v>1905100</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="H83" t="n">
-        <v>34.19</v>
-      </c>
-      <c r="I83" s="10" t="inlineStr">
+        <v>53.39</v>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.258</v>
+        <v>0.272</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.311</v>
+        <v>0.306</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4208,28 +4208,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E84" s="9" t="n">
-        <v>-0.0172</v>
+        <v>0.84</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0.012</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1377400</v>
+        <v>1895900</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.2</v>
+        <v>0.61</v>
       </c>
       <c r="H84" t="n">
-        <v>37.25</v>
+        <v>60.28</v>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
@@ -4237,10 +4237,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.294</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.309</v>
+        <v>0.746</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4253,39 +4253,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>0.0172</v>
+        <v>0.51</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1375100</v>
+        <v>1886400</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.09</v>
+        <v>0.31</v>
       </c>
       <c r="H85" t="n">
-        <v>52.96</v>
-      </c>
-      <c r="I85" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46</v>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.29</v>
+        <v>0.519</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.278</v>
+        <v>0.531</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4298,39 +4298,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0396</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ADNEX</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.445</v>
+        <v>3.04</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>0.023</v>
+        <v>0.01</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1338000</v>
+        <v>1794800</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>2.92</v>
+        <v>0.61</v>
       </c>
       <c r="H86" t="n">
-        <v>62.16</v>
-      </c>
-      <c r="I86" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.89</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.424</v>
+        <v>2.984</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.418</v>
+        <v>3.037</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4343,39 +4343,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>3.16</v>
+        <v>1.26</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>0.0032</v>
+        <v>0.0413</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1327900</v>
+        <v>1786500</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.34</v>
+        <v>1.16</v>
       </c>
       <c r="H87" t="n">
-        <v>62.18</v>
-      </c>
-      <c r="I87" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.6</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>2.974</v>
+        <v>1.265</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>2.785</v>
+        <v>1.322</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4388,39 +4388,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>SKYWLD</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>5.24</v>
+        <v>0.405</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0.0116</v>
+        <v>0.0519</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1320100</v>
+        <v>1784900</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.28</v>
+        <v>3.02</v>
       </c>
       <c r="H88" t="n">
-        <v>63.31</v>
-      </c>
-      <c r="I88" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.2</v>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>5.029</v>
+        <v>0.391</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>5.054</v>
+        <v>0.397</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4433,39 +4433,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E89" s="9" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.215</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0.0238</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1317700</v>
+        <v>1756900</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.11</v>
+        <v>0.38</v>
       </c>
       <c r="H89" t="n">
-        <v>77.17</v>
-      </c>
-      <c r="I89" s="10" t="inlineStr">
+        <v>51.41</v>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.055</v>
+        <v>0.214</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.895</v>
+        <v>0.213</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4478,39 +4478,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E90" s="9" t="n">
-        <v>-0.0182</v>
+        <v>0.455</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>0.0225</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1315000</v>
+        <v>1735300</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.35</v>
+        <v>0.61</v>
       </c>
       <c r="H90" t="n">
-        <v>66.38</v>
-      </c>
-      <c r="I90" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.67</v>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.243</v>
+        <v>0.4</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.215</v>
+        <v>0.359</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4523,39 +4523,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E91" s="9" t="n">
-        <v>-0.022</v>
+        <v>1.38</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1310100</v>
+        <v>1710400</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.21</v>
+        <v>0.57</v>
       </c>
       <c r="H91" t="n">
-        <v>59.49</v>
-      </c>
-      <c r="I91" s="10" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.415</v>
+        <v>1.187</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.408</v>
+        <v>0.971</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4577,19 +4577,19 @@
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E92" s="9" t="n">
-        <v>-0.0261</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>-0.0174</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1263200</v>
+        <v>1690000</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="H92" t="n">
-        <v>33.3</v>
+        <v>34.26</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
@@ -4613,28 +4613,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>0.0073</v>
+        <v>1.84</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1225600</v>
+        <v>1687700</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.09</v>
+        <v>0.38</v>
       </c>
       <c r="H93" t="n">
-        <v>48.73</v>
+        <v>32.95</v>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>2.785</v>
+        <v>1.917</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>2.681</v>
+        <v>2.042</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4658,33 +4658,40 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E94" s="8" t="n">
-        <v>0</v>
+        <v>0.635</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>-0.0379</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1203700</v>
+        <v>1616300</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.03</v>
+        <v>0.5</v>
+      </c>
+      <c r="H94" t="n">
+        <v>52.18</v>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J94" s="2" t="n"/>
-      <c r="K94" s="2" t="n"/>
+      <c r="J94" s="2" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>0.606</v>
+      </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
     </row>
@@ -4696,39 +4703,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.485</v>
+        <v>0.295</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>0.0211</v>
+        <v>0.0172</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1195600</v>
+        <v>1597200</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.37</v>
+        <v>0.1</v>
       </c>
       <c r="H95" t="n">
-        <v>64.33</v>
-      </c>
-      <c r="I95" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.96</v>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.461</v>
+        <v>0.29</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.417</v>
+        <v>0.278</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4741,28 +4748,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E96" s="8" t="n">
-        <v>0</v>
+        <v>0.27</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1178300</v>
+        <v>1581100</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>1.24</v>
+        <v>0.42</v>
       </c>
       <c r="H96" t="n">
-        <v>45.51</v>
+        <v>66.38</v>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
@@ -4770,10 +4777,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.261</v>
+        <v>0.243</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.265</v>
+        <v>0.215</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4786,39 +4793,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.255</v>
+        <v>5.21</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>0.02</v>
+        <v>0.0058</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1133100</v>
+        <v>1567700</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.44</v>
+        <v>0.34</v>
       </c>
       <c r="H97" t="n">
-        <v>49.14</v>
-      </c>
-      <c r="I97" s="10" t="inlineStr">
+        <v>62.02</v>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.254</v>
+        <v>5.027</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.264</v>
+        <v>5.053</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4831,38 +4838,40 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E98" s="8" t="n">
-        <v>0</v>
+        <v>3.16</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>0.0032</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1082500</v>
+        <v>1557600</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="H98" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="I98" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.18</v>
+      </c>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="K98" s="2" t="n"/>
+        <v>2.974</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>2.785</v>
+      </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
     </row>
@@ -4874,39 +4883,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E99" s="9" t="n">
-        <v>-0.0182</v>
+        <v>2.76</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>0.011</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1064500</v>
+        <v>1552100</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.51</v>
+        <v>0.11</v>
       </c>
       <c r="H99" t="n">
-        <v>64.44</v>
-      </c>
-      <c r="I99" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.71</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.251</v>
+        <v>2.786</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0.256</v>
+        <v>2.681</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4919,39 +4928,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>3.28</v>
+        <v>0.23</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0.0031</v>
+        <v>0.0222</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1035300</v>
+        <v>1522500</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.34</v>
+        <v>0.05</v>
       </c>
       <c r="H100" t="n">
-        <v>70.94</v>
-      </c>
-      <c r="I100" s="10" t="inlineStr">
+        <v>31.25</v>
+      </c>
+      <c r="I100" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>2.905</v>
+        <v>0.258</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>2.76</v>
+        <v>0.311</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4964,39 +4973,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E101" s="9" t="n">
-        <v>-0.0169</v>
+        <v>0.26</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0.04</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1008500</v>
+        <v>1520700</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.11</v>
+        <v>0.59</v>
       </c>
       <c r="H101" t="n">
-        <v>51.81</v>
-      </c>
-      <c r="I101" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.09</v>
+      </c>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.157</v>
+        <v>0.254</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1.113</v>
+        <v>0.264</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5009,39 +5018,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>0396</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>ADNEX</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E102" s="8" t="n">
-        <v>0</v>
+        <v>0.45</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1007700</v>
+        <v>1511000</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.52</v>
+        <v>3.3</v>
       </c>
       <c r="H102" t="n">
-        <v>61.65</v>
-      </c>
-      <c r="I102" s="10" t="inlineStr">
+        <v>63.94</v>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.456</v>
+        <v>0.425</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0.46</v>
+        <v>0.418</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5054,28 +5063,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>IFCAMSC</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.205</v>
+        <v>1.64</v>
       </c>
       <c r="E103" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1004500</v>
+        <v>1504700</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>1.9</v>
+        <v>0.23</v>
       </c>
       <c r="H103" t="n">
-        <v>48.37</v>
+        <v>38.36</v>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
@@ -5083,10 +5092,10 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.205</v>
+        <v>1.689</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.215</v>
+        <v>1.805</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5108,19 +5117,19 @@
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>7.25</v>
+        <v>7.22</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>0.0097</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>989600</v>
+        <v>1436300</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="H104" t="n">
-        <v>34.79</v>
+        <v>32.99</v>
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
@@ -5128,7 +5137,7 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>7.497</v>
+        <v>7.494</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>7.768</v>
@@ -5144,28 +5153,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="E105" s="3" t="n">
-        <v>0.0266</v>
+        <v>0.285</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>982700</v>
+        <v>1420800</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="H105" t="n">
-        <v>42.98</v>
+        <v>37.25</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
@@ -5173,10 +5182,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>4.407</v>
+        <v>0.294</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>4.477</v>
+        <v>0.309</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5189,39 +5198,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E106" s="8" t="n">
-        <v>0</v>
+        <v>0.48</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>0.0105</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>947700</v>
+        <v>1402500</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.3</v>
+        <v>0.43</v>
       </c>
       <c r="H106" t="n">
-        <v>59.45</v>
-      </c>
-      <c r="I106" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.86</v>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.581</v>
+        <v>0.46</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0.578</v>
+        <v>0.417</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5234,39 +5243,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0466</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SRKKAI</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E107" s="9" t="n">
-        <v>-0.0182</v>
+        <v>4.28</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0.0363</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>947700</v>
+        <v>1371700</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.91</v>
+        <v>0.17</v>
       </c>
       <c r="H107" t="n">
-        <v>54.08</v>
-      </c>
-      <c r="I107" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.47</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.526</v>
+        <v>4.411</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0.533</v>
+        <v>4.478</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5279,28 +5288,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="E108" s="9" t="n">
-        <v>-0.0013</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0.0089</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>914700</v>
+        <v>1303200</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.1</v>
+        <v>0.61</v>
       </c>
       <c r="H108" t="n">
-        <v>26.21</v>
+        <v>51.22</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
@@ -5308,10 +5317,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>7.748</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>8.164999999999999</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5324,28 +5333,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E109" s="3" t="n">
-        <v>0.0265</v>
+        <v>1.16</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>891300</v>
+        <v>1292700</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.22</v>
+        <v>0.14</v>
       </c>
       <c r="H109" t="n">
-        <v>43.76</v>
+        <v>51.81</v>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
@@ -5353,10 +5362,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.791</v>
+        <v>1.157</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.805</v>
+        <v>1.113</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5369,28 +5378,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>7.74</v>
+        <v>0.75</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0.0013</v>
+        <v>0.0345</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>889000</v>
+        <v>1282400</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="H110" t="n">
-        <v>48.67</v>
+        <v>40.41</v>
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
@@ -5398,10 +5407,10 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>7.77</v>
+        <v>0.769</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>7.755</v>
+        <v>0.827</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5414,28 +5423,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>1.02</v>
+        <v>7.46</v>
       </c>
       <c r="E111" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>862100</v>
+        <v>1250500</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="H111" t="n">
-        <v>64.81</v>
+        <v>26.51</v>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
@@ -5443,10 +5452,10 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.957</v>
+        <v>7.749</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0.803</v>
+        <v>8.164999999999999</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5459,40 +5468,38 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="E112" s="3" t="n">
-        <v>0.0072</v>
+        <v>0.275</v>
+      </c>
+      <c r="E112" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>852900</v>
+        <v>1221600</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H112" t="n">
-        <v>69.08</v>
-      </c>
-      <c r="I112" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>18.18</v>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>3.866</v>
-      </c>
-      <c r="K112" s="2" t="n">
-        <v>3.37</v>
-      </c>
+        <v>0.295</v>
+      </c>
+      <c r="K112" s="2" t="n"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
     </row>
@@ -5504,40 +5511,33 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E113" s="8" t="n">
-        <v>0</v>
+        <v>0.22</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>836500</v>
+        <v>1220300</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H113" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="I113" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J113" s="2" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="K113" s="2" t="n">
-        <v>0.76</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="n"/>
+      <c r="K113" s="2" t="n"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
     </row>
@@ -5549,39 +5549,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E114" s="9" t="n">
-        <v>-0.0076</v>
+        <v>4.25</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0.0143</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>785200</v>
+        <v>1209800</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
       <c r="H114" t="n">
-        <v>65.25</v>
-      </c>
-      <c r="I114" s="10" t="inlineStr">
+        <v>69.76000000000001</v>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.64</v>
+        <v>3.869</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.607</v>
+        <v>3.37</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5594,28 +5594,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>0.0083</v>
+        <v>0.26</v>
+      </c>
+      <c r="E115" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>781700</v>
+        <v>1178300</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.31</v>
+        <v>1.24</v>
       </c>
       <c r="H115" t="n">
-        <v>32.4</v>
+        <v>45.51</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.323</v>
+        <v>0.261</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>1.316</v>
+        <v>0.265</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5639,39 +5639,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="E116" s="3" t="n">
-        <v>0.0063</v>
+        <v>0.485</v>
+      </c>
+      <c r="E116" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>780700</v>
+        <v>1157100</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.2</v>
+        <v>0.59</v>
       </c>
       <c r="H116" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="I116" s="10" t="inlineStr">
+        <v>61.65</v>
+      </c>
+      <c r="I116" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>6.977</v>
+        <v>0.456</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>6.657</v>
+        <v>0.46</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5684,39 +5684,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="E117" s="3" t="n">
-        <v>0.0181</v>
+        <v>1.45</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>-0.0136</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>712200</v>
+        <v>1155300</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="H117" t="n">
-        <v>70.67</v>
-      </c>
-      <c r="I117" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.61</v>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>3.106</v>
+        <v>1.466</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>2.679</v>
+        <v>1.469</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5729,28 +5729,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E118" s="8" t="n">
-        <v>0</v>
+        <v>1.2</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>691400</v>
+        <v>1135900</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.11</v>
+        <v>0.45</v>
       </c>
       <c r="H118" t="n">
-        <v>46</v>
+        <v>29.45</v>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.519</v>
+        <v>1.321</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0.531</v>
+        <v>1.316</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5774,39 +5774,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E119" s="8" t="n">
-        <v>0</v>
+        <v>0.775</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>0.0265</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>688000</v>
+        <v>1131700</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.52</v>
+        <v>0.28</v>
       </c>
       <c r="H119" t="n">
-        <v>64.66</v>
-      </c>
-      <c r="I119" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.76</v>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.641</v>
+        <v>0.791</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0.61</v>
+        <v>0.805</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5819,39 +5819,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E120" s="9" t="n">
-        <v>-0.0072</v>
+        <v>3.28</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0.0031</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>681700</v>
+        <v>1130200</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.17</v>
+        <v>0.37</v>
       </c>
       <c r="H120" t="n">
-        <v>61.73</v>
-      </c>
-      <c r="I120" s="10" t="inlineStr">
+        <v>70.94</v>
+      </c>
+      <c r="I120" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.272</v>
+        <v>2.905</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>1.176</v>
+        <v>2.76</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5864,39 +5864,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E121" s="9" t="n">
-        <v>-0.0051</v>
+        <v>0.605</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>634800</v>
+        <v>1100400</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="H121" t="n">
-        <v>61.19</v>
-      </c>
-      <c r="I121" s="10" t="inlineStr">
+        <v>57.85</v>
+      </c>
+      <c r="I121" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.922</v>
+        <v>0.581</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0.838</v>
+        <v>0.578</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5909,39 +5909,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>5.5</v>
+        <v>7.75</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>0.011</v>
+        <v>0.0026</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>626300</v>
+        <v>1091500</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.24</v>
+        <v>0.09</v>
       </c>
       <c r="H122" t="n">
-        <v>58.31</v>
-      </c>
-      <c r="I122" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.21</v>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>5.271</v>
+        <v>7.771</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>5.297</v>
+        <v>7.755</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5954,39 +5954,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="E123" s="9" t="n">
-        <v>-0.0188</v>
+        <v>0.27</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>625500</v>
+        <v>1077200</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.17</v>
+        <v>0.52</v>
       </c>
       <c r="H123" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="I123" s="10" t="inlineStr">
+        <v>64.44</v>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>2.573</v>
+        <v>0.251</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>1.953</v>
+        <v>0.256</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -5999,40 +5999,36 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>0.005</v>
+        <v>0.26</v>
+      </c>
+      <c r="E124" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>593900</v>
+        <v>1072400</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
       <c r="H124" t="n">
-        <v>62.23</v>
-      </c>
-      <c r="I124" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J124" s="2" t="n">
-        <v>3.837</v>
-      </c>
-      <c r="K124" s="2" t="n">
-        <v>3.519</v>
-      </c>
+        <v>25.13</v>
+      </c>
+      <c r="I124" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="n"/>
+      <c r="K124" s="2" t="n"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
     </row>
@@ -6044,39 +6040,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0466</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>SRKKAI</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>0.027</v>
+        <v>0.54</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>580200</v>
+        <v>1028700</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.09</v>
+        <v>0.99</v>
       </c>
       <c r="H125" t="n">
-        <v>47.85</v>
-      </c>
-      <c r="I125" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.08</v>
+      </c>
+      <c r="I125" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1.151</v>
+        <v>0.526</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>1.161</v>
+        <v>0.533</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6089,39 +6085,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E126" s="8" t="n">
-        <v>0</v>
+        <v>4.67</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>572100</v>
+        <v>1009400</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H126" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="I126" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.6</v>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>13.086</v>
+        <v>4.709</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>13.646</v>
+        <v>4.618</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6134,39 +6130,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>IFCAMSC</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>1.16</v>
+        <v>0.205</v>
       </c>
       <c r="E127" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>571300</v>
+        <v>1007500</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.37</v>
+        <v>1.9</v>
       </c>
       <c r="H127" t="n">
-        <v>60.29</v>
-      </c>
-      <c r="I127" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.37</v>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>1.111</v>
+        <v>0.205</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>1.077</v>
+        <v>0.215</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6179,39 +6175,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>1.89</v>
+        <v>1.02</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>0.0216</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>566000</v>
+        <v>966300</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.08</v>
+        <v>1.59</v>
       </c>
       <c r="H128" t="n">
-        <v>41.18</v>
-      </c>
-      <c r="I128" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.9</v>
+      </c>
+      <c r="I128" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>1.94</v>
+        <v>0.992</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>1.962</v>
+        <v>0.978</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6224,39 +6220,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>2.04</v>
+        <v>5.49</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>0.0049</v>
+        <v>0.0092</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>531300</v>
+        <v>961100</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.18</v>
+        <v>0.38</v>
       </c>
       <c r="H129" t="n">
-        <v>45.23</v>
-      </c>
-      <c r="I129" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.04</v>
+      </c>
+      <c r="I129" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>2.052</v>
+        <v>5.27</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>2.09</v>
+        <v>5.297</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6269,39 +6265,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>4.63</v>
+        <v>7.92</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0051</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>524800</v>
+        <v>935900</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.05</v>
+        <v>0.24</v>
       </c>
       <c r="H130" t="n">
-        <v>43.75</v>
-      </c>
-      <c r="I130" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.09</v>
+      </c>
+      <c r="I130" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>4.705</v>
+        <v>6.976</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>4.617</v>
+        <v>6.657</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6314,39 +6310,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>0.63</v>
+        <v>1.02</v>
       </c>
       <c r="E131" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>510000</v>
+        <v>899700</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.38</v>
+        <v>0.11</v>
       </c>
       <c r="H131" t="n">
-        <v>44.84</v>
-      </c>
-      <c r="I131" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.81</v>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.634</v>
+        <v>0.957</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0.63</v>
+        <v>0.803</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6359,45 +6355,1395 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>2.62</v>
+        <v>1.14</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>0.0195</v>
+        <v>0.027</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>504000</v>
+        <v>876800</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="H132" t="n">
-        <v>74.48</v>
-      </c>
-      <c r="I132" s="10" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.85</v>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>2.335</v>
+        <v>1.151</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>2.1</v>
+        <v>1.161</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
     </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>870400</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H133" t="n">
+        <v>58.69</v>
+      </c>
+      <c r="I133" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="7" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E134" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="4" t="n">
+        <v>860000</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H134" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="I134" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="7" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>RANHILL</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="F135" s="4" t="n">
+        <v>849800</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H135" t="n">
+        <v>70.36</v>
+      </c>
+      <c r="I135" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="n">
+        <v>3.105</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>2.678</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="7" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="F136" s="4" t="n">
+        <v>839200</v>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H136" t="n">
+        <v>43.44</v>
+      </c>
+      <c r="I136" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>13.647</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="7" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="F137" s="4" t="n">
+        <v>811100</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H137" t="n">
+        <v>38</v>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="7" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="F138" s="4" t="n">
+        <v>785500</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H138" t="n">
+        <v>61.73</v>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v>1.272</v>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>1.176</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="7" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E139" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="4" t="n">
+        <v>781500</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H139" t="n">
+        <v>35.34</v>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="K139" s="2" t="n">
+        <v>1.403</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="7" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>5053</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>OSK</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="F140" s="4" t="n">
+        <v>775800</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H140" t="n">
+        <v>24.47</v>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="n">
+        <v>1.837</v>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="7" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="F141" s="4" t="n">
+        <v>720600</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H141" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="I141" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="n">
+        <v>3.836</v>
+      </c>
+      <c r="K141" s="2" t="n">
+        <v>3.519</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="7" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="F142" s="4" t="n">
+        <v>716300</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H142" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="I142" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="n">
+        <v>1.254</v>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="7" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>0291</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>CHB</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="F143" s="4" t="n">
+        <v>710400</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H143" t="n">
+        <v>74.81999999999999</v>
+      </c>
+      <c r="I143" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="n">
+        <v>2.336</v>
+      </c>
+      <c r="K143" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="7" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E144" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="4" t="n">
+        <v>699000</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H144" t="n">
+        <v>64.66</v>
+      </c>
+      <c r="I144" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="K144" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="7" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="F145" s="4" t="n">
+        <v>693800</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H145" t="n">
+        <v>45.23</v>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="n">
+        <v>2.052</v>
+      </c>
+      <c r="K145" s="2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="7" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>7231</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>WELLCAL</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="F146" s="4" t="n">
+        <v>685300</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H146" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="I146" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v>1.118</v>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="7" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>0273</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>VLB</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>-0.0103</v>
+      </c>
+      <c r="F147" s="4" t="n">
+        <v>675100</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H147" t="n">
+        <v>60.24</v>
+      </c>
+      <c r="I147" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="7" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>-0.0219</v>
+      </c>
+      <c r="F148" s="4" t="n">
+        <v>657800</v>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H148" t="n">
+        <v>73.92</v>
+      </c>
+      <c r="I148" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>2.572</v>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>1.953</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="7" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>0325</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E149" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" s="4" t="n">
+        <v>645600</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H149" t="n">
+        <v>60.29</v>
+      </c>
+      <c r="I149" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="K149" s="2" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="7" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="F150" s="4" t="n">
+        <v>629700</v>
+      </c>
+      <c r="G150" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H150" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="K150" s="2" t="n">
+        <v>1.962</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="7" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>5248</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>BAUTO</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E151" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>624900</v>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H151" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="K151" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="7" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E152" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="4" t="n">
+        <v>610000</v>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H152" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="I152" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K152" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="7" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F153" s="4" t="n">
+        <v>604100</v>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H153" t="n">
+        <v>57.53</v>
+      </c>
+      <c r="I153" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="K153" s="2" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="7" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>-0.0089</v>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>584900</v>
+      </c>
+      <c r="G154" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H154" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="I154" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="7" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="E155" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="4" t="n">
+        <v>579400</v>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H155" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>3.212</v>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>3.415</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="7" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>-0.0161</v>
+      </c>
+      <c r="F156" s="4" t="n">
+        <v>555000</v>
+      </c>
+      <c r="G156" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H156" t="n">
+        <v>73.12</v>
+      </c>
+      <c r="I156" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="7" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F157" s="4" t="n">
+        <v>553600</v>
+      </c>
+      <c r="G157" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H157" t="n">
+        <v>68.56</v>
+      </c>
+      <c r="I157" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="K157" s="2" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="7" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>-0.0139</v>
+      </c>
+      <c r="F158" s="4" t="n">
+        <v>543800</v>
+      </c>
+      <c r="G158" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H158" t="n">
+        <v>39.37</v>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>2.259</v>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>2.324</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="7" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>KGB</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="F159" s="4" t="n">
+        <v>534800</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H159" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="I159" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>8.747999999999999</v>
+      </c>
+      <c r="K159" s="2" t="n">
+        <v>8.651999999999999</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="7" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E160" s="10" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="F160" s="4" t="n">
+        <v>532800</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H160" t="n">
+        <v>70.13</v>
+      </c>
+      <c r="I160" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="K160" s="2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="7" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="F161" s="4" t="n">
+        <v>521600</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H161" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>3.518</v>
+      </c>
+      <c r="K161" s="2" t="n">
+        <v>3.676</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="7" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>0.009300000000000001</v>
+      </c>
+      <c r="F162" s="4" t="n">
+        <v>501800</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H162" t="n">
+        <v>77.81</v>
+      </c>
+      <c r="I162" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>9.922000000000001</v>
+      </c>
+      <c r="K162" s="2" t="n">
+        <v>9.355</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M132"/>
+  <autoFilter ref="A1:M162"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-06/bursa-report-2026-10-06.xlsx
+++ b/docs/downloads/2026-10-06/bursa-report-2026-10-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-06" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-06'!$A$1:$M$194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-06'!$A$1:$M$202</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M194"/>
+  <dimension ref="A1:M202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.05019999999999999</v>
+        <v>-0.0408</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>2112400</v>
+        <v>2679200</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>69.91</v>
+        <v>71.2</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>2.563</v>
+        <v>2.566</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1.951</v>
+        <v>1.952</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，但RSI达69.91接近超买，现价3.03远高于50日均线1.951，短期涨幅偏大，信号可靠性需谨慎看待。</t>
+          <t>SAR转多信号，但RSI达71.2已超买，现价RM3.06远高于50日均线RM1.952，偏离较大，信号可靠性存疑。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.095</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0.3077</v>
+        <v>0.4615</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>601818200</v>
+        <v>647286500</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="H3" t="n">
-        <v>20.46</v>
+        <v>23.04</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="J3" s="9" t="n">
-        <v>0.205</v>
+        <v>0.206</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>0.425</v>
@@ -664,13 +664,13 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.245</v>
+        <v>0.25</v>
       </c>
       <c r="E4" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>65144100</v>
+        <v>65201900</v>
       </c>
       <c r="G4" s="12" t="n"/>
       <c r="I4" s="13" t="inlineStr">
@@ -700,19 +700,19 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.31</v>
+        <v>0.315</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>-0.0313</v>
+        <v>-0.0156</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>38668600</v>
+        <v>39163800</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="H5" t="n">
-        <v>71.33</v>
+        <v>73.81</v>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.257</v>
+        <v>0.258</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>0.238</v>
@@ -751,10 +751,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>22847400</v>
+        <v>23180400</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="H6" t="n">
         <v>83.98999999999999</v>
@@ -790,19 +790,19 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.825</v>
+        <v>0.82</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>-0.012</v>
+        <v>-0.018</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>17975100</v>
+        <v>18101200</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H7" t="n">
-        <v>66.89</v>
+        <v>64.78</v>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>-0.06059999999999999</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>17249500</v>
+        <v>17388400</v>
       </c>
       <c r="G8" s="12" t="n">
         <v>0.43</v>
@@ -880,19 +880,19 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.605</v>
+        <v>0.6</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.0164</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>16845600</v>
+        <v>17073900</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H9" t="n">
-        <v>71.92</v>
+        <v>68.92</v>
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
@@ -916,28 +916,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0183</t>
+          <t>0051</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SALUTE</t>
+          <t>CUSCAPI</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.11</v>
+        <v>0.045</v>
       </c>
       <c r="E10" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>16521200</v>
+        <v>16554200</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>2.25</v>
+        <v>0.84</v>
       </c>
       <c r="H10" t="n">
-        <v>46.13</v>
+        <v>30.46</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.115</v>
+        <v>0.054</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.109</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -961,39 +961,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0183</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>SALUTE</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>-0.009899999999999999</v>
+        <v>0.11</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>15849800</v>
+        <v>16521200</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.6</v>
+        <v>2.25</v>
       </c>
       <c r="H11" t="n">
-        <v>58.53</v>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.13</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.481</v>
+        <v>0.115</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.475</v>
+        <v>0.109</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1006,28 +1006,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0.0245</v>
+        <v>0.5</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>14591700</v>
+        <v>15885800</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.18</v>
+        <v>0.6</v>
       </c>
       <c r="H12" t="n">
-        <v>66.29000000000001</v>
+        <v>58.53</v>
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.755</v>
+        <v>0.481</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.704</v>
+        <v>0.475</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1051,39 +1051,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0143</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KEYASIC</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>-0.07690000000000001</v>
+        <v>0.83</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0.0184</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>13345400</v>
+        <v>14772700</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>47.86</v>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.73999999999999</v>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.063</v>
+        <v>0.755</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.058</v>
+        <v>0.704</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1096,39 +1096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>0143</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>KEYASIC</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>0.2105</v>
+        <v>0.06</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>12914700</v>
+        <v>14680400</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>8.59</v>
+        <v>1.7</v>
       </c>
       <c r="H14" t="n">
-        <v>66.62</v>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.86</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.093</v>
+        <v>0.063</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.083</v>
+        <v>0.058</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1141,39 +1141,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0051</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CUSCAPI</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>0</v>
+        <v>0.11</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0.1579</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>12754400</v>
+        <v>13009800</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.65</v>
+        <v>8.65</v>
       </c>
       <c r="H15" t="n">
-        <v>30.46</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.31</v>
+      </c>
+      <c r="I15" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.054</v>
+        <v>0.093</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.083</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1201,10 +1201,10 @@
         <v>-0.0234</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>12675000</v>
+        <v>12872000</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="H16" t="n">
         <v>63.88</v>
@@ -1231,39 +1231,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>0</v>
+        <v>0.8</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0.0191</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>11588700</v>
+        <v>12164600</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="H17" t="n">
-        <v>70.89</v>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.45</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.347</v>
+        <v>0.748</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.221</v>
+        <v>0.696</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>10868100</v>
+        <v>11868100</v>
       </c>
       <c r="G18" s="12" t="n"/>
       <c r="I18" s="13" t="inlineStr">
@@ -1312,28 +1312,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>0.0294</v>
+        <v>0.305</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>10820000</v>
+        <v>11728600</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.17</v>
+        <v>0.6</v>
       </c>
       <c r="H19" t="n">
-        <v>60.35</v>
+        <v>53.3</v>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.162</v>
+        <v>0.303</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.127</v>
+        <v>0.294</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1357,39 +1357,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.305</v>
+        <v>0.38</v>
       </c>
       <c r="E20" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>10678600</v>
+        <v>11624400</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.55</v>
+        <v>0.27</v>
       </c>
       <c r="H20" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.89</v>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.303</v>
+        <v>0.347</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.294</v>
+        <v>0.221</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1402,39 +1402,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>0</v>
+        <v>0.175</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0.0294</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>9914300</v>
+        <v>11235100</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.71</v>
+        <v>0.17</v>
       </c>
       <c r="H21" t="n">
-        <v>53.15</v>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.35</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.775</v>
+        <v>0.162</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.775</v>
+        <v>0.127</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1447,39 +1447,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.115</v>
+        <v>0.155</v>
       </c>
       <c r="E22" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>9890700</v>
+        <v>10950500</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1.44</v>
+        <v>0.37</v>
       </c>
       <c r="H22" t="n">
-        <v>45.95</v>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.33</v>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.118</v>
+        <v>0.156</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.123</v>
+        <v>0.158</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1492,28 +1492,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0.0833</v>
+        <v>0.615</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>9504100</v>
+        <v>10576500</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>2.73</v>
+        <v>1.02</v>
       </c>
       <c r="H23" t="n">
-        <v>70.23</v>
+        <v>53.69</v>
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.456</v>
+        <v>0.608</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.444</v>
+        <v>0.609</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1537,28 +1537,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.615</v>
+        <v>0.78</v>
       </c>
       <c r="E24" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>9319600</v>
+        <v>9914500</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.9</v>
+        <v>0.71</v>
       </c>
       <c r="H24" t="n">
-        <v>53.69</v>
+        <v>53.15</v>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.608</v>
+        <v>0.775</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.609</v>
+        <v>0.775</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1582,39 +1582,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>0.0619</v>
+        <v>0.115</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>9177000</v>
+        <v>9890700</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="H25" t="n">
-        <v>70.69</v>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.95</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.532</v>
+        <v>0.118</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.484</v>
+        <v>0.123</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1636,19 +1636,19 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0.0294</v>
+        <v>0.165</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>-0.0294</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>9082000</v>
+        <v>9647200</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="H26" t="n">
-        <v>43.75</v>
+        <v>40.5</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.196</v>
+        <v>0.195</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>0.177</v>
@@ -1672,39 +1672,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>0</v>
+        <v>0.52</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0.0833</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>8997800</v>
+        <v>9597200</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.59</v>
+        <v>2.76</v>
       </c>
       <c r="H27" t="n">
-        <v>50.21</v>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.23</v>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.456</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.444</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1717,28 +1717,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0.0064</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>8781000</v>
+        <v>9494800</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.18</v>
+        <v>0.62</v>
       </c>
       <c r="H28" t="n">
-        <v>62.83</v>
+        <v>50.21</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -1746,10 +1746,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.747</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.696</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1762,39 +1762,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>-0.005500000000000001</v>
+        <v>0.445</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0.023</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>8681100</v>
+        <v>9488200</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="H29" t="n">
-        <v>59.29</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.08</v>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>1.766</v>
+        <v>0.398</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>1.601</v>
+        <v>0.338</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1807,28 +1807,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.6</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0.0619</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>8102400</v>
+        <v>9423800</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.43</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>46.41</v>
+        <v>70.69</v>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.868</v>
+        <v>0.532</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.87</v>
+        <v>0.484</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1852,39 +1852,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DATAPRP</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.06</v>
+        <v>0.865</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>-0.07690000000000001</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>7840400</v>
+        <v>9389400</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.99</v>
+        <v>0.5</v>
       </c>
       <c r="H31" t="n">
-        <v>35.73</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.41</v>
+      </c>
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.868</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1897,39 +1897,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0.023</v>
+        <v>1.82</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>-0.005500000000000001</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>7806300</v>
+        <v>8803400</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="H32" t="n">
-        <v>67.08</v>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.29</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.398</v>
+        <v>1.766</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.338</v>
+        <v>1.601</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1942,28 +1942,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>-0.0167</v>
+        <v>0.72</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0.0141</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7796500</v>
+        <v>7946500</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>2.67</v>
+        <v>1.08</v>
       </c>
       <c r="H33" t="n">
-        <v>75.17</v>
+        <v>57.56</v>
       </c>
       <c r="I33" s="17" t="inlineStr">
         <is>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.959</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.83</v>
+        <v>0.673</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         <v>0.025</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>7786900</v>
+        <v>7929000</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H34" t="n">
         <v>70.7</v>
@@ -2032,39 +2032,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0.0141</v>
+        <v>0.06</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>7768200</v>
+        <v>7840400</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>1.05</v>
+        <v>0.99</v>
       </c>
       <c r="H35" t="n">
-        <v>57.56</v>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.73</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.673</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2077,39 +2077,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.785</v>
+        <v>1.29</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>0.0608</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>7577600</v>
+        <v>7839000</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>6.13</v>
+        <v>0.65</v>
       </c>
       <c r="H36" t="n">
-        <v>69.20999999999999</v>
-      </c>
-      <c r="I36" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.84</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.338</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>1.305</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2122,39 +2122,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0.0156</v>
+        <v>1.18</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>7275400</v>
+        <v>7800700</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.6</v>
+        <v>2.67</v>
       </c>
       <c r="H37" t="n">
-        <v>45.24</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.17</v>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>1.339</v>
+        <v>0.959</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>1.305</v>
+        <v>0.83</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2167,28 +2167,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>0.197</v>
+        <v>0.0541</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>7048300</v>
+        <v>7583900</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>3.07</v>
+        <v>6.13</v>
       </c>
       <c r="H38" t="n">
-        <v>81.09999999999999</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.556</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.443</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2212,28 +2212,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ITRONIC</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0.0137</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>6792000</v>
+        <v>7182000</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>8.01</v>
+        <v>1.1</v>
       </c>
       <c r="H39" t="n">
-        <v>46.66</v>
+        <v>53.59</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
@@ -2241,10 +2241,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.031</v>
+        <v>0.367</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.031</v>
+        <v>0.367</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2257,28 +2257,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>0.1228</v>
+        <v>0.197</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>6745100</v>
+        <v>7056900</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>2.09</v>
+        <v>3.08</v>
       </c>
       <c r="H40" t="n">
-        <v>87.14</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I40" s="17" t="inlineStr">
         <is>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.467</v>
+        <v>0.556</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.428</v>
+        <v>0.443</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         <v>-0.0357</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>6559100</v>
+        <v>6893900</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="H41" t="n">
         <v>59.98</v>
@@ -2347,28 +2347,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>5.02</v>
+        <v>0.635</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>0.006</v>
+        <v>0.114</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>6366800</v>
+        <v>6864700</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.25</v>
+        <v>2.13</v>
       </c>
       <c r="H42" t="n">
-        <v>62.05</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>4.888</v>
+        <v>0.466</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>4.612</v>
+        <v>0.428</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2392,39 +2392,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>9393</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>ITRONIC</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.295</v>
+        <v>0.03</v>
       </c>
       <c r="E43" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>6352200</v>
+        <v>6792000</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>2.7</v>
+        <v>8.01</v>
       </c>
       <c r="H43" t="n">
-        <v>49.23</v>
-      </c>
-      <c r="I43" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.66</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.295</v>
+        <v>0.031</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.296</v>
+        <v>0.031</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2437,39 +2437,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>5.6</v>
+        <v>5.02</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>0.0108</v>
+        <v>0.006</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>5879800</v>
+        <v>6702400</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.42</v>
+        <v>0.26</v>
       </c>
       <c r="H44" t="n">
-        <v>50.17</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.05</v>
+      </c>
+      <c r="I44" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>5.662</v>
+        <v>4.888</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>5.276</v>
+        <v>4.612</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2482,39 +2482,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.365</v>
+        <v>0.295</v>
       </c>
       <c r="E45" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>5845000</v>
+        <v>6352200</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.89</v>
+        <v>2.7</v>
       </c>
       <c r="H45" t="n">
-        <v>48.24</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.23</v>
+      </c>
+      <c r="I45" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.366</v>
+        <v>0.295</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.367</v>
+        <v>0.296</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2527,39 +2527,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>0</v>
+        <v>5.59</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>5657600</v>
+        <v>6051100</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.72</v>
+        <v>0.43</v>
       </c>
       <c r="H46" t="n">
-        <v>66</v>
-      </c>
-      <c r="I46" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.78</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.342</v>
+        <v>5.661</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.321</v>
+        <v>5.276</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2572,39 +2572,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E47" s="16" t="n">
-        <v>-0.0127</v>
+        <v>0.365</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>5642400</v>
+        <v>5702500</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="H47" t="n">
-        <v>34.79</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66</v>
+      </c>
+      <c r="I47" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.404</v>
+        <v>0.342</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.411</v>
+        <v>0.321</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2617,39 +2617,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="E48" s="16" t="n">
-        <v>-0.039</v>
+        <v>-0.0127</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>5629400</v>
+        <v>5662600</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.65</v>
+        <v>0.51</v>
       </c>
       <c r="H48" t="n">
-        <v>65.28</v>
-      </c>
-      <c r="I48" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.79</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.345</v>
+        <v>0.404</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.316</v>
+        <v>0.411</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2662,33 +2662,40 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EVOCOM</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>-0.039</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>5555000</v>
+        <v>5651400</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J49" s="9" t="n"/>
-      <c r="K49" s="9" t="n"/>
+        <v>0.66</v>
+      </c>
+      <c r="H49" t="n">
+        <v>65.28</v>
+      </c>
+      <c r="I49" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>0.316</v>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
     </row>
@@ -2700,40 +2707,33 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>EVOCOM</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E50" s="15" t="n">
-        <v>0</v>
+        <v>0.115</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>5510500</v>
+        <v>5576700</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="H50" t="n">
-        <v>46.33</v>
-      </c>
-      <c r="I50" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J50" s="9" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="K50" s="9" t="n">
-        <v>0.158</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="n"/>
+      <c r="K50" s="9" t="n"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
     </row>
@@ -2760,10 +2760,10 @@
         <v>-0.0488</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>5263600</v>
+        <v>5338500</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="H51" t="n">
         <v>51.26</v>
@@ -2805,10 +2805,10 @@
         <v>0.002</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>5172300</v>
+        <v>5305800</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="H52" t="n">
         <v>41.51</v>
@@ -2835,28 +2835,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5.78</v>
+        <v>0.5</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>0.0684</v>
+        <v>0.0101</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>5081400</v>
+        <v>5261600</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>1.51</v>
+        <v>0.77</v>
       </c>
       <c r="H53" t="n">
-        <v>53.56</v>
+        <v>28.67</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>5.615</v>
+        <v>0.536</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>5.74</v>
+        <v>0.577</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2880,28 +2880,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>2.08</v>
+        <v>5.8</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>0.0246</v>
+        <v>0.0721</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>5072400</v>
+        <v>5220000</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.27</v>
+        <v>1.55</v>
       </c>
       <c r="H54" t="n">
-        <v>47.66</v>
+        <v>53.99</v>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>2.099</v>
+        <v>5.617</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>2.075</v>
+        <v>5.74</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2925,39 +2925,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0.0101</v>
+        <v>2.89</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>-0.0034</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>5040600</v>
+        <v>5137300</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.74</v>
+        <v>0.54</v>
       </c>
       <c r="H55" t="n">
-        <v>28.67</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.43</v>
+      </c>
+      <c r="I55" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.536</v>
+        <v>2.748</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.577</v>
+        <v>2.569</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2970,39 +2970,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>-0.0034</v>
+        <v>2.08</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0.0246</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>4945100</v>
+        <v>5111900</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.52</v>
+        <v>0.27</v>
       </c>
       <c r="H56" t="n">
-        <v>60.43</v>
-      </c>
-      <c r="I56" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.66</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>2.748</v>
+        <v>2.099</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>2.569</v>
+        <v>2.075</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3015,28 +3015,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0258</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AGMO</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0.0339</v>
+        <v>0.715</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>-0.0205</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>4696500</v>
+        <v>5009000</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>10.91</v>
+        <v>0.51</v>
       </c>
       <c r="H57" t="n">
-        <v>61.78</v>
+        <v>64.78</v>
       </c>
       <c r="I57" s="17" t="inlineStr">
         <is>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.278</v>
+        <v>0.657</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.305</v>
+        <v>0.595</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3060,28 +3060,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>0258</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OWG</t>
+          <t>AGMO</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.205</v>
+        <v>0.305</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>0.025</v>
+        <v>0.0339</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>4686900</v>
+        <v>4696500</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>19.74</v>
+        <v>10.91</v>
       </c>
       <c r="H58" t="n">
-        <v>66.73</v>
+        <v>61.78</v>
       </c>
       <c r="I58" s="17" t="inlineStr">
         <is>
@@ -3089,10 +3089,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.184</v>
+        <v>0.278</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.188</v>
+        <v>0.305</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3105,28 +3105,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>OWG</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>-0.0274</v>
+        <v>0.205</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>0.025</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>4631900</v>
+        <v>4692500</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.47</v>
+        <v>19.76</v>
       </c>
       <c r="H59" t="n">
-        <v>63.57</v>
+        <v>66.73</v>
       </c>
       <c r="I59" s="17" t="inlineStr">
         <is>
@@ -3134,10 +3134,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.656</v>
+        <v>0.184</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.595</v>
+        <v>0.188</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3159,19 +3159,19 @@
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>4497500</v>
+        <v>4571800</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="H60" t="n">
-        <v>58.67</v>
+        <v>59.67</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>2.457</v>
+        <v>2.458</v>
       </c>
       <c r="K60" s="9" t="n">
         <v>2.333</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>4366900</v>
+        <v>4549900</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H61" t="n">
         <v>38.36</v>
@@ -3249,19 +3249,19 @@
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>0.0115</v>
+        <v>0.0191</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>4307100</v>
+        <v>4330100</v>
       </c>
       <c r="G62" s="12" t="n">
         <v>1.2</v>
       </c>
       <c r="H62" t="n">
-        <v>65.20999999999999</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>2.566</v>
+        <v>2.568</v>
       </c>
       <c r="K62" s="9" t="n">
         <v>2.23</v>
@@ -3300,10 +3300,10 @@
         <v>0</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>4060400</v>
+        <v>4263200</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="H63" t="n">
         <v>52.53</v>
@@ -3330,39 +3330,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E64" s="16" t="n">
-        <v>-0.0385</v>
+        <v>1.08</v>
+      </c>
+      <c r="E64" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>4006700</v>
+        <v>4259300</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.91</v>
+        <v>0.37</v>
       </c>
       <c r="H64" t="n">
-        <v>55.34</v>
-      </c>
-      <c r="I64" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.09</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.121</v>
+        <v>1.069</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.125</v>
+        <v>1.03</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3375,28 +3375,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>2.18</v>
+        <v>2.58</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.0039</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3992200</v>
+        <v>4148300</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="H65" t="n">
-        <v>43.72</v>
+        <v>52.43</v>
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>2.257</v>
+        <v>2.569</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>2.217</v>
+        <v>2.476</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3420,28 +3420,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>2.58</v>
+        <v>2.18</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>0.0039</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3758300</v>
+        <v>4110700</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="H66" t="n">
-        <v>52.43</v>
+        <v>43.72</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3449,10 +3449,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>2.569</v>
+        <v>2.257</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>2.476</v>
+        <v>2.217</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3465,39 +3465,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>1.06</v>
+        <v>0.125</v>
       </c>
       <c r="E67" s="16" t="n">
-        <v>-0.0185</v>
+        <v>-0.0385</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3717300</v>
+        <v>4007800</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.32</v>
+        <v>0.91</v>
       </c>
       <c r="H67" t="n">
-        <v>49.69</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.34</v>
+      </c>
+      <c r="I67" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>1.067</v>
+        <v>0.121</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>1.03</v>
+        <v>0.125</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3510,28 +3510,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0290</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PANDA</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.185</v>
+        <v>2.68</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>0.0571</v>
+        <v>0.0113</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3622100</v>
+        <v>3704400</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>28.84</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H68" t="n">
-        <v>55.91</v>
+        <v>62.16</v>
       </c>
       <c r="I68" s="17" t="inlineStr">
         <is>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.179</v>
+        <v>2.583</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.186</v>
+        <v>2.56</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3555,28 +3555,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>0.0173</v>
+        <v>4.67</v>
+      </c>
+      <c r="E69" s="16" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3466200</v>
+        <v>3685600</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="H69" t="n">
-        <v>52.81</v>
+        <v>33.68</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>3.585</v>
+        <v>4.774</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>2.624</v>
+        <v>4.915</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3600,28 +3600,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0290</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>PANDA</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E70" s="15" t="n">
-        <v>0</v>
+        <v>0.185</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0.0571</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>3388200</v>
+        <v>3681500</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.64</v>
+        <v>29.31</v>
       </c>
       <c r="H70" t="n">
-        <v>56.19</v>
+        <v>55.91</v>
       </c>
       <c r="I70" s="17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.323</v>
+        <v>0.179</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.338</v>
+        <v>0.186</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3645,39 +3645,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E71" s="16" t="n">
-        <v>-0.0256</v>
+        <v>3.53</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>0.0202</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>3326900</v>
+        <v>3648200</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="H71" t="n">
-        <v>71.88</v>
-      </c>
-      <c r="I71" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.01</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>1.054</v>
+        <v>3.586</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.894</v>
+        <v>2.624</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3690,39 +3690,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>0.0104</v>
+        <v>1.15</v>
+      </c>
+      <c r="E72" s="16" t="n">
+        <v>-0.0171</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>3305000</v>
+        <v>3542700</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.09</v>
+        <v>0.3</v>
       </c>
       <c r="H72" t="n">
-        <v>26.07</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.43000000000001</v>
+      </c>
+      <c r="I72" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.573</v>
+        <v>1.055</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.78</v>
+        <v>0.895</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="E73" s="16" t="n">
-        <v>-0.0171</v>
+        <v>0.485</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>0.0104</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>3261000</v>
+        <v>3420500</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>1.01</v>
+        <v>0.09</v>
       </c>
       <c r="H73" t="n">
-        <v>73.87</v>
-      </c>
-      <c r="I73" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.07</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>2.534</v>
+        <v>0.573</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>2.078</v>
+        <v>0.78</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3780,28 +3780,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1.19</v>
+        <v>2.87</v>
       </c>
       <c r="E74" s="16" t="n">
-        <v>-0.0083</v>
+        <v>-0.0171</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>3232500</v>
+        <v>3389500</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.79</v>
+        <v>1.05</v>
       </c>
       <c r="H74" t="n">
-        <v>63.36</v>
+        <v>73.87</v>
       </c>
       <c r="I74" s="17" t="inlineStr">
         <is>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>1.141</v>
+        <v>2.534</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1.05</v>
+        <v>2.078</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3825,28 +3825,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>0.0151</v>
+        <v>0.335</v>
+      </c>
+      <c r="E75" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>3011200</v>
+        <v>3388200</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H75" t="n">
-        <v>62.98</v>
+        <v>56.19</v>
       </c>
       <c r="I75" s="17" t="inlineStr">
         <is>
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.584</v>
+        <v>0.323</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>2.56</v>
+        <v>0.338</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3879,19 +3879,19 @@
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.65</v>
+        <v>0.645</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>0.0156</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2987400</v>
+        <v>3369100</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="H76" t="n">
-        <v>59.69</v>
+        <v>58.69</v>
       </c>
       <c r="I76" s="17" t="inlineStr">
         <is>
@@ -3915,39 +3915,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="E77" s="16" t="n">
-        <v>-0.0064</v>
+        <v>1.2</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2945700</v>
+        <v>3301300</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.18</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H77" t="n">
-        <v>34.48</v>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.7</v>
+      </c>
+      <c r="I77" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>4.775</v>
+        <v>1.142</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>4.916</v>
+        <v>1.05</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3960,33 +3960,40 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E78" s="15" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0.0089</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2908400</v>
+        <v>3185500</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.08</v>
+        <v>1.48</v>
+      </c>
+      <c r="H78" t="n">
+        <v>51.22</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J78" s="9" t="n"/>
-      <c r="K78" s="9" t="n"/>
+      <c r="J78" s="9" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="K78" s="9" t="n">
+        <v>0.5620000000000001</v>
+      </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
     </row>
@@ -3998,39 +4005,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>EWICAP</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>0.0222</v>
+        <v>0.13</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>-0.07139999999999999</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2883300</v>
+        <v>3130900</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.1</v>
+        <v>1.39</v>
       </c>
       <c r="H79" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="I79" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>19.9</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.258</v>
+        <v>0.168</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.311</v>
+        <v>0.181</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4052,19 +4059,19 @@
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.695</v>
+        <v>0.7</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>0.0296</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2795700</v>
+        <v>3046200</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="H80" t="n">
-        <v>74.79000000000001</v>
+        <v>75.34</v>
       </c>
       <c r="I80" s="17" t="inlineStr">
         <is>
@@ -4072,7 +4079,7 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.612</v>
+        <v>0.613</v>
       </c>
       <c r="K80" s="9" t="n">
         <v>0.518</v>
@@ -4088,39 +4095,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E81" s="10" t="n">
-        <v>0.0089</v>
+        <v>0.445</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>-0.022</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2781000</v>
+        <v>3033600</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>1.29</v>
+        <v>0.48</v>
       </c>
       <c r="H81" t="n">
-        <v>51.22</v>
-      </c>
-      <c r="I81" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.49</v>
+      </c>
+      <c r="I81" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.415</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.408</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4148,10 +4155,10 @@
         <v>0.0196</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2747500</v>
+        <v>3014200</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="H82" t="n">
         <v>68.36</v>
@@ -4178,28 +4185,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.445</v>
+        <v>0.29</v>
       </c>
       <c r="E83" s="16" t="n">
-        <v>-0.022</v>
+        <v>-0.0169</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2726700</v>
+        <v>2983700</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.44</v>
+        <v>0.29</v>
       </c>
       <c r="H83" t="n">
-        <v>59.49</v>
+        <v>55.52</v>
       </c>
       <c r="I83" s="17" t="inlineStr">
         <is>
@@ -4207,10 +4214,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.415</v>
+        <v>0.273</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.408</v>
+        <v>0.306</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4223,28 +4230,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E84" s="15" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2719200</v>
+        <v>2948400</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.54</v>
+        <v>0.1</v>
       </c>
       <c r="H84" t="n">
-        <v>62.72</v>
+        <v>31.25</v>
       </c>
       <c r="I84" s="17" t="inlineStr">
         <is>
@@ -4252,10 +4259,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.9</v>
+        <v>0.258</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.858</v>
+        <v>0.311</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4268,40 +4275,33 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.225</v>
+      </c>
+      <c r="E85" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2661900</v>
+        <v>2908400</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="H85" t="n">
-        <v>62.28</v>
-      </c>
-      <c r="I85" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J85" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="K85" s="9" t="n">
-        <v>0.746</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="n"/>
+      <c r="K85" s="9" t="n"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
     </row>
@@ -4313,28 +4313,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.545</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>0.0583</v>
+        <v>0.0062</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2605900</v>
+        <v>2877300</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>5.96</v>
+        <v>1.05</v>
       </c>
       <c r="H86" t="n">
-        <v>69.91</v>
+        <v>62.28</v>
       </c>
       <c r="I86" s="17" t="inlineStr">
         <is>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.506</v>
+        <v>0.77</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.5</v>
+        <v>0.746</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4358,39 +4358,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>3.04</v>
+        <v>5.21</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>0.01</v>
+        <v>0.0058</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2583400</v>
+        <v>2820800</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.88</v>
+        <v>0.61</v>
       </c>
       <c r="H87" t="n">
-        <v>54.89</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.02</v>
+      </c>
+      <c r="I87" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>2.984</v>
+        <v>5.027</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>3.037</v>
+        <v>5.053</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4403,39 +4403,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>2.28</v>
+        <v>7.19</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>0.0411</v>
+        <v>0.0014</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2569100</v>
+        <v>2814600</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>1.32</v>
+        <v>0.39</v>
       </c>
       <c r="H88" t="n">
-        <v>69.37</v>
-      </c>
-      <c r="I88" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.09</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>2.039</v>
+        <v>7.491</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>1.93</v>
+        <v>7.767</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4448,39 +4448,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E89" s="15" t="n">
-        <v>0</v>
+        <v>1.74</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2509600</v>
+        <v>2791000</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>1.21</v>
+        <v>0.55</v>
       </c>
       <c r="H89" t="n">
-        <v>69.31</v>
-      </c>
-      <c r="I89" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.08</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.252</v>
+        <v>1.752</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.256</v>
+        <v>1.783</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4493,39 +4493,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>7.18</v>
+        <v>0.21</v>
       </c>
       <c r="E90" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2433000</v>
+        <v>2780200</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="H90" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.06</v>
+      </c>
+      <c r="I90" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>7.49</v>
+        <v>0.213</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>7.767</v>
+        <v>0.213</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4538,39 +4538,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E91" s="16" t="n">
-        <v>-0.0052</v>
+        <v>2.3</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>0.05019999999999999</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2397900</v>
+        <v>2725000</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.61</v>
+        <v>1.4</v>
       </c>
       <c r="H91" t="n">
-        <v>28.04</v>
-      </c>
-      <c r="I91" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.15000000000001</v>
+      </c>
+      <c r="I91" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>1.013</v>
+        <v>2.041</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>1.076</v>
+        <v>1.93</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4583,39 +4583,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SKYWLD</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>0.039</v>
+        <v>0.925</v>
+      </c>
+      <c r="E92" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>2353900</v>
+        <v>2719200</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>3.98</v>
+        <v>0.54</v>
       </c>
       <c r="H92" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="I92" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.72</v>
+      </c>
+      <c r="I92" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.39</v>
+        <v>0.9</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.397</v>
+        <v>0.858</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4628,28 +4628,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>1.75</v>
+        <v>3.05</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>0.0116</v>
+        <v>0.0133</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>2346600</v>
+        <v>2705900</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.47</v>
+        <v>0.93</v>
       </c>
       <c r="H93" t="n">
-        <v>48.53</v>
+        <v>55.7</v>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
@@ -4657,10 +4657,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>1.753</v>
+        <v>2.985</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>1.783</v>
+        <v>3.037</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4673,28 +4673,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FPGROUP</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.44</v>
+        <v>0.545</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>0.0476</v>
+        <v>0.0583</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>2300900</v>
+        <v>2619500</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>2.32</v>
+        <v>5.99</v>
       </c>
       <c r="H94" t="n">
-        <v>63.2</v>
+        <v>69.91</v>
       </c>
       <c r="I94" s="17" t="inlineStr">
         <is>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.41</v>
+        <v>0.506</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.417</v>
+        <v>0.5</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4718,39 +4718,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5277</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>FPGROUP</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>2.77</v>
+        <v>0.43</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>0.0147</v>
+        <v>0.0238</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>2271300</v>
+        <v>2599100</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.17</v>
+        <v>2.62</v>
       </c>
       <c r="H95" t="n">
-        <v>50.65</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.94</v>
+      </c>
+      <c r="I95" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>2.787</v>
+        <v>0.409</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>2.681</v>
+        <v>0.417</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4763,40 +4763,38 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E96" s="16" t="n">
-        <v>-0.0339</v>
+        <v>0.28</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>0.0182</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>2269700</v>
+        <v>2557600</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="H96" t="n">
-        <v>53.39</v>
-      </c>
-      <c r="I96" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>20.18</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="K96" s="9" t="n">
-        <v>0.306</v>
-      </c>
+        <v>0.296</v>
+      </c>
+      <c r="K96" s="9" t="n"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
     </row>
@@ -4808,28 +4806,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1.84</v>
+        <v>0.96</v>
       </c>
       <c r="E97" s="16" t="n">
-        <v>-0.0108</v>
+        <v>-0.0052</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>2232500</v>
+        <v>2523100</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.51</v>
+        <v>0.64</v>
       </c>
       <c r="H97" t="n">
-        <v>32.95</v>
+        <v>28.04</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -4837,10 +4835,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>1.917</v>
+        <v>1.013</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>2.042</v>
+        <v>1.076</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4853,39 +4851,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E98" s="16" t="n">
-        <v>-0.0068</v>
+        <v>0.275</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>2204100</v>
+        <v>2509600</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.44</v>
+        <v>1.21</v>
       </c>
       <c r="H98" t="n">
-        <v>47.58</v>
-      </c>
-      <c r="I98" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.31</v>
+      </c>
+      <c r="I98" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>1.467</v>
+        <v>0.252</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1.469</v>
+        <v>0.256</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4898,39 +4896,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.555</v>
+        <v>0.23</v>
       </c>
       <c r="E99" s="16" t="n">
-        <v>-0.0348</v>
+        <v>-0.0213</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>2177900</v>
+        <v>2423000</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.39</v>
+        <v>2.35</v>
       </c>
       <c r="H99" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.68000000000001</v>
+      </c>
+      <c r="I99" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.605</v>
+        <v>0.212</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.649</v>
+        <v>0.203</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4943,39 +4941,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>0.0172</v>
+        <v>1.47</v>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>2137300</v>
+        <v>2397600</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.14</v>
+        <v>0.47</v>
       </c>
       <c r="H100" t="n">
-        <v>52.96</v>
-      </c>
-      <c r="I100" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.96</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.29</v>
+        <v>1.468</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.278</v>
+        <v>1.47</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4988,28 +4986,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>SKYWLD</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E101" s="15" t="n">
-        <v>0</v>
+        <v>0.4</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>0.039</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>2129400</v>
+        <v>2372100</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>4.01</v>
       </c>
       <c r="H101" t="n">
-        <v>69.5</v>
+        <v>57.1</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -5017,10 +5015,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.243</v>
+        <v>0.39</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.215</v>
+        <v>0.397</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5033,28 +5031,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>1.25</v>
+        <v>2.78</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>0.0331</v>
+        <v>0.0183</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>2121300</v>
+        <v>2328500</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>1.37</v>
+        <v>0.17</v>
       </c>
       <c r="H102" t="n">
-        <v>46.27</v>
+        <v>51.56</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -5062,10 +5060,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>1.265</v>
+        <v>2.788</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>1.321</v>
+        <v>2.681</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5078,28 +5076,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E103" s="16" t="n">
-        <v>-0.0098</v>
+        <v>1.27</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>0.0496</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>2069600</v>
+        <v>2292800</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.34</v>
+        <v>1.48</v>
       </c>
       <c r="H103" t="n">
-        <v>44.35</v>
+        <v>48.87</v>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
@@ -5107,10 +5105,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.518</v>
+        <v>1.266</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.531</v>
+        <v>1.322</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5123,39 +5121,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E104" s="10" t="n">
-        <v>0.0337</v>
+        <v>1.84</v>
+      </c>
+      <c r="E104" s="16" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>2048600</v>
+        <v>2282800</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.72</v>
+        <v>0.52</v>
       </c>
       <c r="H104" t="n">
-        <v>72.51000000000001</v>
-      </c>
-      <c r="I104" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.95</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.4</v>
+        <v>1.917</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.359</v>
+        <v>2.042</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5168,39 +5166,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CENSOF</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E105" s="15" t="n">
-        <v>0</v>
+        <v>0.27</v>
+      </c>
+      <c r="E105" s="16" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>2035500</v>
+        <v>2249400</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>1.98</v>
+        <v>0.6</v>
       </c>
       <c r="H105" t="n">
-        <v>69.45999999999999</v>
-      </c>
-      <c r="I105" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>66.38</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.213</v>
+        <v>0.243</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.203</v>
+        <v>0.215</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5213,28 +5211,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>0.0181</v>
+        <v>0.555</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>-0.0348</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>2034700</v>
+        <v>2213100</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.66</v>
+        <v>0.4</v>
       </c>
       <c r="H106" t="n">
-        <v>61.19</v>
+        <v>32.39</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -5242,10 +5240,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.605</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.746</v>
+        <v>0.649</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5258,28 +5256,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>5.21</v>
+        <v>0.295</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>0.0058</v>
+        <v>0.0172</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>2004100</v>
+        <v>2147200</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.43</v>
+        <v>0.14</v>
       </c>
       <c r="H107" t="n">
-        <v>62.02</v>
+        <v>52.96</v>
       </c>
       <c r="I107" s="17" t="inlineStr">
         <is>
@@ -5287,10 +5285,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>5.027</v>
+        <v>0.29</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>5.053</v>
+        <v>0.278</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5303,28 +5301,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="E108" s="16" t="n">
-        <v>-0.0032</v>
+        <v>0.46</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>0.0337</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>2003600</v>
+        <v>2134300</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.51</v>
+        <v>0.75</v>
       </c>
       <c r="H108" t="n">
-        <v>61.15</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="I108" s="17" t="inlineStr">
         <is>
@@ -5332,10 +5330,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>2.972</v>
+        <v>0.4</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>2.784</v>
+        <v>0.359</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5348,28 +5346,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E109" s="15" t="n">
-        <v>0</v>
+        <v>0.505</v>
+      </c>
+      <c r="E109" s="16" t="n">
+        <v>-0.0098</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1985200</v>
+        <v>2118800</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.13</v>
+        <v>0.34</v>
       </c>
       <c r="H109" t="n">
-        <v>18.18</v>
+        <v>44.35</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -5377,9 +5375,11 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="K109" s="9" t="n"/>
+        <v>0.518</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>0.531</v>
+      </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
     </row>
@@ -5391,39 +5391,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.615</v>
+        <v>0.84</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1966400</v>
+        <v>2102700</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="H110" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="I110" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.28</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.612</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.596</v>
+        <v>0.746</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5436,39 +5436,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.74</v>
+        <v>4.23</v>
       </c>
       <c r="E111" s="10" t="n">
-        <v>0.0207</v>
+        <v>0.0095</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1908600</v>
+        <v>2056400</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
       <c r="H111" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="I111" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.31</v>
+      </c>
+      <c r="I111" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.768</v>
+        <v>3.867</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.827</v>
+        <v>3.37</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5481,39 +5481,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>4.24</v>
+        <v>0.74</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>0.0119</v>
+        <v>0.0207</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1907100</v>
+        <v>2026000</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.23</v>
+        <v>0.37</v>
       </c>
       <c r="H112" t="n">
-        <v>69.54000000000001</v>
-      </c>
-      <c r="I112" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.9</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>3.868</v>
+        <v>0.768</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>3.37</v>
+        <v>0.827</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>0.0387</v>
+        <v>3.14</v>
+      </c>
+      <c r="E113" s="16" t="n">
+        <v>-0.0032</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1865000</v>
+        <v>2023300</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.24</v>
+        <v>0.52</v>
       </c>
       <c r="H113" t="n">
-        <v>44.83</v>
-      </c>
-      <c r="I113" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.15</v>
+      </c>
+      <c r="I113" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>4.412</v>
+        <v>2.972</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>4.478</v>
+        <v>2.784</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5571,39 +5571,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E114" s="10" t="n">
-        <v>0.0074</v>
+        <v>7.72</v>
+      </c>
+      <c r="E114" s="16" t="n">
+        <v>-0.0013</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1824400</v>
+        <v>2017600</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.61</v>
+        <v>0.17</v>
       </c>
       <c r="H114" t="n">
-        <v>77.53</v>
-      </c>
-      <c r="I114" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.62</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>1.185</v>
+        <v>7.768</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.97</v>
+        <v>7.755</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5616,28 +5616,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>7.45</v>
+        <v>1.17</v>
       </c>
       <c r="E115" s="16" t="n">
-        <v>-0.0013</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1815400</v>
+        <v>1985300</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="H115" t="n">
-        <v>26.21</v>
+        <v>53.44</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>7.748</v>
+        <v>1.158</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>8.164999999999999</v>
+        <v>1.113</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5670,19 +5670,19 @@
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.64</v>
+        <v>0.635</v>
       </c>
       <c r="E116" s="16" t="n">
-        <v>-0.0303</v>
+        <v>-0.0379</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1787700</v>
+        <v>1966800</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="H116" t="n">
-        <v>54.93</v>
+        <v>52.18</v>
       </c>
       <c r="I116" s="13" t="inlineStr">
         <is>
@@ -5706,28 +5706,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E117" s="15" t="n">
-        <v>0</v>
+        <v>0.615</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>0.008199999999999999</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1769900</v>
+        <v>1966400</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.38</v>
+        <v>0.65</v>
       </c>
       <c r="H117" t="n">
-        <v>47.06</v>
+        <v>58.38</v>
       </c>
       <c r="I117" s="17" t="inlineStr">
         <is>
@@ -5735,10 +5735,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.213</v>
+        <v>0.612</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.213</v>
+        <v>0.596</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5751,28 +5751,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E118" s="15" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E118" s="16" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1753900</v>
+        <v>1953800</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.54</v>
+        <v>0.65</v>
       </c>
       <c r="H118" t="n">
-        <v>61.26</v>
+        <v>53.73</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.46</v>
+        <v>0.863</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.417</v>
+        <v>0.857</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5796,28 +5796,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E119" s="16" t="n">
-        <v>-0.0169</v>
+        <v>4.29</v>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>0.0387</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1752300</v>
+        <v>1950800</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="H119" t="n">
-        <v>51.81</v>
+        <v>44.83</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>1.157</v>
+        <v>4.412</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1.113</v>
+        <v>4.478</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5841,28 +5841,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>7.74</v>
+        <v>0.79</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>0.0013</v>
+        <v>0.0464</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1746300</v>
+        <v>1904200</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.15</v>
+        <v>0.47</v>
       </c>
       <c r="H120" t="n">
-        <v>48.67</v>
+        <v>48.32</v>
       </c>
       <c r="I120" s="13" t="inlineStr">
         <is>
@@ -5870,10 +5870,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>7.77</v>
+        <v>0.792</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>7.755</v>
+        <v>0.806</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5886,28 +5886,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.255</v>
+        <v>1.37</v>
       </c>
       <c r="E121" s="10" t="n">
-        <v>0.02</v>
+        <v>0.0148</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1733600</v>
+        <v>1849600</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H121" t="n">
-        <v>49.14</v>
+        <v>78.03</v>
       </c>
       <c r="I121" s="17" t="inlineStr">
         <is>
@@ -5915,10 +5915,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.254</v>
+        <v>1.186</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.264</v>
+        <v>0.971</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5931,28 +5931,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>1.25</v>
+        <v>7.45</v>
       </c>
       <c r="E122" s="16" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0013</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1661000</v>
+        <v>1834700</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="H122" t="n">
-        <v>33.85</v>
+        <v>26.21</v>
       </c>
       <c r="I122" s="13" t="inlineStr">
         <is>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>1.3</v>
+        <v>7.748</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>1.403</v>
+        <v>8.164999999999999</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5976,28 +5976,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.29</v>
+        <v>1.26</v>
       </c>
       <c r="E123" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1600500</v>
+        <v>1798000</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="H123" t="n">
-        <v>41.47</v>
+        <v>35.34</v>
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.294</v>
+        <v>1.301</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.309</v>
+        <v>1.403</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6021,28 +6021,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0396</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ADNEX</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.45</v>
+        <v>0.255</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>0.0345</v>
+        <v>0.02</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1576700</v>
+        <v>1767200</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>3.44</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H124" t="n">
-        <v>63.94</v>
+        <v>49.14</v>
       </c>
       <c r="I124" s="17" t="inlineStr">
         <is>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.425</v>
+        <v>0.254</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.418</v>
+        <v>0.264</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6066,39 +6066,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.475</v>
+      </c>
+      <c r="E125" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1548700</v>
+        <v>1753900</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>2.54</v>
+        <v>0.54</v>
       </c>
       <c r="H125" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="I125" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.26</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.992</v>
+        <v>0.46</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.978</v>
+        <v>0.417</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6111,39 +6111,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E126" s="15" t="n">
-        <v>0</v>
+        <v>0.285</v>
+      </c>
+      <c r="E126" s="16" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1500700</v>
+        <v>1660300</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="H126" t="n">
-        <v>68.88</v>
-      </c>
-      <c r="I126" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.25</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.286</v>
+        <v>0.294</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.273</v>
+        <v>0.309</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="E127" s="10" t="n">
-        <v>0.0196</v>
+        <v>13</v>
+      </c>
+      <c r="E127" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1480300</v>
+        <v>1624600</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="H127" t="n">
-        <v>49.33</v>
-      </c>
-      <c r="I127" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.6</v>
+      </c>
+      <c r="I127" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>4.711</v>
+        <v>13.086</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>4.618</v>
+        <v>13.646</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6201,28 +6201,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E128" s="16" t="n">
-        <v>-0.005699999999999999</v>
+        <v>4.67</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1478200</v>
+        <v>1621100</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.49</v>
+        <v>0.17</v>
       </c>
       <c r="H128" t="n">
-        <v>53.73</v>
+        <v>47.6</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.863</v>
+        <v>4.709</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.857</v>
+        <v>4.618</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6246,33 +6246,40 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0396</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>ADNEX</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E129" s="16" t="n">
-        <v>-0.0476</v>
+        <v>0.45</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1449000</v>
+        <v>1577200</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.13</v>
+        <v>3.45</v>
+      </c>
+      <c r="H129" t="n">
+        <v>63.94</v>
       </c>
       <c r="I129" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J129" s="9" t="n"/>
-      <c r="K129" s="9" t="n"/>
+      <c r="J129" s="9" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="K129" s="9" t="n">
+        <v>0.418</v>
+      </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
     </row>
@@ -6284,28 +6291,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="E130" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1447200</v>
+        <v>1565100</v>
       </c>
       <c r="G130" s="12" t="n">
         <v>0.24</v>
       </c>
       <c r="H130" t="n">
-        <v>68.36</v>
+        <v>68.88</v>
       </c>
       <c r="I130" s="17" t="inlineStr">
         <is>
@@ -6313,10 +6320,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.778</v>
+        <v>0.286</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.76</v>
+        <v>0.273</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6329,39 +6336,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E131" s="15" t="n">
-        <v>0</v>
+        <v>1.02</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1432100</v>
+        <v>1548700</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>1.23</v>
+        <v>2.54</v>
       </c>
       <c r="H131" t="n">
-        <v>39.02</v>
-      </c>
-      <c r="I131" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.9</v>
+      </c>
+      <c r="I131" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.425</v>
+        <v>0.992</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.444</v>
+        <v>0.978</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6374,28 +6381,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E132" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E132" s="16" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1410200</v>
+        <v>1478800</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="H132" t="n">
-        <v>54.3</v>
+        <v>61.37</v>
       </c>
       <c r="I132" s="13" t="inlineStr">
         <is>
@@ -6403,10 +6410,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.452</v>
+        <v>0.955</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.421</v>
+        <v>0.802</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6419,28 +6426,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="E133" s="10" t="n">
-        <v>0.0031</v>
+        <v>5.44</v>
+      </c>
+      <c r="E133" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1405900</v>
+        <v>1477200</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.47</v>
+        <v>0.58</v>
       </c>
       <c r="H133" t="n">
-        <v>70.94</v>
+        <v>56.62</v>
       </c>
       <c r="I133" s="17" t="inlineStr">
         <is>
@@ -6448,10 +6455,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>2.905</v>
+        <v>5.266</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>2.76</v>
+        <v>5.296</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6464,39 +6471,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E134" s="16" t="n">
-        <v>-0.0098</v>
+        <v>0.8</v>
+      </c>
+      <c r="E134" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1403800</v>
+        <v>1458300</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="H134" t="n">
-        <v>63.04</v>
-      </c>
-      <c r="I134" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.36</v>
+      </c>
+      <c r="I134" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.956</v>
+        <v>0.778</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.803</v>
+        <v>0.76</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6509,39 +6516,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E135" s="15" t="n">
-        <v>0</v>
+        <v>0.42</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>0.012</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1386600</v>
+        <v>1455400</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.71</v>
+        <v>1.25</v>
       </c>
       <c r="H135" t="n">
-        <v>61.65</v>
-      </c>
-      <c r="I135" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.2</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.456</v>
+        <v>0.425</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.46</v>
+        <v>0.444</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6554,39 +6561,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.785</v>
+        <v>3.28</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>0.0397</v>
+        <v>0.0031</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1381900</v>
+        <v>1451600</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.34</v>
+        <v>0.48</v>
       </c>
       <c r="H136" t="n">
-        <v>46.88</v>
-      </c>
-      <c r="I136" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.94</v>
+      </c>
+      <c r="I136" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>0.792</v>
+        <v>2.905</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.806</v>
+        <v>2.76</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6599,40 +6606,33 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="E137" s="10" t="n">
-        <v>0.0018</v>
+        <v>0.305</v>
+      </c>
+      <c r="E137" s="16" t="n">
+        <v>-0.0317</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>1376700</v>
+        <v>1449400</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H137" t="n">
-        <v>56.91</v>
+        <v>0.13</v>
       </c>
       <c r="I137" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J137" s="9" t="n">
-        <v>5.267</v>
-      </c>
-      <c r="K137" s="9" t="n">
-        <v>5.296</v>
-      </c>
+      <c r="J137" s="9" t="n"/>
+      <c r="K137" s="9" t="n"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
     </row>
@@ -6659,10 +6659,10 @@
         <v>0</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1326700</v>
+        <v>1442000</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="H138" t="n">
         <v>30.34</v>
@@ -6689,28 +6689,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>ECOFIRS</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>0.0196</v>
+        <v>0.32</v>
+      </c>
+      <c r="E139" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>1320100</v>
+        <v>1417800</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="H139" t="n">
-        <v>55.44</v>
+        <v>41.35</v>
       </c>
       <c r="I139" s="17" t="inlineStr">
         <is>
@@ -6718,10 +6718,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>0.247</v>
+        <v>0.331</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>0.252</v>
+        <v>0.34</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6734,36 +6734,40 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.26</v>
+        <v>0.46</v>
       </c>
       <c r="E140" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1319400</v>
+        <v>1411300</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="H140" t="n">
-        <v>25.13</v>
-      </c>
-      <c r="I140" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J140" s="9" t="n"/>
-      <c r="K140" s="9" t="n"/>
+        <v>54.3</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>0.421</v>
+      </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
     </row>
@@ -6790,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>1268900</v>
+        <v>1408400</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="H141" t="n">
         <v>45.4</v>
@@ -6820,28 +6824,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>13.02</v>
-      </c>
-      <c r="E142" s="10" t="n">
-        <v>0.0015</v>
+        <v>0.485</v>
+      </c>
+      <c r="E142" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1264200</v>
+        <v>1406900</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.15</v>
+        <v>0.72</v>
       </c>
       <c r="H142" t="n">
-        <v>42.54</v>
+        <v>61.65</v>
       </c>
       <c r="I142" s="17" t="inlineStr">
         <is>
@@ -6849,10 +6853,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>13.088</v>
+        <v>0.456</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>13.646</v>
+        <v>0.46</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6865,39 +6869,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E143" s="16" t="n">
-        <v>-0.0145</v>
+        <v>0.305</v>
+      </c>
+      <c r="E143" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1263700</v>
+        <v>1387200</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="H143" t="n">
-        <v>60.63</v>
-      </c>
-      <c r="I143" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.55</v>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>1.271</v>
+        <v>0.306</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>1.176</v>
+        <v>0.298</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6910,28 +6914,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>0.61</v>
+        <v>1.38</v>
       </c>
       <c r="E144" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1262200</v>
+        <v>1382500</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="H144" t="n">
-        <v>59.45</v>
+        <v>62.88</v>
       </c>
       <c r="I144" s="17" t="inlineStr">
         <is>
@@ -6939,10 +6943,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>0.581</v>
+        <v>1.273</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>0.578</v>
+        <v>1.176</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6955,28 +6959,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>7.88</v>
+        <v>0.61</v>
       </c>
       <c r="E145" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1195500</v>
+        <v>1359600</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.3</v>
+        <v>0.43</v>
       </c>
       <c r="H145" t="n">
-        <v>73.64</v>
+        <v>59.45</v>
       </c>
       <c r="I145" s="17" t="inlineStr">
         <is>
@@ -6984,10 +6988,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>6.972</v>
+        <v>0.581</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>6.656</v>
+        <v>0.578</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7000,12 +7004,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
@@ -7015,25 +7019,21 @@
         <v>0</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1178300</v>
+        <v>1328200</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>1.24</v>
+        <v>0.11</v>
       </c>
       <c r="H146" t="n">
-        <v>45.51</v>
-      </c>
-      <c r="I146" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J146" s="9" t="n">
-        <v>0.261</v>
-      </c>
-      <c r="K146" s="9" t="n">
-        <v>0.265</v>
-      </c>
+        <v>25.13</v>
+      </c>
+      <c r="I146" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="n"/>
+      <c r="K146" s="9" t="n"/>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
     </row>
@@ -7045,28 +7045,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0466</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SRKKAI</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E147" s="16" t="n">
-        <v>-0.0182</v>
+        <v>0.26</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>1168600</v>
+        <v>1324800</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>1.12</v>
+        <v>0.46</v>
       </c>
       <c r="H147" t="n">
-        <v>54.08</v>
+        <v>55.44</v>
       </c>
       <c r="I147" s="17" t="inlineStr">
         <is>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>0.526</v>
+        <v>0.247</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>0.533</v>
+        <v>0.252</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7090,28 +7090,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E148" s="15" t="n">
-        <v>0</v>
+        <v>7.86</v>
+      </c>
+      <c r="E148" s="16" t="n">
+        <v>-0.0025</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>1140100</v>
+        <v>1293100</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="H148" t="n">
-        <v>76.33</v>
+        <v>73</v>
       </c>
       <c r="I148" s="17" t="inlineStr">
         <is>
@@ -7119,10 +7119,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>1.029</v>
+        <v>6.97</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>0.863</v>
+        <v>6.656</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7135,39 +7135,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>2.67</v>
+        <v>2.04</v>
       </c>
       <c r="E149" s="10" t="n">
-        <v>0.0389</v>
+        <v>0.0049</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>1121600</v>
+        <v>1247300</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.74</v>
+        <v>0.42</v>
       </c>
       <c r="H149" t="n">
-        <v>76.06999999999999</v>
-      </c>
-      <c r="I149" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.23</v>
+      </c>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>2.34</v>
+        <v>2.052</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>2.101</v>
+        <v>2.09</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7180,28 +7180,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="E150" s="10" t="n">
-        <v>0.006</v>
+        <v>1.12</v>
+      </c>
+      <c r="E150" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>1108000</v>
+        <v>1245800</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="H150" t="n">
-        <v>69.39</v>
+        <v>76.33</v>
       </c>
       <c r="I150" s="17" t="inlineStr">
         <is>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>3.103</v>
+        <v>1.029</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>2.678</v>
+        <v>0.863</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7225,28 +7225,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0466</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>SRKKAI</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E151" s="10" t="n">
-        <v>0.0129</v>
+        <v>0.54</v>
+      </c>
+      <c r="E151" s="16" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>1098700</v>
+        <v>1194600</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.17</v>
+        <v>1.14</v>
       </c>
       <c r="H151" t="n">
-        <v>69.22</v>
+        <v>54.08</v>
       </c>
       <c r="I151" s="17" t="inlineStr">
         <is>
@@ -7254,10 +7254,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>0.718</v>
+        <v>0.526</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>0.647</v>
+        <v>0.533</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7270,39 +7270,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>2.04</v>
+        <v>2.67</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>0.0049</v>
+        <v>0.0389</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>1097800</v>
+        <v>1179500</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.37</v>
+        <v>0.78</v>
       </c>
       <c r="H152" t="n">
-        <v>45.23</v>
-      </c>
-      <c r="I152" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.06999999999999</v>
+      </c>
+      <c r="I152" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>2.052</v>
+        <v>2.34</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>2.09</v>
+        <v>2.101</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7315,39 +7315,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E153" s="10" t="n">
-        <v>0.012</v>
+        <v>0.26</v>
+      </c>
+      <c r="E153" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>1065200</v>
+        <v>1178300</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.6</v>
+        <v>1.24</v>
       </c>
       <c r="H153" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="I153" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.51</v>
+      </c>
+      <c r="I153" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>0.86</v>
+        <v>0.261</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>0.931</v>
+        <v>0.265</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7360,39 +7360,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>IFCAMSC</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E154" s="16" t="n">
-        <v>-0.0244</v>
+        <v>3.32</v>
+      </c>
+      <c r="E154" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>1022500</v>
+        <v>1177200</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>1.93</v>
+        <v>0.55</v>
       </c>
       <c r="H154" t="n">
-        <v>42.22</v>
-      </c>
-      <c r="I154" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.72</v>
+      </c>
+      <c r="I154" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>0.204</v>
+        <v>3.101</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>0.215</v>
+        <v>2.677</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7405,28 +7405,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E155" s="10" t="n">
-        <v>0.018</v>
+        <v>1.7</v>
+      </c>
+      <c r="E155" s="16" t="n">
+        <v>-0.023</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>1021600</v>
+        <v>1146400</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.16</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H155" t="n">
-        <v>46.32</v>
+        <v>24.47</v>
       </c>
       <c r="I155" s="13" t="inlineStr">
         <is>
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>1.15</v>
+        <v>1.837</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>1.16</v>
+        <v>1.94</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7465,10 +7465,10 @@
         <v>0.0053</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>997200</v>
+        <v>1144400</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H156" t="n">
         <v>35.8</v>
@@ -7495,28 +7495,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>10.98</v>
+        <v>0.84</v>
       </c>
       <c r="E157" s="10" t="n">
-        <v>0.0204</v>
+        <v>0.012</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>996000</v>
+        <v>1127900</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.31</v>
+        <v>0.63</v>
       </c>
       <c r="H157" t="n">
-        <v>78.98999999999999</v>
+        <v>37.3</v>
       </c>
       <c r="I157" s="17" t="inlineStr">
         <is>
@@ -7524,10 +7524,10 @@
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>9.933</v>
+        <v>0.86</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>9.358000000000001</v>
+        <v>0.931</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7540,39 +7540,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>3.37</v>
+        <v>0.79</v>
       </c>
       <c r="E158" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0194</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>972200</v>
+        <v>1107200</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="H158" t="n">
-        <v>33.28</v>
-      </c>
-      <c r="I158" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.86</v>
+      </c>
+      <c r="I158" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>3.516</v>
+        <v>0.719</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>3.675</v>
+        <v>0.647</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7585,39 +7585,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="E159" s="16" t="n">
-        <v>-0.0172</v>
+        <v>11</v>
+      </c>
+      <c r="E159" s="10" t="n">
+        <v>0.0223</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>948800</v>
+        <v>1093100</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.67</v>
+        <v>0.34</v>
       </c>
       <c r="H159" t="n">
-        <v>25.22</v>
-      </c>
-      <c r="I159" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.18000000000001</v>
+      </c>
+      <c r="I159" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>1.838</v>
+        <v>9.935</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>1.94</v>
+        <v>9.358000000000001</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7639,19 +7639,19 @@
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="E160" s="10" t="n">
-        <v>0.0166</v>
+        <v>0.015</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>939600</v>
+        <v>1089000</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H160" t="n">
-        <v>41.95</v>
+        <v>41.27</v>
       </c>
       <c r="I160" s="13" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>6.212</v>
+        <v>6.211</v>
       </c>
       <c r="K160" s="9" t="n">
         <v>6.43</v>
@@ -7675,28 +7675,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>4.01</v>
+        <v>7.98</v>
       </c>
       <c r="E161" s="10" t="n">
-        <v>0.005</v>
+        <v>0.0101</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>889500</v>
+        <v>1034400</v>
       </c>
       <c r="G161" s="12" t="n">
         <v>0.29</v>
       </c>
       <c r="H161" t="n">
-        <v>62.23</v>
+        <v>55.99</v>
       </c>
       <c r="I161" s="17" t="inlineStr">
         <is>
@@ -7704,10 +7704,10 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>3.837</v>
+        <v>7.889</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>3.519</v>
+        <v>7.837</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7720,28 +7720,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="E162" s="15" t="n">
-        <v>0</v>
+        <v>1.14</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>0.027</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>855200</v>
+        <v>1029400</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.38</v>
+        <v>0.16</v>
       </c>
       <c r="H162" t="n">
-        <v>31.03</v>
+        <v>47.85</v>
       </c>
       <c r="I162" s="13" t="inlineStr">
         <is>
@@ -7749,10 +7749,10 @@
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>1.522</v>
+        <v>1.151</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>1.637</v>
+        <v>1.161</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7765,39 +7765,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>IFCAMSC</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>1.22</v>
+        <v>0.2</v>
       </c>
       <c r="E163" s="16" t="n">
-        <v>-0.0161</v>
+        <v>-0.0244</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>848000</v>
+        <v>1022500</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.12</v>
+        <v>1.93</v>
       </c>
       <c r="H163" t="n">
-        <v>73.12</v>
-      </c>
-      <c r="I163" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.22</v>
+      </c>
+      <c r="I163" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>1.034</v>
+        <v>0.204</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>0.798</v>
+        <v>0.215</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7810,39 +7810,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>0.65</v>
+        <v>3.37</v>
       </c>
       <c r="E164" s="10" t="n">
-        <v>0.0156</v>
+        <v>0.003</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>839600</v>
+        <v>1020700</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="H164" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="I164" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.28</v>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>0.629</v>
+        <v>3.516</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>0.596</v>
+        <v>3.675</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7855,28 +7855,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E165" s="10" t="n">
-        <v>0.027</v>
+        <v>0.925</v>
+      </c>
+      <c r="E165" s="16" t="n">
+        <v>-0.0054</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>825600</v>
+        <v>926000</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="H165" t="n">
-        <v>42.79</v>
+        <v>47.63</v>
       </c>
       <c r="I165" s="13" t="inlineStr">
         <is>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>1.941</v>
+        <v>0.927</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>1.962</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7900,28 +7900,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>8.01</v>
+        <v>0.645</v>
       </c>
       <c r="E166" s="10" t="n">
-        <v>0.0139</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>819700</v>
+        <v>920500</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="H166" t="n">
-        <v>57.32</v>
+        <v>57.53</v>
       </c>
       <c r="I166" s="17" t="inlineStr">
         <is>
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>7.892</v>
+        <v>0.629</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>7.838</v>
+        <v>0.595</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7945,28 +7945,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="E167" s="16" t="n">
-        <v>-0.0044</v>
+        <v>4.01</v>
+      </c>
+      <c r="E167" s="10" t="n">
+        <v>0.005</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>768200</v>
+        <v>899600</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="H167" t="n">
-        <v>59.95</v>
+        <v>62.23</v>
       </c>
       <c r="I167" s="17" t="inlineStr">
         <is>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>8.742000000000001</v>
+        <v>3.837</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>8.651</v>
+        <v>3.519</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -7990,28 +7990,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E168" s="15" t="n">
-        <v>0</v>
+        <v>1.46</v>
+      </c>
+      <c r="E168" s="16" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>763200</v>
+        <v>890100</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="H168" t="n">
-        <v>50.08</v>
+        <v>29.67</v>
       </c>
       <c r="I168" s="13" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>0.927</v>
+        <v>1.521</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.637</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8035,28 +8035,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E169" s="15" t="n">
-        <v>0</v>
+        <v>1.22</v>
+      </c>
+      <c r="E169" s="16" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>753100</v>
+        <v>859600</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.51</v>
+        <v>0.12</v>
       </c>
       <c r="H169" t="n">
-        <v>60.43</v>
+        <v>73.12</v>
       </c>
       <c r="I169" s="17" t="inlineStr">
         <is>
@@ -8064,10 +8064,10 @@
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>0.482</v>
+        <v>1.034</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>0.475</v>
+        <v>0.798</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8080,39 +8080,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="E170" s="16" t="n">
-        <v>-0.0205</v>
+        <v>1.89</v>
+      </c>
+      <c r="E170" s="10" t="n">
+        <v>0.0216</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>741000</v>
+        <v>848800</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.4</v>
+        <v>0.12</v>
       </c>
       <c r="H170" t="n">
-        <v>58.42</v>
-      </c>
-      <c r="I170" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.18</v>
+      </c>
+      <c r="I170" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>0.921</v>
+        <v>1.94</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>0.838</v>
+        <v>1.962</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8125,39 +8125,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1.16</v>
+        <v>3.12</v>
       </c>
       <c r="E171" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>740900</v>
+        <v>837100</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.48</v>
+        <v>0.21</v>
       </c>
       <c r="H171" t="n">
-        <v>60.29</v>
-      </c>
-      <c r="I171" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.75</v>
+      </c>
+      <c r="I171" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>1.111</v>
+        <v>3.212</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>1.077</v>
+        <v>3.415</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8170,39 +8170,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>WELLCAL</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>3.12</v>
+        <v>1.13</v>
       </c>
       <c r="E172" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>737800</v>
+        <v>806100</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>0.19</v>
+        <v>2.7</v>
       </c>
       <c r="H172" t="n">
-        <v>35.75</v>
-      </c>
-      <c r="I172" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.43</v>
+      </c>
+      <c r="I172" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>3.212</v>
+        <v>1.119</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>3.415</v>
+        <v>1.114</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8215,39 +8215,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E173" s="10" t="n">
-        <v>0.0224</v>
+        <v>9.08</v>
+      </c>
+      <c r="E173" s="16" t="n">
+        <v>-0.0044</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>725100</v>
+        <v>802400</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="H173" t="n">
-        <v>55.19</v>
-      </c>
-      <c r="I173" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.95</v>
+      </c>
+      <c r="I173" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>1.354</v>
+        <v>8.742000000000001</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>1.211</v>
+        <v>8.651</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8260,28 +8260,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E174" s="16" t="n">
-        <v>-0.0139</v>
+        <v>4.3</v>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>711400</v>
+        <v>786900</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.77</v>
+        <v>0.31</v>
       </c>
       <c r="H174" t="n">
-        <v>39.37</v>
+        <v>48.19</v>
       </c>
       <c r="I174" s="13" t="inlineStr">
         <is>
@@ -8289,10 +8289,10 @@
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>2.259</v>
+        <v>4.332</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>2.324</v>
+        <v>4.373</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8305,28 +8305,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>WELLCAL</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E175" s="16" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.505</v>
+      </c>
+      <c r="E175" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>706100</v>
+        <v>777100</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>2.36</v>
+        <v>0.53</v>
       </c>
       <c r="H175" t="n">
-        <v>51.7</v>
+        <v>60.43</v>
       </c>
       <c r="I175" s="17" t="inlineStr">
         <is>
@@ -8334,10 +8334,10 @@
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>1.118</v>
+        <v>0.482</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>1.114</v>
+        <v>0.475</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8350,39 +8350,39 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="E176" s="10" t="n">
-        <v>0.009399999999999999</v>
+        <v>1.16</v>
+      </c>
+      <c r="E176" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>702400</v>
+        <v>764400</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.28</v>
+        <v>0.49</v>
       </c>
       <c r="H176" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="I176" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.29</v>
+      </c>
+      <c r="I176" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>4.333</v>
+        <v>1.111</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>4.374</v>
+        <v>1.077</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8395,28 +8395,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E177" s="15" t="n">
-        <v>0</v>
+        <v>0.64</v>
+      </c>
+      <c r="E177" s="10" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>701200</v>
+        <v>756000</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>0.53</v>
+        <v>0.65</v>
       </c>
       <c r="H177" t="n">
-        <v>64.66</v>
+        <v>88.41</v>
       </c>
       <c r="I177" s="17" t="inlineStr">
         <is>
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>0.641</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>0.61</v>
+        <v>0.535</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8440,39 +8440,39 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="E178" s="10" t="n">
-        <v>0.0138</v>
+        <v>2.13</v>
+      </c>
+      <c r="E178" s="16" t="n">
+        <v>-0.0139</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>683700</v>
+        <v>755400</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.17</v>
+        <v>0.82</v>
       </c>
       <c r="H178" t="n">
-        <v>45.48</v>
-      </c>
-      <c r="I178" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.37</v>
+      </c>
+      <c r="I178" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>6.607</v>
+        <v>2.259</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>6.871</v>
+        <v>2.324</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8485,39 +8485,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="E179" s="10" t="n">
-        <v>0.011</v>
+        <v>0.955</v>
+      </c>
+      <c r="E179" s="16" t="n">
+        <v>-0.0205</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>682700</v>
+        <v>749600</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>0.24</v>
+        <v>0.41</v>
       </c>
       <c r="H179" t="n">
-        <v>30.39</v>
-      </c>
-      <c r="I179" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.42</v>
+      </c>
+      <c r="I179" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>1.919</v>
+        <v>0.921</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>2.041</v>
+        <v>0.838</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8530,28 +8530,28 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D180" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E180" s="15" t="n">
-        <v>0</v>
+        <v>6.58</v>
+      </c>
+      <c r="E180" s="10" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>680000</v>
+        <v>733600</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>0.51</v>
+        <v>0.18</v>
       </c>
       <c r="H180" t="n">
-        <v>44.84</v>
+        <v>44.73</v>
       </c>
       <c r="I180" s="17" t="inlineStr">
         <is>
@@ -8559,10 +8559,10 @@
         </is>
       </c>
       <c r="J180" s="9" t="n">
-        <v>0.634</v>
+        <v>6.606</v>
       </c>
       <c r="K180" s="9" t="n">
-        <v>0.63</v>
+        <v>6.87</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="14" t="inlineStr"/>
@@ -8575,28 +8575,28 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D181" s="9" t="n">
-        <v>2.17</v>
+        <v>1.37</v>
       </c>
       <c r="E181" s="10" t="n">
-        <v>0.014</v>
+        <v>0.0224</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>654800</v>
+        <v>725100</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>0.11</v>
+        <v>0.26</v>
       </c>
       <c r="H181" t="n">
-        <v>48.83</v>
+        <v>55.19</v>
       </c>
       <c r="I181" s="13" t="inlineStr">
         <is>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="J181" s="9" t="n">
-        <v>2.193</v>
+        <v>1.354</v>
       </c>
       <c r="K181" s="9" t="n">
-        <v>2.116</v>
+        <v>1.211</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="14" t="inlineStr"/>
@@ -8620,28 +8620,28 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D182" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E182" s="15" t="n">
-        <v>0</v>
+        <v>1.31</v>
+      </c>
+      <c r="E182" s="16" t="n">
+        <v>-0.0368</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>616100</v>
+        <v>701800</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="H182" t="n">
-        <v>39.05</v>
+        <v>68.75</v>
       </c>
       <c r="I182" s="17" t="inlineStr">
         <is>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="J182" s="9" t="n">
-        <v>0.916</v>
+        <v>1.142</v>
       </c>
       <c r="K182" s="9" t="n">
-        <v>0.968</v>
+        <v>1.13</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="14" t="inlineStr"/>
@@ -8665,28 +8665,28 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E183" s="16" t="n">
-        <v>-0.0368</v>
+        <v>0.675</v>
+      </c>
+      <c r="E183" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>605300</v>
+        <v>701200</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>0.2</v>
+        <v>0.53</v>
       </c>
       <c r="H183" t="n">
-        <v>68.75</v>
+        <v>64.66</v>
       </c>
       <c r="I183" s="17" t="inlineStr">
         <is>
@@ -8694,10 +8694,10 @@
         </is>
       </c>
       <c r="J183" s="9" t="n">
-        <v>1.142</v>
+        <v>0.641</v>
       </c>
       <c r="K183" s="9" t="n">
-        <v>1.13</v>
+        <v>0.61</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="14" t="inlineStr"/>
@@ -8710,28 +8710,28 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D184" s="9" t="n">
-        <v>0.92</v>
+        <v>1.82</v>
       </c>
       <c r="E184" s="10" t="n">
-        <v>0.011</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>604800</v>
+        <v>693900</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="H184" t="n">
-        <v>34.14</v>
+        <v>28.11</v>
       </c>
       <c r="I184" s="13" t="inlineStr">
         <is>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="J184" s="9" t="n">
-        <v>0.988</v>
+        <v>1.918</v>
       </c>
       <c r="K184" s="9" t="n">
-        <v>1.019</v>
+        <v>2.041</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="14" t="inlineStr"/>
@@ -8755,28 +8755,28 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D185" s="9" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="E185" s="16" t="n">
-        <v>-0.0072</v>
+        <v>0.63</v>
+      </c>
+      <c r="E185" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>593900</v>
+        <v>680000</v>
       </c>
       <c r="G185" s="12" t="n">
-        <v>0.13</v>
+        <v>0.51</v>
       </c>
       <c r="H185" t="n">
-        <v>55.21</v>
+        <v>44.84</v>
       </c>
       <c r="I185" s="17" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         </is>
       </c>
       <c r="J185" s="9" t="n">
-        <v>6.778</v>
+        <v>0.634</v>
       </c>
       <c r="K185" s="9" t="n">
-        <v>6.846</v>
+        <v>0.63</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="14" t="inlineStr"/>
@@ -8800,28 +8800,28 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D186" s="9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="E186" s="16" t="n">
-        <v>-0.0038</v>
+        <v>2.16</v>
+      </c>
+      <c r="E186" s="10" t="n">
+        <v>0.009300000000000001</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>572900</v>
+        <v>674300</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>0.42</v>
+        <v>0.12</v>
       </c>
       <c r="H186" t="n">
-        <v>34.17</v>
+        <v>48</v>
       </c>
       <c r="I186" s="13" t="inlineStr">
         <is>
@@ -8829,10 +8829,10 @@
         </is>
       </c>
       <c r="J186" s="9" t="n">
-        <v>2.879</v>
+        <v>2.192</v>
       </c>
       <c r="K186" s="9" t="n">
-        <v>2.842</v>
+        <v>2.115</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" s="14" t="inlineStr"/>
@@ -8845,39 +8845,39 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D187" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E187" s="10" t="n">
-        <v>0.009300000000000001</v>
+        <v>6.86</v>
+      </c>
+      <c r="E187" s="16" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>558400</v>
+        <v>660100</v>
       </c>
       <c r="G187" s="12" t="n">
         <v>0.15</v>
       </c>
       <c r="H187" t="n">
-        <v>38.97</v>
-      </c>
-      <c r="I187" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.95</v>
+      </c>
+      <c r="I187" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J187" s="9" t="n">
-        <v>0.5590000000000001</v>
+        <v>6.779</v>
       </c>
       <c r="K187" s="9" t="n">
-        <v>0.587</v>
+        <v>6.847</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" s="14" t="inlineStr"/>
@@ -8890,39 +8890,39 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0366</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>ICENTS</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D188" s="9" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E188" s="15" t="n">
-        <v>0</v>
+        <v>0.765</v>
+      </c>
+      <c r="E188" s="10" t="n">
+        <v>0.02</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>551100</v>
+        <v>655300</v>
       </c>
       <c r="G188" s="12" t="n">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
       <c r="H188" t="n">
-        <v>57.38</v>
-      </c>
-      <c r="I188" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.87</v>
+      </c>
+      <c r="I188" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J188" s="9" t="n">
-        <v>0.83</v>
+        <v>0.736</v>
       </c>
       <c r="K188" s="9" t="n">
-        <v>0.756</v>
+        <v>0.75</v>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" s="14" t="inlineStr"/>
@@ -8935,39 +8935,39 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D189" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E189" s="10" t="n">
-        <v>0.0157</v>
+        <v>4.28</v>
+      </c>
+      <c r="E189" s="16" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>547700</v>
+        <v>644400</v>
       </c>
       <c r="G189" s="12" t="n">
-        <v>0.47</v>
+        <v>0.12</v>
       </c>
       <c r="H189" t="n">
-        <v>88.87</v>
-      </c>
-      <c r="I189" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.03</v>
+      </c>
+      <c r="I189" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J189" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>4.546</v>
       </c>
       <c r="K189" s="9" t="n">
-        <v>0.535</v>
+        <v>4.888</v>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" s="14" t="inlineStr"/>
@@ -8980,28 +8980,28 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D190" s="9" t="n">
-        <v>1.63</v>
+        <v>0.915</v>
       </c>
       <c r="E190" s="10" t="n">
-        <v>0.0252</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>540300</v>
+        <v>627600</v>
       </c>
       <c r="G190" s="12" t="n">
-        <v>0.58</v>
+        <v>0.29</v>
       </c>
       <c r="H190" t="n">
-        <v>49.47</v>
+        <v>32.88</v>
       </c>
       <c r="I190" s="13" t="inlineStr">
         <is>
@@ -9009,10 +9009,10 @@
         </is>
       </c>
       <c r="J190" s="9" t="n">
-        <v>1.623</v>
+        <v>0.988</v>
       </c>
       <c r="K190" s="9" t="n">
-        <v>1.692</v>
+        <v>1.019</v>
       </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" s="14" t="inlineStr"/>
@@ -9025,28 +9025,28 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D191" s="9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E191" s="10" t="n">
-        <v>0.0133</v>
+        <v>0.9</v>
+      </c>
+      <c r="E191" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>539800</v>
+        <v>618100</v>
       </c>
       <c r="G191" s="12" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="H191" t="n">
-        <v>58.45</v>
+        <v>39.05</v>
       </c>
       <c r="I191" s="17" t="inlineStr">
         <is>
@@ -9054,10 +9054,10 @@
         </is>
       </c>
       <c r="J191" s="9" t="n">
-        <v>0.736</v>
+        <v>0.916</v>
       </c>
       <c r="K191" s="9" t="n">
-        <v>0.75</v>
+        <v>0.968</v>
       </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" s="14" t="inlineStr"/>
@@ -9070,28 +9070,28 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>TMK</t>
         </is>
       </c>
       <c r="D192" s="9" t="n">
-        <v>0.645</v>
+        <v>2.65</v>
       </c>
       <c r="E192" s="16" t="n">
-        <v>-0.0373</v>
+        <v>-0.0038</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>532000</v>
+        <v>607100</v>
       </c>
       <c r="G192" s="12" t="n">
-        <v>1.26</v>
+        <v>0.45</v>
       </c>
       <c r="H192" t="n">
-        <v>49.78</v>
+        <v>34.17</v>
       </c>
       <c r="I192" s="13" t="inlineStr">
         <is>
@@ -9099,10 +9099,10 @@
         </is>
       </c>
       <c r="J192" s="9" t="n">
-        <v>0.643</v>
+        <v>2.879</v>
       </c>
       <c r="K192" s="9" t="n">
-        <v>0.655</v>
+        <v>2.842</v>
       </c>
       <c r="L192" t="inlineStr"/>
       <c r="M192" s="14" t="inlineStr"/>
@@ -9115,28 +9115,28 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="D193" s="9" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="E193" s="16" t="n">
-        <v>-0.004699999999999999</v>
+        <v>4.24</v>
+      </c>
+      <c r="E193" s="10" t="n">
+        <v>0.0266</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>524900</v>
+        <v>567900</v>
       </c>
       <c r="G193" s="12" t="n">
-        <v>0.1</v>
+        <v>0.65</v>
       </c>
       <c r="H193" t="n">
-        <v>26.03</v>
+        <v>54.07</v>
       </c>
       <c r="I193" s="13" t="inlineStr">
         <is>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="J193" s="9" t="n">
-        <v>4.546</v>
+        <v>4.109</v>
       </c>
       <c r="K193" s="9" t="n">
-        <v>4.888</v>
+        <v>4.258</v>
       </c>
       <c r="L193" t="inlineStr"/>
       <c r="M193" s="14" t="inlineStr"/>
@@ -9160,45 +9160,405 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>PJBUMI</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D194" s="9" t="n">
-        <v>4.12</v>
+        <v>0.54</v>
       </c>
       <c r="E194" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>522300</v>
+        <v>558500</v>
       </c>
       <c r="G194" s="12" t="n">
-        <v>0.79</v>
+        <v>0.15</v>
       </c>
       <c r="H194" t="n">
-        <v>67.45999999999999</v>
-      </c>
-      <c r="I194" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.62</v>
+      </c>
+      <c r="I194" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J194" s="9" t="n">
-        <v>4.03</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K194" s="9" t="n">
-        <v>3.902</v>
+        <v>0.587</v>
       </c>
       <c r="L194" t="inlineStr"/>
       <c r="M194" s="14" t="inlineStr"/>
     </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>7197</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>GESHEN</t>
+        </is>
+      </c>
+      <c r="D195" s="9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E195" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" s="11" t="n">
+        <v>557500</v>
+      </c>
+      <c r="G195" s="12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H195" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="I195" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J195" s="9" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="K195" s="9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" s="14" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>0366</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>ICENTS</t>
+        </is>
+      </c>
+      <c r="D196" s="9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E196" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" s="11" t="n">
+        <v>551100</v>
+      </c>
+      <c r="G196" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H196" t="n">
+        <v>57.38</v>
+      </c>
+      <c r="I196" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J196" s="9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K196" s="9" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" s="14" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>BMGREEN</t>
+        </is>
+      </c>
+      <c r="D197" s="9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E197" s="10" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="F197" s="11" t="n">
+        <v>540300</v>
+      </c>
+      <c r="G197" s="12" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H197" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="I197" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J197" s="9" t="n">
+        <v>1.623</v>
+      </c>
+      <c r="K197" s="9" t="n">
+        <v>1.692</v>
+      </c>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" s="14" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>7163</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>PJBUMI</t>
+        </is>
+      </c>
+      <c r="D198" s="9" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="E198" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" s="11" t="n">
+        <v>535700</v>
+      </c>
+      <c r="G198" s="12" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H198" t="n">
+        <v>67.45999999999999</v>
+      </c>
+      <c r="I198" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J198" s="9" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="K198" s="9" t="n">
+        <v>3.902</v>
+      </c>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" s="14" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>5202</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>MSM</t>
+        </is>
+      </c>
+      <c r="D199" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E199" s="16" t="n">
+        <v>-0.0373</v>
+      </c>
+      <c r="F199" s="11" t="n">
+        <v>532000</v>
+      </c>
+      <c r="G199" s="12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="H199" t="n">
+        <v>49.78</v>
+      </c>
+      <c r="I199" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J199" s="9" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="K199" s="9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" s="14" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>9075</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>THETA</t>
+        </is>
+      </c>
+      <c r="D200" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E200" s="16" t="n">
+        <v>-0.0236</v>
+      </c>
+      <c r="F200" s="11" t="n">
+        <v>510200</v>
+      </c>
+      <c r="G200" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H200" t="n">
+        <v>43.59</v>
+      </c>
+      <c r="I200" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J200" s="9" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="K200" s="9" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" s="14" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>SUNCON</t>
+        </is>
+      </c>
+      <c r="D201" s="9" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="E201" s="16" t="n">
+        <v>-0.0066</v>
+      </c>
+      <c r="F201" s="11" t="n">
+        <v>509500</v>
+      </c>
+      <c r="G201" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H201" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="I201" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J201" s="9" t="n">
+        <v>7.641</v>
+      </c>
+      <c r="K201" s="9" t="n">
+        <v>7.817</v>
+      </c>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" s="14" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>5212</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>PAVREIT</t>
+        </is>
+      </c>
+      <c r="D202" s="9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E202" s="10" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="F202" s="11" t="n">
+        <v>503000</v>
+      </c>
+      <c r="G202" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H202" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="I202" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J202" s="9" t="n">
+        <v>1.564</v>
+      </c>
+      <c r="K202" s="9" t="n">
+        <v>1.629</v>
+      </c>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M194"/>
+  <autoFilter ref="A1:M202"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-06/bursa-report-2026-10-06.xlsx
+++ b/docs/downloads/2026-10-06/bursa-report-2026-10-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-06" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-06'!$A$1:$M$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-06'!$A$1:$M$203</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M202"/>
+  <dimension ref="A1:M203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.0408</v>
+        <v>-0.047</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>2679200</v>
+        <v>2851400</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>71.2</v>
+        <v>70.33</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>2.566</v>
+        <v>2.564</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1.952</v>
+        <v>1.951</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，但RSI达71.2已超买，现价RM3.06远高于50日均线RM1.952，偏离较大，信号可靠性存疑。</t>
+          <t>SAR转多信号，但RSI达70.33已近超买，现价3.04远高于50日均线1.951，偏离较大。</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
         <v>0.4615</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>647286500</v>
+        <v>647420300</v>
       </c>
       <c r="G3" s="12" t="n">
         <v>1.32</v>
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>23180400</v>
+        <v>23200400</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>4.06</v>
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.11</v>
+        <v>0.115</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>0.1579</v>
+        <v>0.2105</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>13009800</v>
+        <v>13021800</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>8.65</v>
+        <v>8.66</v>
       </c>
       <c r="H15" t="n">
-        <v>64.31</v>
+        <v>66.62</v>
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
@@ -1195,19 +1195,19 @@
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.625</v>
+        <v>0.62</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>-0.0234</v>
+        <v>-0.0313</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>12872000</v>
+        <v>12905500</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>0.7</v>
       </c>
       <c r="H16" t="n">
-        <v>63.88</v>
+        <v>62.83</v>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>0.0191</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>12164600</v>
+        <v>12196700</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0.26</v>
@@ -1912,7 +1912,7 @@
         <v>-0.005500000000000001</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>8803400</v>
+        <v>8803500</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>0.38</v>
@@ -1957,7 +1957,7 @@
         <v>0.0141</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7946500</v>
+        <v>7997700</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>1.08</v>
@@ -2542,7 +2542,7 @@
         <v>0.009000000000000001</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>6051100</v>
+        <v>6056100</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>0.43</v>
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.37</v>
+        <v>0.375</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>-0.039</v>
+        <v>-0.026</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>5651400</v>
+        <v>5657400</v>
       </c>
       <c r="G49" s="12" t="n">
         <v>0.66</v>
       </c>
       <c r="H49" t="n">
-        <v>65.28</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="I49" s="17" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>0.345</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.316</v>
+        <v>0.317</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2760,7 +2760,7 @@
         <v>-0.0488</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>5338500</v>
+        <v>5340200</v>
       </c>
       <c r="G51" s="12" t="n">
         <v>0.23</v>
@@ -2799,19 +2799,19 @@
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>10.02</v>
+        <v>10.04</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>5305800</v>
+        <v>5314000</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>0.45</v>
       </c>
       <c r="H52" t="n">
-        <v>41.51</v>
+        <v>43.15</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>10.095</v>
+        <v>10.097</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>10.249</v>
@@ -2895,10 +2895,10 @@
         <v>0.0721</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>5220000</v>
+        <v>5221000</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H54" t="n">
         <v>53.99</v>
@@ -3024,19 +3024,19 @@
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.715</v>
+        <v>0.71</v>
       </c>
       <c r="E57" s="16" t="n">
-        <v>-0.0205</v>
+        <v>-0.0274</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>5009000</v>
+        <v>5019000</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>0.51</v>
       </c>
       <c r="H57" t="n">
-        <v>64.78</v>
+        <v>63.57</v>
       </c>
       <c r="I57" s="17" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.657</v>
+        <v>0.656</v>
       </c>
       <c r="K57" s="9" t="n">
         <v>0.595</v>
@@ -3165,7 +3165,7 @@
         <v>0.008</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>4571800</v>
+        <v>4571900</v>
       </c>
       <c r="G60" s="12" t="n">
         <v>0.31</v>
@@ -3210,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>4549900</v>
+        <v>4553900</v>
       </c>
       <c r="G61" s="12" t="n">
         <v>0.6899999999999999</v>
@@ -3240,39 +3240,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>0.0191</v>
+        <v>1.08</v>
+      </c>
+      <c r="E62" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>4330100</v>
+        <v>4481300</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>1.2</v>
+        <v>0.39</v>
       </c>
       <c r="H62" t="n">
-        <v>66.43000000000001</v>
-      </c>
-      <c r="I62" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.09</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>2.568</v>
+        <v>1.069</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>2.23</v>
+        <v>1.03</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3285,28 +3285,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E63" s="15" t="n">
-        <v>0</v>
+        <v>2.67</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0.0191</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>4263200</v>
+        <v>4330100</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="H63" t="n">
-        <v>52.53</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="I63" s="17" t="inlineStr">
         <is>
@@ -3314,10 +3314,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.153</v>
+        <v>2.568</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.151</v>
+        <v>2.23</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3330,39 +3330,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>1.08</v>
+        <v>0.155</v>
       </c>
       <c r="E64" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>4259300</v>
+        <v>4263200</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.37</v>
+        <v>1.21</v>
       </c>
       <c r="H64" t="n">
-        <v>53.09</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.53</v>
+      </c>
+      <c r="I64" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>1.069</v>
+        <v>0.153</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>1.03</v>
+        <v>0.151</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3570,7 +3570,7 @@
         <v>-0.008500000000000001</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3685600</v>
+        <v>3693100</v>
       </c>
       <c r="G69" s="12" t="n">
         <v>0.22</v>
@@ -3705,7 +3705,7 @@
         <v>-0.0171</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>3542700</v>
+        <v>3575400</v>
       </c>
       <c r="G72" s="12" t="n">
         <v>0.3</v>
@@ -3750,7 +3750,7 @@
         <v>0.0104</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>3420500</v>
+        <v>3427800</v>
       </c>
       <c r="G73" s="12" t="n">
         <v>0.09</v>
@@ -3789,19 +3789,19 @@
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="E74" s="16" t="n">
-        <v>-0.0171</v>
+        <v>-0.0137</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>3389500</v>
+        <v>3389600</v>
       </c>
       <c r="G74" s="12" t="n">
         <v>1.05</v>
       </c>
       <c r="H74" t="n">
-        <v>73.87</v>
+        <v>74.61</v>
       </c>
       <c r="I74" s="17" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>2.534</v>
+        <v>2.535</v>
       </c>
       <c r="K74" s="9" t="n">
         <v>2.078</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3301300</v>
+        <v>3304600</v>
       </c>
       <c r="G77" s="12" t="n">
         <v>0.8100000000000001</v>
@@ -4065,10 +4065,10 @@
         <v>0.03700000000000001</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>3046200</v>
+        <v>3058000</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H80" t="n">
         <v>75.34</v>
@@ -4245,7 +4245,7 @@
         <v>0.0222</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2948400</v>
+        <v>2978400</v>
       </c>
       <c r="G84" s="12" t="n">
         <v>0.1</v>
@@ -4275,33 +4275,40 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E85" s="15" t="n">
-        <v>0</v>
+        <v>5.2</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0.0039</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2908400</v>
+        <v>2922400</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J85" s="9" t="n"/>
-      <c r="K85" s="9" t="n"/>
+        <v>0.63</v>
+      </c>
+      <c r="H85" t="n">
+        <v>61.57</v>
+      </c>
+      <c r="I85" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>5.026</v>
+      </c>
+      <c r="K85" s="9" t="n">
+        <v>5.053</v>
+      </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
     </row>
@@ -4313,40 +4320,33 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E86" s="10" t="n">
-        <v>0.0062</v>
+        <v>0.225</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2877300</v>
+        <v>2908400</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H86" t="n">
-        <v>62.28</v>
-      </c>
-      <c r="I86" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J86" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="K86" s="9" t="n">
-        <v>0.746</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="n"/>
+      <c r="K86" s="9" t="n"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
     </row>
@@ -4358,28 +4358,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>5.21</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>0.0058</v>
+        <v>0.0062</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2820800</v>
+        <v>2877300</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.61</v>
+        <v>1.05</v>
       </c>
       <c r="H87" t="n">
-        <v>62.02</v>
+        <v>62.28</v>
       </c>
       <c r="I87" s="17" t="inlineStr">
         <is>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>5.027</v>
+        <v>0.77</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>5.053</v>
+        <v>0.746</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4418,7 +4418,7 @@
         <v>0.0014</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2814600</v>
+        <v>2817500</v>
       </c>
       <c r="G88" s="12" t="n">
         <v>0.39</v>
@@ -4508,7 +4508,7 @@
         <v>0</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2780200</v>
+        <v>2783200</v>
       </c>
       <c r="G90" s="12" t="n">
         <v>0.6</v>
@@ -4553,7 +4553,7 @@
         <v>0.05019999999999999</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2725000</v>
+        <v>2730000</v>
       </c>
       <c r="G91" s="12" t="n">
         <v>1.4</v>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>0.0133</v>
+        <v>0.0166</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>2705900</v>
+        <v>2706300</v>
       </c>
       <c r="G93" s="12" t="n">
         <v>0.93</v>
       </c>
       <c r="H93" t="n">
-        <v>55.7</v>
+        <v>56.48</v>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>2.985</v>
+        <v>2.986</v>
       </c>
       <c r="K93" s="9" t="n">
         <v>3.037</v>
@@ -4778,7 +4778,7 @@
         <v>0.0182</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>2557600</v>
+        <v>2558800</v>
       </c>
       <c r="G96" s="12" t="n">
         <v>0.16</v>
@@ -4950,19 +4950,19 @@
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="E100" s="15" t="n">
-        <v>0</v>
+        <v>1.46</v>
+      </c>
+      <c r="E100" s="16" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>2397600</v>
+        <v>2405500</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="H100" t="n">
-        <v>50.96</v>
+        <v>47.58</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>1.468</v>
+        <v>1.467</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>1.47</v>
+        <v>1.469</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5076,28 +5076,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E103" s="10" t="n">
-        <v>0.0496</v>
+        <v>1.84</v>
+      </c>
+      <c r="E103" s="16" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>2292800</v>
+        <v>2305800</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>1.48</v>
+        <v>0.52</v>
       </c>
       <c r="H103" t="n">
-        <v>48.87</v>
+        <v>32.95</v>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>1.266</v>
+        <v>1.917</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>1.322</v>
+        <v>2.042</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5121,28 +5121,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="E104" s="16" t="n">
-        <v>-0.0108</v>
+        <v>1.27</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>0.0496</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>2282800</v>
+        <v>2292800</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.52</v>
+        <v>1.48</v>
       </c>
       <c r="H104" t="n">
-        <v>32.95</v>
+        <v>48.87</v>
       </c>
       <c r="I104" s="13" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>1.917</v>
+        <v>1.266</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>2.042</v>
+        <v>1.322</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5406,7 +5406,7 @@
         <v>0.012</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>2102700</v>
+        <v>2113000</v>
       </c>
       <c r="G110" s="12" t="n">
         <v>0.68</v>
@@ -5451,7 +5451,7 @@
         <v>0.0095</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>2056400</v>
+        <v>2056500</v>
       </c>
       <c r="G111" s="12" t="n">
         <v>0.24</v>
@@ -5490,19 +5490,19 @@
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.74</v>
+        <v>0.745</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>0.0207</v>
+        <v>0.0276</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>2026000</v>
+        <v>2027300</v>
       </c>
       <c r="G112" s="12" t="n">
         <v>0.37</v>
       </c>
       <c r="H112" t="n">
-        <v>36.9</v>
+        <v>38.7</v>
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>-0.0013</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>2017600</v>
+        <v>2018100</v>
       </c>
       <c r="G114" s="12" t="n">
         <v>0.17</v>
@@ -5811,7 +5811,7 @@
         <v>0.0387</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1950800</v>
+        <v>1952400</v>
       </c>
       <c r="G119" s="12" t="n">
         <v>0.25</v>
@@ -5856,7 +5856,7 @@
         <v>0.0464</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1904200</v>
+        <v>1907800</v>
       </c>
       <c r="G120" s="12" t="n">
         <v>0.47</v>
@@ -5946,7 +5946,7 @@
         <v>-0.0013</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1834700</v>
+        <v>1835500</v>
       </c>
       <c r="G122" s="12" t="n">
         <v>0.2</v>
@@ -5991,7 +5991,7 @@
         <v>0</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1798000</v>
+        <v>1803000</v>
       </c>
       <c r="G123" s="12" t="n">
         <v>0.17</v>
@@ -6216,7 +6216,7 @@
         <v>0.0152</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1621100</v>
+        <v>1623400</v>
       </c>
       <c r="G128" s="12" t="n">
         <v>0.17</v>
@@ -6381,39 +6381,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E132" s="16" t="n">
-        <v>-0.0196</v>
+        <v>5.44</v>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1478800</v>
+        <v>1484400</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.18</v>
+        <v>0.58</v>
       </c>
       <c r="H132" t="n">
-        <v>61.37</v>
-      </c>
-      <c r="I132" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.62</v>
+      </c>
+      <c r="I132" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.955</v>
+        <v>5.266</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.802</v>
+        <v>5.296</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6426,39 +6426,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="E133" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E133" s="16" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1477200</v>
+        <v>1478800</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.58</v>
+        <v>0.18</v>
       </c>
       <c r="H133" t="n">
-        <v>56.62</v>
-      </c>
-      <c r="I133" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.37</v>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>5.266</v>
+        <v>0.955</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>5.296</v>
+        <v>0.802</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -7105,7 +7105,7 @@
         <v>-0.0025</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>1293100</v>
+        <v>1295000</v>
       </c>
       <c r="G148" s="12" t="n">
         <v>0.33</v>
@@ -7144,19 +7144,19 @@
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="E149" s="10" t="n">
-        <v>0.0049</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>1247300</v>
+        <v>1248900</v>
       </c>
       <c r="G149" s="12" t="n">
         <v>0.42</v>
       </c>
       <c r="H149" t="n">
-        <v>45.23</v>
+        <v>47.52</v>
       </c>
       <c r="I149" s="13" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>2.052</v>
+        <v>2.053</v>
       </c>
       <c r="K149" s="9" t="n">
         <v>2.09</v>
@@ -7270,28 +7270,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="E152" s="10" t="n">
-        <v>0.0389</v>
+        <v>3.32</v>
+      </c>
+      <c r="E152" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>1179500</v>
+        <v>1180300</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.78</v>
+        <v>0.55</v>
       </c>
       <c r="H152" t="n">
-        <v>76.06999999999999</v>
+        <v>68.72</v>
       </c>
       <c r="I152" s="17" t="inlineStr">
         <is>
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>2.34</v>
+        <v>3.101</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>2.101</v>
+        <v>2.677</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7315,39 +7315,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E153" s="15" t="n">
-        <v>0</v>
+        <v>2.67</v>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>0.0389</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>1178300</v>
+        <v>1179800</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>1.24</v>
+        <v>0.78</v>
       </c>
       <c r="H153" t="n">
-        <v>45.51</v>
-      </c>
-      <c r="I153" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.06999999999999</v>
+      </c>
+      <c r="I153" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>0.261</v>
+        <v>2.34</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>0.265</v>
+        <v>2.101</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7360,39 +7360,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>3.32</v>
+        <v>0.26</v>
       </c>
       <c r="E154" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>1177200</v>
+        <v>1178300</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.55</v>
+        <v>1.24</v>
       </c>
       <c r="H154" t="n">
-        <v>68.72</v>
-      </c>
-      <c r="I154" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.51</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>3.101</v>
+        <v>0.261</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>2.677</v>
+        <v>0.265</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7405,28 +7405,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E155" s="16" t="n">
-        <v>-0.023</v>
+        <v>1.82</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>1146400</v>
+        <v>1155100</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="H155" t="n">
-        <v>24.47</v>
+        <v>28.11</v>
       </c>
       <c r="I155" s="13" t="inlineStr">
         <is>
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>1.837</v>
+        <v>1.918</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>1.94</v>
+        <v>2.041</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7459,19 +7459,19 @@
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E156" s="10" t="n">
-        <v>0.0053</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E156" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>1144400</v>
+        <v>1146700</v>
       </c>
       <c r="G156" s="12" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="H156" t="n">
-        <v>35.8</v>
+        <v>33.44</v>
       </c>
       <c r="I156" s="13" t="inlineStr">
         <is>
@@ -7495,39 +7495,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E157" s="10" t="n">
-        <v>0.012</v>
+        <v>1.7</v>
+      </c>
+      <c r="E157" s="16" t="n">
+        <v>-0.023</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>1127900</v>
+        <v>1146400</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.63</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H157" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="I157" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.47</v>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>0.86</v>
+        <v>1.837</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>0.931</v>
+        <v>1.94</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7540,28 +7540,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="E158" s="10" t="n">
-        <v>0.0194</v>
+        <v>0.012</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>1107200</v>
+        <v>1132300</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.17</v>
+        <v>0.63</v>
       </c>
       <c r="H158" t="n">
-        <v>69.86</v>
+        <v>37.3</v>
       </c>
       <c r="I158" s="17" t="inlineStr">
         <is>
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>0.719</v>
+        <v>0.86</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>0.647</v>
+        <v>0.931</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7585,28 +7585,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>11</v>
+        <v>0.79</v>
       </c>
       <c r="E159" s="10" t="n">
-        <v>0.0223</v>
+        <v>0.0194</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>1093100</v>
+        <v>1107200</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.34</v>
+        <v>0.17</v>
       </c>
       <c r="H159" t="n">
-        <v>79.18000000000001</v>
+        <v>69.86</v>
       </c>
       <c r="I159" s="17" t="inlineStr">
         <is>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>9.935</v>
+        <v>0.719</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>9.358000000000001</v>
+        <v>0.647</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7630,39 +7630,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>6.11</v>
+        <v>10.98</v>
       </c>
       <c r="E160" s="10" t="n">
-        <v>0.015</v>
+        <v>0.0204</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>1089000</v>
+        <v>1094800</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.08</v>
+        <v>0.34</v>
       </c>
       <c r="H160" t="n">
-        <v>41.27</v>
-      </c>
-      <c r="I160" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.98999999999999</v>
+      </c>
+      <c r="I160" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>6.211</v>
+        <v>9.933</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>6.43</v>
+        <v>9.358000000000001</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7675,39 +7675,39 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>7.98</v>
+        <v>6.11</v>
       </c>
       <c r="E161" s="10" t="n">
-        <v>0.0101</v>
+        <v>0.015</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1034400</v>
+        <v>1089000</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.29</v>
+        <v>0.08</v>
       </c>
       <c r="H161" t="n">
-        <v>55.99</v>
-      </c>
-      <c r="I161" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.27</v>
+      </c>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>7.889</v>
+        <v>6.211</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>7.837</v>
+        <v>6.43</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7720,39 +7720,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>1.14</v>
+        <v>7.98</v>
       </c>
       <c r="E162" s="10" t="n">
-        <v>0.027</v>
+        <v>0.0101</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>1029400</v>
+        <v>1047900</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.16</v>
+        <v>0.29</v>
       </c>
       <c r="H162" t="n">
-        <v>47.85</v>
-      </c>
-      <c r="I162" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.99</v>
+      </c>
+      <c r="I162" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>1.151</v>
+        <v>7.889</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>1.161</v>
+        <v>7.837</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7765,28 +7765,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>IFCAMSC</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E163" s="16" t="n">
-        <v>-0.0244</v>
+        <v>1.14</v>
+      </c>
+      <c r="E163" s="10" t="n">
+        <v>0.027</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>1022500</v>
+        <v>1029400</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>1.93</v>
+        <v>0.16</v>
       </c>
       <c r="H163" t="n">
-        <v>42.22</v>
+        <v>47.85</v>
       </c>
       <c r="I163" s="13" t="inlineStr">
         <is>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>0.204</v>
+        <v>1.151</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>0.215</v>
+        <v>1.161</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7810,28 +7810,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>IFCAMSC</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="E164" s="10" t="n">
-        <v>0.003</v>
+        <v>0.2</v>
+      </c>
+      <c r="E164" s="16" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>1020700</v>
+        <v>1022500</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.17</v>
+        <v>1.93</v>
       </c>
       <c r="H164" t="n">
-        <v>33.28</v>
+        <v>42.22</v>
       </c>
       <c r="I164" s="13" t="inlineStr">
         <is>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>3.516</v>
+        <v>0.204</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>3.675</v>
+        <v>0.215</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7855,28 +7855,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E165" s="16" t="n">
-        <v>-0.0054</v>
+        <v>3.37</v>
+      </c>
+      <c r="E165" s="10" t="n">
+        <v>0.003</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>926000</v>
+        <v>1022100</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="H165" t="n">
-        <v>47.63</v>
+        <v>33.28</v>
       </c>
       <c r="I165" s="13" t="inlineStr">
         <is>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>0.927</v>
+        <v>3.516</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.675</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7900,39 +7900,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E166" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.92</v>
+      </c>
+      <c r="E166" s="16" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>920500</v>
+        <v>926700</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="H166" t="n">
-        <v>57.53</v>
-      </c>
-      <c r="I166" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.4</v>
+      </c>
+      <c r="I166" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>0.629</v>
+        <v>0.926</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>0.595</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7945,28 +7945,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>4.01</v>
+        <v>0.645</v>
       </c>
       <c r="E167" s="10" t="n">
-        <v>0.005</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>899600</v>
+        <v>920500</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="H167" t="n">
-        <v>62.23</v>
+        <v>57.53</v>
       </c>
       <c r="I167" s="17" t="inlineStr">
         <is>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>3.837</v>
+        <v>0.629</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>3.519</v>
+        <v>0.595</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -7990,39 +7990,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E168" s="16" t="n">
-        <v>-0.0068</v>
+        <v>4.01</v>
+      </c>
+      <c r="E168" s="10" t="n">
+        <v>0.005</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>890100</v>
+        <v>899600</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="H168" t="n">
-        <v>29.67</v>
-      </c>
-      <c r="I168" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.23</v>
+      </c>
+      <c r="I168" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>1.521</v>
+        <v>3.837</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>1.637</v>
+        <v>3.519</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8035,39 +8035,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="E169" s="16" t="n">
-        <v>-0.0161</v>
+        <v>-0.0068</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>859600</v>
+        <v>890100</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="H169" t="n">
-        <v>73.12</v>
-      </c>
-      <c r="I169" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.67</v>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>1.034</v>
+        <v>1.521</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>0.798</v>
+        <v>1.637</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8080,39 +8080,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="E170" s="10" t="n">
-        <v>0.0216</v>
+        <v>1.22</v>
+      </c>
+      <c r="E170" s="16" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>848800</v>
+        <v>859600</v>
       </c>
       <c r="G170" s="12" t="n">
         <v>0.12</v>
       </c>
       <c r="H170" t="n">
-        <v>41.18</v>
-      </c>
-      <c r="I170" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.12</v>
+      </c>
+      <c r="I170" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>1.94</v>
+        <v>1.034</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>1.962</v>
+        <v>0.798</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8125,28 +8125,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="E171" s="15" t="n">
-        <v>0</v>
+        <v>1.89</v>
+      </c>
+      <c r="E171" s="10" t="n">
+        <v>0.0216</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>837100</v>
+        <v>848800</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="H171" t="n">
-        <v>35.75</v>
+        <v>41.18</v>
       </c>
       <c r="I171" s="13" t="inlineStr">
         <is>
@@ -8154,10 +8154,10 @@
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>3.212</v>
+        <v>1.94</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>3.415</v>
+        <v>1.962</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8170,39 +8170,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>WELLCAL</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>1.13</v>
+        <v>3.12</v>
       </c>
       <c r="E172" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>806100</v>
+        <v>837100</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2.7</v>
+        <v>0.21</v>
       </c>
       <c r="H172" t="n">
-        <v>57.43</v>
-      </c>
-      <c r="I172" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.75</v>
+      </c>
+      <c r="I172" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>1.119</v>
+        <v>3.212</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>1.114</v>
+        <v>3.415</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8215,28 +8215,28 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>WELLCAL</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="E173" s="16" t="n">
-        <v>-0.0044</v>
+        <v>1.13</v>
+      </c>
+      <c r="E173" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>802400</v>
+        <v>806100</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.32</v>
+        <v>2.7</v>
       </c>
       <c r="H173" t="n">
-        <v>59.95</v>
+        <v>57.43</v>
       </c>
       <c r="I173" s="17" t="inlineStr">
         <is>
@@ -8244,10 +8244,10 @@
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>8.742000000000001</v>
+        <v>1.119</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>8.651</v>
+        <v>1.114</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8260,39 +8260,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E174" s="10" t="n">
-        <v>0.006999999999999999</v>
+        <v>9.08</v>
+      </c>
+      <c r="E174" s="16" t="n">
+        <v>-0.0044</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>786900</v>
+        <v>802400</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="H174" t="n">
-        <v>48.19</v>
-      </c>
-      <c r="I174" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.95</v>
+      </c>
+      <c r="I174" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>4.332</v>
+        <v>8.742000000000001</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>4.373</v>
+        <v>8.651</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8305,39 +8305,39 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E175" s="15" t="n">
-        <v>0</v>
+        <v>4.3</v>
+      </c>
+      <c r="E175" s="10" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>777100</v>
+        <v>786900</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.53</v>
+        <v>0.31</v>
       </c>
       <c r="H175" t="n">
-        <v>60.43</v>
-      </c>
-      <c r="I175" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.19</v>
+      </c>
+      <c r="I175" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>0.482</v>
+        <v>4.332</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>0.475</v>
+        <v>4.373</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8350,28 +8350,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>1.16</v>
+        <v>0.505</v>
       </c>
       <c r="E176" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>764400</v>
+        <v>777100</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
       <c r="H176" t="n">
-        <v>60.29</v>
+        <v>60.43</v>
       </c>
       <c r="I176" s="17" t="inlineStr">
         <is>
@@ -8379,10 +8379,10 @@
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>1.111</v>
+        <v>0.482</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>1.077</v>
+        <v>0.475</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8395,28 +8395,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E177" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>1.16</v>
+      </c>
+      <c r="E177" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>756000</v>
+        <v>764400</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="H177" t="n">
-        <v>88.41</v>
+        <v>60.29</v>
       </c>
       <c r="I177" s="17" t="inlineStr">
         <is>
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.111</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>0.535</v>
+        <v>1.077</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8440,39 +8440,39 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E178" s="16" t="n">
-        <v>-0.0139</v>
+        <v>0.64</v>
+      </c>
+      <c r="E178" s="10" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>755400</v>
+        <v>756000</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.82</v>
+        <v>0.65</v>
       </c>
       <c r="H178" t="n">
-        <v>39.37</v>
-      </c>
-      <c r="I178" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>88.41</v>
+      </c>
+      <c r="I178" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>2.259</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>2.324</v>
+        <v>0.535</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8485,39 +8485,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>0.955</v>
+        <v>2.13</v>
       </c>
       <c r="E179" s="16" t="n">
-        <v>-0.0205</v>
+        <v>-0.0139</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>749600</v>
+        <v>755400</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>0.41</v>
+        <v>0.82</v>
       </c>
       <c r="H179" t="n">
-        <v>58.42</v>
-      </c>
-      <c r="I179" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.37</v>
+      </c>
+      <c r="I179" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>0.921</v>
+        <v>2.259</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>0.838</v>
+        <v>2.324</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8530,28 +8530,28 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D180" s="9" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="E180" s="10" t="n">
-        <v>0.0123</v>
+        <v>0.955</v>
+      </c>
+      <c r="E180" s="16" t="n">
+        <v>-0.0205</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>733600</v>
+        <v>749600</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>0.18</v>
+        <v>0.41</v>
       </c>
       <c r="H180" t="n">
-        <v>44.73</v>
+        <v>58.42</v>
       </c>
       <c r="I180" s="17" t="inlineStr">
         <is>
@@ -8559,10 +8559,10 @@
         </is>
       </c>
       <c r="J180" s="9" t="n">
-        <v>6.606</v>
+        <v>0.921</v>
       </c>
       <c r="K180" s="9" t="n">
-        <v>6.87</v>
+        <v>0.838</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="14" t="inlineStr"/>
@@ -8575,39 +8575,39 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D181" s="9" t="n">
-        <v>1.37</v>
+        <v>6.58</v>
       </c>
       <c r="E181" s="10" t="n">
-        <v>0.0224</v>
+        <v>0.0123</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>725100</v>
+        <v>733600</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>0.26</v>
+        <v>0.18</v>
       </c>
       <c r="H181" t="n">
-        <v>55.19</v>
-      </c>
-      <c r="I181" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.73</v>
+      </c>
+      <c r="I181" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J181" s="9" t="n">
-        <v>1.354</v>
+        <v>6.606</v>
       </c>
       <c r="K181" s="9" t="n">
-        <v>1.211</v>
+        <v>6.87</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="14" t="inlineStr"/>
@@ -8620,39 +8620,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D182" s="9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E182" s="16" t="n">
-        <v>-0.0368</v>
+        <v>1.37</v>
+      </c>
+      <c r="E182" s="10" t="n">
+        <v>0.0224</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>701800</v>
+        <v>725100</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="H182" t="n">
-        <v>68.75</v>
-      </c>
-      <c r="I182" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.19</v>
+      </c>
+      <c r="I182" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J182" s="9" t="n">
-        <v>1.142</v>
+        <v>1.354</v>
       </c>
       <c r="K182" s="9" t="n">
-        <v>1.13</v>
+        <v>1.211</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="14" t="inlineStr"/>
@@ -8665,28 +8665,28 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D183" s="9" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E183" s="15" t="n">
-        <v>0</v>
+        <v>1.31</v>
+      </c>
+      <c r="E183" s="16" t="n">
+        <v>-0.0368</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>701200</v>
+        <v>701800</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>0.53</v>
+        <v>0.24</v>
       </c>
       <c r="H183" t="n">
-        <v>64.66</v>
+        <v>68.75</v>
       </c>
       <c r="I183" s="17" t="inlineStr">
         <is>
@@ -8694,10 +8694,10 @@
         </is>
       </c>
       <c r="J183" s="9" t="n">
-        <v>0.641</v>
+        <v>1.142</v>
       </c>
       <c r="K183" s="9" t="n">
-        <v>0.61</v>
+        <v>1.13</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="14" t="inlineStr"/>
@@ -8710,39 +8710,39 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D184" s="9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="E184" s="10" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.675</v>
+      </c>
+      <c r="E184" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>693900</v>
+        <v>701200</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>0.24</v>
+        <v>0.53</v>
       </c>
       <c r="H184" t="n">
-        <v>28.11</v>
-      </c>
-      <c r="I184" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.66</v>
+      </c>
+      <c r="I184" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J184" s="9" t="n">
-        <v>1.918</v>
+        <v>0.641</v>
       </c>
       <c r="K184" s="9" t="n">
-        <v>2.041</v>
+        <v>0.61</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="14" t="inlineStr"/>
@@ -8860,7 +8860,7 @@
         <v>-0.0058</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>660100</v>
+        <v>662300</v>
       </c>
       <c r="G187" s="12" t="n">
         <v>0.15</v>
@@ -8950,7 +8950,7 @@
         <v>-0.004699999999999999</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>644400</v>
+        <v>645600</v>
       </c>
       <c r="G189" s="12" t="n">
         <v>0.12</v>
@@ -8995,7 +8995,7 @@
         <v>0.005500000000000001</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>627600</v>
+        <v>628800</v>
       </c>
       <c r="G190" s="12" t="n">
         <v>0.29</v>
@@ -9430,28 +9430,28 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>THETA</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D200" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E200" s="16" t="n">
-        <v>-0.0236</v>
+        <v>1.55</v>
+      </c>
+      <c r="E200" s="10" t="n">
+        <v>0.0131</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>510200</v>
+        <v>516100</v>
       </c>
       <c r="G200" s="12" t="n">
-        <v>0.45</v>
+        <v>0.12</v>
       </c>
       <c r="H200" t="n">
-        <v>43.59</v>
+        <v>44.1</v>
       </c>
       <c r="I200" s="13" t="inlineStr">
         <is>
@@ -9459,10 +9459,10 @@
         </is>
       </c>
       <c r="J200" s="9" t="n">
-        <v>0.642</v>
+        <v>1.564</v>
       </c>
       <c r="K200" s="9" t="n">
-        <v>0.662</v>
+        <v>1.629</v>
       </c>
       <c r="L200" t="inlineStr"/>
       <c r="M200" s="14" t="inlineStr"/>
@@ -9490,7 +9490,7 @@
         <v>-0.0066</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>509500</v>
+        <v>514500</v>
       </c>
       <c r="G201" s="12" t="n">
         <v>0.14</v>
@@ -9520,28 +9520,28 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>THETA</t>
         </is>
       </c>
       <c r="D202" s="9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E202" s="10" t="n">
-        <v>0.0131</v>
+        <v>0.62</v>
+      </c>
+      <c r="E202" s="16" t="n">
+        <v>-0.0236</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>503000</v>
+        <v>510200</v>
       </c>
       <c r="G202" s="12" t="n">
-        <v>0.12</v>
+        <v>0.45</v>
       </c>
       <c r="H202" t="n">
-        <v>44.1</v>
+        <v>43.59</v>
       </c>
       <c r="I202" s="13" t="inlineStr">
         <is>
@@ -9549,16 +9549,61 @@
         </is>
       </c>
       <c r="J202" s="9" t="n">
-        <v>1.564</v>
+        <v>0.642</v>
       </c>
       <c r="K202" s="9" t="n">
-        <v>1.629</v>
+        <v>0.662</v>
       </c>
       <c r="L202" t="inlineStr"/>
       <c r="M202" s="14" t="inlineStr"/>
     </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>IHH</t>
+        </is>
+      </c>
+      <c r="D203" s="9" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="E203" s="10" t="n">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="F203" s="11" t="n">
+        <v>507700</v>
+      </c>
+      <c r="G203" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H203" t="n">
+        <v>47.17</v>
+      </c>
+      <c r="I203" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J203" s="9" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="K203" s="9" t="n">
+        <v>8.028</v>
+      </c>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M202"/>
+  <autoFilter ref="A1:M203"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-06/bursa-report-2026-10-06.xlsx
+++ b/docs/downloads/2026-10-06/bursa-report-2026-10-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-06" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-06'!$A$1:$M$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-06'!$A$1:$M$206</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M203"/>
+  <dimension ref="A1:M206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.047</v>
+        <v>-0.03759999999999999</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>2851400</v>
+        <v>3060000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>70.33</v>
+        <v>71.64</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>2.564</v>
+        <v>2.567</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1.951</v>
+        <v>1.952</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，但RSI达70.33已近超买，现价3.04远高于50日均线1.951，偏离较大。</t>
+          <t>SAR转多，但RSI达71.64已超买，现价3.07远高于50日均线1.952，偏离较大，信号可靠性偏弱。</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>0.4615</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>647420300</v>
+        <v>663296500</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="H3" t="n">
         <v>23.04</v>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>65201900</v>
+        <v>66113400</v>
       </c>
       <c r="G4" s="12" t="n"/>
       <c r="I4" s="13" t="inlineStr">
@@ -706,10 +706,10 @@
         <v>-0.0156</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>39163800</v>
+        <v>39647500</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="H5" t="n">
         <v>73.81</v>
@@ -751,10 +751,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>23200400</v>
+        <v>23235100</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>4.06</v>
+        <v>4.07</v>
       </c>
       <c r="H6" t="n">
         <v>83.98999999999999</v>
@@ -790,19 +790,19 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.82</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>-0.018</v>
+        <v>-0.024</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>18101200</v>
+        <v>18283200</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="H7" t="n">
-        <v>64.78</v>
+        <v>62.8</v>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.779</v>
+        <v>0.778</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>0.773</v>
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.155</v>
+        <v>0.15</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.06059999999999999</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>17388400</v>
+        <v>17539800</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="H8" t="n">
-        <v>48.89</v>
+        <v>46.53</v>
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>0</v>
+        <v>0.05</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0.1111</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>16554200</v>
+        <v>16593200</v>
       </c>
       <c r="G10" s="12" t="n">
         <v>0.84</v>
       </c>
       <c r="H10" t="n">
-        <v>30.46</v>
+        <v>39.19</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.054</v>
+        <v>0.055</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0.07199999999999999</v>
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.5</v>
+        <v>0.495</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>-0.009899999999999999</v>
+        <v>-0.0198</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>15885800</v>
+        <v>16004200</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>0.6</v>
       </c>
       <c r="H12" t="n">
-        <v>58.53</v>
+        <v>56.48</v>
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.481</v>
+        <v>0.48</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0.475</v>
@@ -1051,28 +1051,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>ASTEEL</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.83</v>
+        <v>0.115</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.0184</v>
+        <v>0.2105</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>14772700</v>
+        <v>15572000</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.2</v>
+        <v>10.36</v>
       </c>
       <c r="H13" t="n">
-        <v>65.73999999999999</v>
+        <v>66.62</v>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.755</v>
+        <v>0.093</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.704</v>
+        <v>0.083</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1096,39 +1096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0143</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KEYASIC</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>-0.07690000000000001</v>
+        <v>0.835</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0.0245</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>14680400</v>
+        <v>14984000</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1.7</v>
+        <v>1.21</v>
       </c>
       <c r="H14" t="n">
-        <v>47.86</v>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.29000000000001</v>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.063</v>
+        <v>0.755</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.058</v>
+        <v>0.704</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1141,39 +1141,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>0143</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ASTEEL</t>
+          <t>KEYASIC</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0.2105</v>
+        <v>0.065</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>13021800</v>
+        <v>14680800</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>8.66</v>
+        <v>1.7</v>
       </c>
       <c r="H15" t="n">
-        <v>66.62</v>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.68</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.093</v>
+        <v>0.063</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.083</v>
+        <v>0.058</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1186,39 +1186,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>-0.0313</v>
+        <v>0.805</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0.0255</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>12905500</v>
+        <v>13058500</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.7</v>
+        <v>0.27</v>
       </c>
       <c r="H16" t="n">
-        <v>62.83</v>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.2</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.749</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.505</v>
+        <v>0.696</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1231,39 +1231,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0.0191</v>
+        <v>0.625</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>-0.0234</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>12196700</v>
+        <v>13039300</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.26</v>
+        <v>0.71</v>
       </c>
       <c r="H17" t="n">
-        <v>64.45</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.88</v>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.748</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.696</v>
+        <v>0.505</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1276,31 +1276,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.005</v>
+        <v>0.305</v>
       </c>
       <c r="E18" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>11868100</v>
-      </c>
-      <c r="G18" s="12" t="n"/>
+        <v>12213600</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H18" t="n">
+        <v>53.3</v>
+      </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>0.294</v>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
     </row>
@@ -1312,28 +1321,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>0</v>
+        <v>0.175</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0.0294</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>11728600</v>
+        <v>11931300</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.6</v>
+        <v>0.18</v>
       </c>
       <c r="H19" t="n">
-        <v>53.3</v>
+        <v>60.35</v>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
@@ -1341,10 +1350,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.303</v>
+        <v>0.162</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.294</v>
+        <v>0.127</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1357,40 +1366,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.38</v>
+        <v>0.005</v>
       </c>
       <c r="E20" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>11624400</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="H20" t="n">
-        <v>70.89</v>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="K20" s="9" t="n">
-        <v>0.221</v>
-      </c>
+        <v>11868100</v>
+      </c>
+      <c r="G20" s="12" t="n"/>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n"/>
+      <c r="K20" s="9" t="n"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
     </row>
@@ -1402,39 +1402,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0.0294</v>
+        <v>0.375</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>11235100</v>
+        <v>11640400</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.17</v>
+        <v>0.27</v>
       </c>
       <c r="H21" t="n">
-        <v>60.35</v>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.56999999999999</v>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.162</v>
+        <v>0.347</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.127</v>
+        <v>0.221</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1462,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>10950500</v>
+        <v>10951500</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>0.37</v>
@@ -1537,28 +1537,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>9914500</v>
+        <v>9918200</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.71</v>
+        <v>0.53</v>
       </c>
       <c r="H24" t="n">
-        <v>53.15</v>
+        <v>46.41</v>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.775</v>
+        <v>0.868</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.775</v>
+        <v>0.87</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1582,39 +1582,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0209</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AIMFLEX</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.115</v>
+        <v>0.78</v>
       </c>
       <c r="E25" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>9890700</v>
+        <v>9916800</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1.44</v>
+        <v>0.71</v>
       </c>
       <c r="H25" t="n">
-        <v>45.95</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.15</v>
+      </c>
+      <c r="I25" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.118</v>
+        <v>0.775</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.123</v>
+        <v>0.775</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1627,28 +1627,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0065</t>
+          <t>0209</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EFORCE</t>
+          <t>AIMFLEX</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>-0.0294</v>
+        <v>0.115</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>9647200</v>
+        <v>9890700</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="H26" t="n">
-        <v>40.5</v>
+        <v>45.95</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.195</v>
+        <v>0.118</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.177</v>
+        <v>0.123</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1672,39 +1672,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0065</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>EFORCE</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0.0833</v>
+        <v>0.17</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>9597200</v>
+        <v>9677500</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>2.76</v>
+        <v>1.25</v>
       </c>
       <c r="H27" t="n">
-        <v>70.23</v>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.86</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.456</v>
+        <v>0.196</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.444</v>
+        <v>0.177</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1717,39 +1717,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>0</v>
+        <v>0.445</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0.023</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>9494800</v>
+        <v>9602900</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.62</v>
+        <v>0.46</v>
       </c>
       <c r="H28" t="n">
-        <v>50.21</v>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.08</v>
+      </c>
+      <c r="I28" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.398</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.338</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1762,28 +1762,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.445</v>
+        <v>0.52</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>0.023</v>
+        <v>0.0833</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>9488200</v>
+        <v>9598400</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.45</v>
+        <v>2.76</v>
       </c>
       <c r="H29" t="n">
-        <v>67.08</v>
+        <v>70.23</v>
       </c>
       <c r="I29" s="17" t="inlineStr">
         <is>
@@ -1791,10 +1791,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.398</v>
+        <v>0.456</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.338</v>
+        <v>0.444</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1816,19 +1816,19 @@
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.6</v>
+        <v>0.605</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>0.0619</v>
+        <v>0.0708</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>9423800</v>
+        <v>9517400</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H30" t="n">
-        <v>70.69</v>
+        <v>71.39</v>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.532</v>
+        <v>0.533</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>0.484</v>
@@ -1852,39 +1852,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>9389400</v>
+        <v>9499300</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="H31" t="n">
-        <v>46.41</v>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.21</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.868</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.87</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1912,10 +1912,10 @@
         <v>-0.005500000000000001</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>8803500</v>
+        <v>9099800</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="H32" t="n">
         <v>59.29</v>
@@ -1942,39 +1942,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>0.0141</v>
+        <v>0.065</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7997700</v>
+        <v>8500400</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H33" t="n">
-        <v>57.56</v>
-      </c>
-      <c r="I33" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.073</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.673</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1987,28 +1987,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.41</v>
+        <v>0.72</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>0.025</v>
+        <v>0.0141</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>7929000</v>
+        <v>8140800</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="H34" t="n">
-        <v>70.7</v>
+        <v>57.56</v>
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.383</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.374</v>
+        <v>0.673</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2032,39 +2032,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DATAPRP</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>-0.07690000000000001</v>
+        <v>0.41</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0.025</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>7840400</v>
+        <v>7968700</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.99</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>35.73</v>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.7</v>
+      </c>
+      <c r="I35" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.383</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.374</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2092,7 +2092,7 @@
         <v>0.007800000000000001</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>7839000</v>
+        <v>7878900</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>0.65</v>
@@ -2131,19 +2131,19 @@
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>-0.0167</v>
+        <v>-0.025</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>7800700</v>
+        <v>7831500</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="H37" t="n">
-        <v>75.17</v>
+        <v>73.78</v>
       </c>
       <c r="I37" s="17" t="inlineStr">
         <is>
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.959</v>
+        <v>0.958</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.83</v>
+        <v>0.829</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2182,10 +2182,10 @@
         <v>0.0541</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>7583900</v>
+        <v>7618800</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>6.13</v>
+        <v>6.16</v>
       </c>
       <c r="H38" t="n">
         <v>68.65000000000001</v>
@@ -2266,19 +2266,19 @@
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.79</v>
+        <v>0.785</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>0.197</v>
+        <v>0.1894</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>7056900</v>
+        <v>7143000</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="H40" t="n">
-        <v>81.09999999999999</v>
+        <v>80.89</v>
       </c>
       <c r="I40" s="17" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.556</v>
+        <v>0.555</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>0.443</v>
@@ -2302,39 +2302,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E41" s="16" t="n">
-        <v>-0.0357</v>
+        <v>5.02</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0.006</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>6893900</v>
+        <v>6980000</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.44</v>
+        <v>0.27</v>
       </c>
       <c r="H41" t="n">
-        <v>59.98</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.05</v>
+      </c>
+      <c r="I41" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.51</v>
+        <v>4.888</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.428</v>
+        <v>4.612</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2356,19 +2356,19 @@
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.635</v>
+        <v>0.64</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>0.114</v>
+        <v>0.1228</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>6864700</v>
+        <v>6924500</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="H42" t="n">
-        <v>86.90000000000001</v>
+        <v>87.14</v>
       </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.466</v>
+        <v>0.467</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>0.428</v>
@@ -2392,28 +2392,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ITRONIC</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>0</v>
+        <v>0.535</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>-0.0446</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>6792000</v>
+        <v>6896900</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>8.01</v>
+        <v>0.44</v>
       </c>
       <c r="H43" t="n">
-        <v>46.66</v>
+        <v>58.84</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.031</v>
+        <v>0.509</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.031</v>
+        <v>0.428</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2437,39 +2437,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>9393</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>ITRONIC</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>0.006</v>
+        <v>0.03</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>6702400</v>
+        <v>6792000</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.26</v>
+        <v>8.01</v>
       </c>
       <c r="H44" t="n">
-        <v>62.05</v>
-      </c>
-      <c r="I44" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.66</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>4.888</v>
+        <v>0.031</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>4.612</v>
+        <v>0.031</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2482,39 +2482,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>0</v>
+        <v>0.195</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>-0.0488</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>6352200</v>
+        <v>6376700</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>2.7</v>
+        <v>0.27</v>
       </c>
       <c r="H45" t="n">
-        <v>49.23</v>
-      </c>
-      <c r="I45" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.26</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.295</v>
+        <v>0.196</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.296</v>
+        <v>0.182</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2527,39 +2527,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.295</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>6056100</v>
+        <v>6352200</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.43</v>
+        <v>2.7</v>
       </c>
       <c r="H46" t="n">
-        <v>49.78</v>
-      </c>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.23</v>
+      </c>
+      <c r="I46" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>5.661</v>
+        <v>0.295</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>5.276</v>
+        <v>0.296</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2572,39 +2572,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E47" s="15" t="n">
-        <v>0</v>
+        <v>5.59</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>5702500</v>
+        <v>6120200</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.73</v>
+        <v>0.43</v>
       </c>
       <c r="H47" t="n">
-        <v>66</v>
-      </c>
-      <c r="I47" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.78</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.342</v>
+        <v>5.661</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.321</v>
+        <v>5.276</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2617,39 +2617,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="E48" s="16" t="n">
-        <v>-0.0127</v>
+        <v>-0.039</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>5662600</v>
+        <v>5764500</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.51</v>
+        <v>0.67</v>
       </c>
       <c r="H48" t="n">
-        <v>34.79</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.28</v>
+      </c>
+      <c r="I48" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.404</v>
+        <v>0.345</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.411</v>
+        <v>0.316</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2662,40 +2662,33 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>EVOCOM</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>-0.026</v>
+        <v>0.11</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>5657400</v>
+        <v>5737700</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="H49" t="n">
-        <v>68.29000000000001</v>
-      </c>
-      <c r="I49" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J49" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="K49" s="9" t="n">
-        <v>0.317</v>
-      </c>
+        <v>0.26</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="n"/>
+      <c r="K49" s="9" t="n"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
     </row>
@@ -2707,33 +2700,40 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EVOCOM</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.115</v>
+        <v>10.02</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>0.0455</v>
+        <v>0.002</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>5576700</v>
+        <v>5714500</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.25</v>
+        <v>0.49</v>
+      </c>
+      <c r="H50" t="n">
+        <v>41.51</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J50" s="9" t="n"/>
-      <c r="K50" s="9" t="n"/>
+      <c r="J50" s="9" t="n">
+        <v>10.095</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>10.249</v>
+      </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
     </row>
@@ -2745,39 +2745,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="E51" s="16" t="n">
-        <v>-0.0488</v>
+        <v>0.365</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>5340200</v>
+        <v>5708600</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.23</v>
+        <v>0.73</v>
       </c>
       <c r="H51" t="n">
-        <v>51.26</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66</v>
+      </c>
+      <c r="I51" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.196</v>
+        <v>0.342</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.182</v>
+        <v>0.321</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2790,28 +2790,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>0.004</v>
+        <v>0.39</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>5314000</v>
+        <v>5683500</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.45</v>
+        <v>0.51</v>
       </c>
       <c r="H52" t="n">
-        <v>43.15</v>
+        <v>34.79</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>10.097</v>
+        <v>0.404</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>10.249</v>
+        <v>0.411</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2835,39 +2835,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0.0101</v>
+        <v>2.86</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>-0.0138</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>5261600</v>
+        <v>5506000</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.77</v>
+        <v>0.58</v>
       </c>
       <c r="H53" t="n">
-        <v>28.67</v>
-      </c>
-      <c r="I53" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.6</v>
+      </c>
+      <c r="I53" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.536</v>
+        <v>2.745</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.577</v>
+        <v>2.568</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2880,39 +2880,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>0.0721</v>
+        <v>0.72</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>5221000</v>
+        <v>5276700</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>1.56</v>
+        <v>0.54</v>
       </c>
       <c r="H54" t="n">
-        <v>53.99</v>
-      </c>
-      <c r="I54" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.04000000000001</v>
+      </c>
+      <c r="I54" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>5.617</v>
+        <v>0.657</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>5.74</v>
+        <v>0.595</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2925,39 +2925,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>-0.0034</v>
+        <v>5.79</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0.0702</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>5137300</v>
+        <v>5276700</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.54</v>
+        <v>1.57</v>
       </c>
       <c r="H55" t="n">
-        <v>60.43</v>
-      </c>
-      <c r="I55" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.78</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>2.748</v>
+        <v>5.616</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>2.569</v>
+        <v>5.74</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2970,28 +2970,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>2.08</v>
+        <v>0.505</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>0.0246</v>
+        <v>0.0202</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>5111900</v>
+        <v>5270800</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.27</v>
+        <v>0.77</v>
       </c>
       <c r="H56" t="n">
-        <v>47.66</v>
+        <v>31.63</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>2.099</v>
+        <v>0.537</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>2.075</v>
+        <v>0.577</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3015,39 +3015,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>-0.0274</v>
+        <v>2.07</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0.0197</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>5019000</v>
+        <v>5204500</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.51</v>
+        <v>0.27</v>
       </c>
       <c r="H57" t="n">
-        <v>63.57</v>
-      </c>
-      <c r="I57" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.25</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.656</v>
+        <v>2.098</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.595</v>
+        <v>2.075</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3060,39 +3060,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0258</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AGMO</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0.0339</v>
+        <v>1.08</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>4696500</v>
+        <v>5169300</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>10.91</v>
+        <v>0.45</v>
       </c>
       <c r="H58" t="n">
-        <v>61.78</v>
-      </c>
-      <c r="I58" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.09</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.278</v>
+        <v>1.069</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.305</v>
+        <v>1.03</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3105,39 +3105,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OWG</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.205</v>
+        <v>2.51</v>
       </c>
       <c r="E59" s="10" t="n">
-        <v>0.025</v>
+        <v>0.008</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>4692500</v>
+        <v>4756000</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>19.76</v>
+        <v>0.32</v>
       </c>
       <c r="H59" t="n">
-        <v>66.73</v>
-      </c>
-      <c r="I59" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.67</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.184</v>
+        <v>2.458</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.188</v>
+        <v>2.333</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3150,39 +3150,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>OWG</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>2.51</v>
+        <v>0.205</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>0.008</v>
+        <v>0.025</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>4571900</v>
+        <v>4706600</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.31</v>
+        <v>19.82</v>
       </c>
       <c r="H60" t="n">
-        <v>59.67</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.73</v>
+      </c>
+      <c r="I60" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>2.458</v>
+        <v>0.184</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>2.333</v>
+        <v>0.188</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3195,39 +3195,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0258</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>AGMO</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E61" s="15" t="n">
-        <v>0</v>
+        <v>0.305</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>0.0339</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>4553900</v>
+        <v>4696500</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>10.91</v>
       </c>
       <c r="H61" t="n">
-        <v>38.36</v>
-      </c>
-      <c r="I61" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.78</v>
+      </c>
+      <c r="I61" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>1.689</v>
+        <v>0.278</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>1.805</v>
+        <v>0.305</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3240,28 +3240,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E62" s="15" t="n">
-        <v>0</v>
+        <v>1.65</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>4481300</v>
+        <v>4555100</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.39</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>53.09</v>
+        <v>40.09</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>1.069</v>
+        <v>1.69</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>1.03</v>
+        <v>1.806</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3285,39 +3285,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2.67</v>
+        <v>2.17</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>0.0191</v>
+        <v>0.0046</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>4330100</v>
+        <v>4455600</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>1.2</v>
+        <v>0.31</v>
       </c>
       <c r="H63" t="n">
-        <v>66.43000000000001</v>
-      </c>
-      <c r="I63" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.81</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>2.568</v>
+        <v>2.256</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>2.23</v>
+        <v>2.217</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3330,28 +3330,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E64" s="15" t="n">
-        <v>0</v>
+        <v>0.33</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>-0.0149</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>4263200</v>
+        <v>4361200</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>1.21</v>
+        <v>0.82</v>
       </c>
       <c r="H64" t="n">
-        <v>52.53</v>
+        <v>53.31</v>
       </c>
       <c r="I64" s="17" t="inlineStr">
         <is>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.153</v>
+        <v>0.322</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.151</v>
+        <v>0.338</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3375,39 +3375,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>0.0039</v>
+        <v>0.0153</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>4148300</v>
+        <v>4345400</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.24</v>
+        <v>1.21</v>
       </c>
       <c r="H65" t="n">
-        <v>52.43</v>
-      </c>
-      <c r="I65" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.83</v>
+      </c>
+      <c r="I65" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>2.569</v>
+        <v>2.567</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>2.476</v>
+        <v>2.23</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3420,39 +3420,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.155</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>4110700</v>
+        <v>4263200</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.28</v>
+        <v>1.21</v>
       </c>
       <c r="H66" t="n">
-        <v>43.72</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.53</v>
+      </c>
+      <c r="I66" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>2.257</v>
+        <v>0.153</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>2.217</v>
+        <v>0.151</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3465,39 +3465,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E67" s="16" t="n">
-        <v>-0.0385</v>
+        <v>2.57</v>
+      </c>
+      <c r="E67" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>4007800</v>
+        <v>4182500</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.91</v>
+        <v>0.24</v>
       </c>
       <c r="H67" t="n">
-        <v>55.34</v>
-      </c>
-      <c r="I67" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.6</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.121</v>
+        <v>2.568</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.125</v>
+        <v>2.476</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3510,39 +3510,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>0.0113</v>
+        <v>4.66</v>
+      </c>
+      <c r="E68" s="16" t="n">
+        <v>-0.0106</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3704400</v>
+        <v>4008000</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="H68" t="n">
-        <v>62.16</v>
-      </c>
-      <c r="I68" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.91</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>2.583</v>
+        <v>4.773</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>2.56</v>
+        <v>4.915</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3555,39 +3555,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>4.67</v>
+        <v>0.125</v>
       </c>
       <c r="E69" s="16" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0385</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3693100</v>
+        <v>4007800</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.22</v>
+        <v>0.91</v>
       </c>
       <c r="H69" t="n">
-        <v>33.68</v>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.34</v>
+      </c>
+      <c r="I69" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>4.774</v>
+        <v>0.121</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>4.915</v>
+        <v>0.125</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3600,28 +3600,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0290</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PANDA</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.185</v>
+        <v>2.68</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>0.0571</v>
+        <v>0.0113</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>3681500</v>
+        <v>3807500</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>29.31</v>
+        <v>0.71</v>
       </c>
       <c r="H70" t="n">
-        <v>55.91</v>
+        <v>62.16</v>
       </c>
       <c r="I70" s="17" t="inlineStr">
         <is>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.179</v>
+        <v>2.583</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.186</v>
+        <v>2.56</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3654,19 +3654,19 @@
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>0.0202</v>
+        <v>0.0173</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>3648200</v>
+        <v>3695200</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="H71" t="n">
-        <v>53.01</v>
+        <v>52.81</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>3.586</v>
+        <v>3.585</v>
       </c>
       <c r="K71" s="9" t="n">
         <v>2.624</v>
@@ -3690,28 +3690,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E72" s="16" t="n">
-        <v>-0.0171</v>
+        <v>0.65</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>3575400</v>
+        <v>3693000</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.3</v>
+        <v>1.02</v>
       </c>
       <c r="H72" t="n">
-        <v>74.43000000000001</v>
+        <v>59.69</v>
       </c>
       <c r="I72" s="17" t="inlineStr">
         <is>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>1.055</v>
+        <v>0.614</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.895</v>
+        <v>0.609</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0290</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>PANDA</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.485</v>
+        <v>0.185</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>0.0104</v>
+        <v>0.0571</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>3427800</v>
+        <v>3681500</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.09</v>
+        <v>29.31</v>
       </c>
       <c r="H73" t="n">
-        <v>26.07</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.91</v>
+      </c>
+      <c r="I73" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.573</v>
+        <v>0.179</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.78</v>
+        <v>0.186</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3780,28 +3780,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>2.88</v>
+        <v>1.15</v>
       </c>
       <c r="E74" s="16" t="n">
-        <v>-0.0137</v>
+        <v>-0.0171</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>3389600</v>
+        <v>3595900</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="H74" t="n">
-        <v>74.61</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="I74" s="17" t="inlineStr">
         <is>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>2.535</v>
+        <v>1.055</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>2.078</v>
+        <v>0.895</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3825,39 +3825,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E75" s="15" t="n">
-        <v>0</v>
+        <v>0.49</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>3388200</v>
+        <v>3538200</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.64</v>
+        <v>0.09</v>
       </c>
       <c r="H75" t="n">
-        <v>56.19</v>
-      </c>
-      <c r="I75" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.31</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.323</v>
+        <v>0.574</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.338</v>
+        <v>0.78</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3870,28 +3870,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>2.88</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>3369100</v>
+        <v>3460700</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.93</v>
+        <v>1.08</v>
       </c>
       <c r="H76" t="n">
-        <v>58.69</v>
+        <v>74.61</v>
       </c>
       <c r="I76" s="17" t="inlineStr">
         <is>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.614</v>
+        <v>2.535</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.609</v>
+        <v>2.078</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3930,10 +3930,10 @@
         <v>0</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>3304600</v>
+        <v>3435200</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="H77" t="n">
         <v>65.7</v>
@@ -3960,39 +3960,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>0.0089</v>
+        <v>0.0196</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>3185500</v>
+        <v>3233000</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>1.48</v>
+        <v>0.46</v>
       </c>
       <c r="H78" t="n">
-        <v>51.22</v>
-      </c>
-      <c r="I78" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.36</v>
+      </c>
+      <c r="I78" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.712</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.637</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4005,39 +4005,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>EWICAP</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E79" s="16" t="n">
-        <v>-0.07139999999999999</v>
+        <v>0.7</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0.03700000000000001</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>3130900</v>
+        <v>3193700</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="H79" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="I79" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.34</v>
+      </c>
+      <c r="I79" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.168</v>
+        <v>0.613</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.181</v>
+        <v>0.518</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4050,39 +4050,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>3058000</v>
+        <v>3189500</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="H80" t="n">
-        <v>75.34</v>
-      </c>
-      <c r="I80" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.46</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.613</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.518</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4095,39 +4095,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>EWICAP</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.445</v>
+        <v>0.13</v>
       </c>
       <c r="E81" s="16" t="n">
-        <v>-0.022</v>
+        <v>-0.07139999999999999</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>3033600</v>
+        <v>3130900</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.48</v>
+        <v>1.39</v>
       </c>
       <c r="H81" t="n">
-        <v>59.49</v>
-      </c>
-      <c r="I81" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>19.9</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.415</v>
+        <v>0.168</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.408</v>
+        <v>0.181</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4140,28 +4140,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.78</v>
+        <v>5.21</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>0.0196</v>
+        <v>0.0058</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>3014200</v>
+        <v>3111600</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.43</v>
+        <v>0.67</v>
       </c>
       <c r="H82" t="n">
-        <v>68.36</v>
+        <v>62.02</v>
       </c>
       <c r="I82" s="17" t="inlineStr">
         <is>
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.712</v>
+        <v>5.027</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.637</v>
+        <v>5.053</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4185,28 +4185,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.29</v>
+        <v>0.445</v>
       </c>
       <c r="E83" s="16" t="n">
-        <v>-0.0169</v>
+        <v>-0.022</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2983700</v>
+        <v>3043600</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.29</v>
+        <v>0.49</v>
       </c>
       <c r="H83" t="n">
-        <v>55.52</v>
+        <v>59.49</v>
       </c>
       <c r="I83" s="17" t="inlineStr">
         <is>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.273</v>
+        <v>0.415</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.306</v>
+        <v>0.408</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4230,39 +4230,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.23</v>
+        <v>7.21</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>0.0222</v>
+        <v>0.0042</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2978400</v>
+        <v>3040800</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.1</v>
+        <v>0.42</v>
       </c>
       <c r="H84" t="n">
-        <v>31.25</v>
-      </c>
-      <c r="I84" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.37</v>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.258</v>
+        <v>7.493</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.311</v>
+        <v>7.768</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4275,28 +4275,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>0.0039</v>
+        <v>0.29</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2922400</v>
+        <v>2983700</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.63</v>
+        <v>0.29</v>
       </c>
       <c r="H85" t="n">
-        <v>61.57</v>
+        <v>55.52</v>
       </c>
       <c r="I85" s="17" t="inlineStr">
         <is>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>5.026</v>
+        <v>0.273</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>5.053</v>
+        <v>0.306</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4320,33 +4320,40 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E86" s="15" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2908400</v>
+        <v>2978400</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J86" s="9" t="n"/>
-      <c r="K86" s="9" t="n"/>
+        <v>0.1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="I86" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="K86" s="9" t="n">
+        <v>0.311</v>
+      </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
     </row>
@@ -4373,10 +4380,10 @@
         <v>0.0062</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2877300</v>
+        <v>2947400</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H87" t="n">
         <v>62.28</v>
@@ -4403,40 +4410,33 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>0.0014</v>
+        <v>0.225</v>
+      </c>
+      <c r="E88" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2817500</v>
+        <v>2908400</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="H88" t="n">
-        <v>31.09</v>
+        <v>0.08</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J88" s="9" t="n">
-        <v>7.491</v>
-      </c>
-      <c r="K88" s="9" t="n">
-        <v>7.767</v>
-      </c>
+      <c r="J88" s="9" t="n"/>
+      <c r="K88" s="9" t="n"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
     </row>
@@ -4448,39 +4448,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>0.0058</v>
+        <v>0.21</v>
+      </c>
+      <c r="E89" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2791000</v>
+        <v>2892200</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="H89" t="n">
-        <v>47.08</v>
-      </c>
-      <c r="I89" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.06</v>
+      </c>
+      <c r="I89" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>1.752</v>
+        <v>0.213</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>1.783</v>
+        <v>0.213</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4493,39 +4493,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E90" s="15" t="n">
-        <v>0</v>
+        <v>3.05</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2783200</v>
+        <v>2798900</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.6</v>
+        <v>0.96</v>
       </c>
       <c r="H90" t="n">
-        <v>47.06</v>
-      </c>
-      <c r="I90" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.7</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.213</v>
+        <v>2.985</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.213</v>
+        <v>3.037</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4538,39 +4538,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2.3</v>
+        <v>1.74</v>
       </c>
       <c r="E91" s="10" t="n">
-        <v>0.05019999999999999</v>
+        <v>0.0058</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2730000</v>
+        <v>2791000</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>1.4</v>
+        <v>0.55</v>
       </c>
       <c r="H91" t="n">
-        <v>70.15000000000001</v>
-      </c>
-      <c r="I91" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.08</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>2.041</v>
+        <v>1.752</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>1.93</v>
+        <v>1.783</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4583,28 +4583,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>CENSOF</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.925</v>
+        <v>0.235</v>
       </c>
       <c r="E92" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>2719200</v>
+        <v>2780200</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.54</v>
+        <v>2.7</v>
       </c>
       <c r="H92" t="n">
-        <v>62.72</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="I92" s="17" t="inlineStr">
         <is>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.9</v>
+        <v>0.213</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.858</v>
+        <v>0.203</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4628,39 +4628,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>0.0166</v>
+        <v>0.925</v>
+      </c>
+      <c r="E93" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>2706300</v>
+        <v>2769200</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.93</v>
+        <v>0.55</v>
       </c>
       <c r="H93" t="n">
-        <v>56.48</v>
-      </c>
-      <c r="I93" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.72</v>
+      </c>
+      <c r="I93" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>2.986</v>
+        <v>0.9</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>3.037</v>
+        <v>0.858</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4673,28 +4673,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.545</v>
+        <v>2.3</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>0.0583</v>
+        <v>0.05019999999999999</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>2619500</v>
+        <v>2750300</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>5.99</v>
+        <v>1.41</v>
       </c>
       <c r="H94" t="n">
-        <v>69.91</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="I94" s="17" t="inlineStr">
         <is>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.506</v>
+        <v>2.041</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.5</v>
+        <v>1.93</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4718,40 +4718,38 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FPGROUP</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.43</v>
+        <v>0.28</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>0.0238</v>
+        <v>0.0182</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>2599100</v>
+        <v>2749300</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>2.62</v>
+        <v>0.18</v>
       </c>
       <c r="H95" t="n">
-        <v>59.94</v>
-      </c>
-      <c r="I95" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>20.18</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="K95" s="9" t="n">
-        <v>0.417</v>
-      </c>
+        <v>0.296</v>
+      </c>
+      <c r="K95" s="9" t="n"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
     </row>
@@ -4763,38 +4761,40 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.28</v>
+        <v>0.545</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>0.0182</v>
+        <v>0.0583</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>2558800</v>
+        <v>2627000</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.16</v>
+        <v>6</v>
       </c>
       <c r="H96" t="n">
-        <v>20.18</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.91</v>
+      </c>
+      <c r="I96" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.296</v>
-      </c>
-      <c r="K96" s="9" t="n"/>
+        <v>0.506</v>
+      </c>
+      <c r="K96" s="9" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
     </row>
@@ -4806,39 +4806,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5277</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>FPGROUP</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E97" s="16" t="n">
-        <v>-0.0052</v>
+        <v>0.43</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0.0238</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>2523100</v>
+        <v>2601400</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.64</v>
+        <v>2.62</v>
       </c>
       <c r="H97" t="n">
-        <v>28.04</v>
-      </c>
-      <c r="I97" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.94</v>
+      </c>
+      <c r="I97" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>1.013</v>
+        <v>0.409</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>1.076</v>
+        <v>0.417</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4851,39 +4851,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.275</v>
+        <v>1.47</v>
       </c>
       <c r="E98" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>2509600</v>
+        <v>2598300</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>1.21</v>
+        <v>0.51</v>
       </c>
       <c r="H98" t="n">
-        <v>69.31</v>
-      </c>
-      <c r="I98" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.96</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.252</v>
+        <v>1.468</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.256</v>
+        <v>1.47</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4896,39 +4896,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CENSOF</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E99" s="16" t="n">
-        <v>-0.0213</v>
+        <v>0.75</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>2423000</v>
+        <v>2579100</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>2.35</v>
+        <v>0.47</v>
       </c>
       <c r="H99" t="n">
-        <v>64.68000000000001</v>
-      </c>
-      <c r="I99" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.41</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.212</v>
+        <v>0.769</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.203</v>
+        <v>0.827</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4941,28 +4941,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>1.46</v>
+        <v>0.96</v>
       </c>
       <c r="E100" s="16" t="n">
-        <v>-0.0068</v>
+        <v>-0.0052</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>2405500</v>
+        <v>2541300</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.48</v>
+        <v>0.64</v>
       </c>
       <c r="H100" t="n">
-        <v>47.58</v>
+        <v>28.04</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>1.467</v>
+        <v>1.013</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>1.469</v>
+        <v>1.076</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4986,28 +4986,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SKYWLD</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>0.039</v>
+        <v>0.555</v>
+      </c>
+      <c r="E101" s="16" t="n">
+        <v>-0.0348</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>2372100</v>
+        <v>2531400</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>4.01</v>
+        <v>0.45</v>
       </c>
       <c r="H101" t="n">
-        <v>57.1</v>
+        <v>32.39</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.39</v>
+        <v>0.605</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.397</v>
+        <v>0.649</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5031,39 +5031,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>0.0183</v>
+        <v>0.275</v>
+      </c>
+      <c r="E102" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>2328500</v>
+        <v>2509600</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.17</v>
+        <v>1.21</v>
       </c>
       <c r="H102" t="n">
-        <v>51.56</v>
-      </c>
-      <c r="I102" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.31</v>
+      </c>
+      <c r="I102" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>2.788</v>
+        <v>0.252</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>2.681</v>
+        <v>0.256</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5076,28 +5076,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>SKYWLD</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="E103" s="16" t="n">
-        <v>-0.0108</v>
+        <v>0.4</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>0.039</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>2305800</v>
+        <v>2408900</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.52</v>
+        <v>4.07</v>
       </c>
       <c r="H103" t="n">
-        <v>32.95</v>
+        <v>57.1</v>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>1.917</v>
+        <v>0.39</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>2.042</v>
+        <v>0.397</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5121,28 +5121,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>1.27</v>
+        <v>2.77</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>0.0496</v>
+        <v>0.0147</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>2292800</v>
+        <v>2391100</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1.48</v>
+        <v>0.18</v>
       </c>
       <c r="H104" t="n">
-        <v>48.87</v>
+        <v>50.65</v>
       </c>
       <c r="I104" s="13" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>1.266</v>
+        <v>2.787</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>1.322</v>
+        <v>2.681</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5166,39 +5166,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E105" s="16" t="n">
-        <v>-0.0182</v>
+        <v>0.455</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>0.0225</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>2249400</v>
+        <v>2384300</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.6</v>
+        <v>0.84</v>
       </c>
       <c r="H105" t="n">
-        <v>66.38</v>
-      </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.67</v>
+      </c>
+      <c r="I105" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.243</v>
+        <v>0.4</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.215</v>
+        <v>0.359</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5211,28 +5211,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.555</v>
+        <v>1.84</v>
       </c>
       <c r="E106" s="16" t="n">
-        <v>-0.0348</v>
+        <v>-0.0108</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>2213100</v>
+        <v>2354600</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="H106" t="n">
-        <v>32.39</v>
+        <v>32.95</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.605</v>
+        <v>1.917</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.649</v>
+        <v>2.042</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5256,39 +5256,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E107" s="10" t="n">
-        <v>0.0172</v>
+        <v>0.27</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>2147200</v>
+        <v>2349400</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.14</v>
+        <v>0.62</v>
       </c>
       <c r="H107" t="n">
-        <v>52.96</v>
-      </c>
-      <c r="I107" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>66.38</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.29</v>
+        <v>0.243</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.278</v>
+        <v>0.215</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5301,39 +5301,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.46</v>
+        <v>1.26</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>0.0337</v>
+        <v>0.0413</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>2134300</v>
+        <v>2339700</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.75</v>
+        <v>1.51</v>
       </c>
       <c r="H108" t="n">
-        <v>72.51000000000001</v>
-      </c>
-      <c r="I108" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.6</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.4</v>
+        <v>1.265</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.359</v>
+        <v>1.322</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5346,28 +5346,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.505</v>
+        <v>7.45</v>
       </c>
       <c r="E109" s="16" t="n">
-        <v>-0.0098</v>
+        <v>-0.0013</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>2118800</v>
+        <v>2286500</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.34</v>
+        <v>0.25</v>
       </c>
       <c r="H109" t="n">
-        <v>44.35</v>
+        <v>26.21</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.518</v>
+        <v>7.748</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.531</v>
+        <v>8.164999999999999</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5391,39 +5391,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.84</v>
+        <v>0.295</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>0.012</v>
+        <v>0.0172</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>2113000</v>
+        <v>2227600</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.68</v>
+        <v>0.14</v>
       </c>
       <c r="H110" t="n">
-        <v>60.28</v>
-      </c>
-      <c r="I110" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.96</v>
+      </c>
+      <c r="I110" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.29</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.746</v>
+        <v>0.278</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5436,39 +5436,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="E111" s="10" t="n">
-        <v>0.0095</v>
+        <v>1.17</v>
+      </c>
+      <c r="E111" s="16" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>2056500</v>
+        <v>2200700</v>
       </c>
       <c r="G111" s="12" t="n">
         <v>0.24</v>
       </c>
       <c r="H111" t="n">
-        <v>69.31</v>
-      </c>
-      <c r="I111" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.44</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>3.867</v>
+        <v>1.158</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>3.37</v>
+        <v>1.113</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5481,39 +5481,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.745</v>
+        <v>4.23</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>0.0276</v>
+        <v>0.0095</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>2027300</v>
+        <v>2193900</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.37</v>
+        <v>0.26</v>
       </c>
       <c r="H112" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="I112" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.31</v>
+      </c>
+      <c r="I112" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.768</v>
+        <v>3.867</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.827</v>
+        <v>3.37</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="E113" s="16" t="n">
-        <v>-0.0032</v>
+        <v>0.84</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>0.012</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>2023300</v>
+        <v>2132100</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.52</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H113" t="n">
-        <v>61.15</v>
-      </c>
-      <c r="I113" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.28</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>2.972</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>2.784</v>
+        <v>0.746</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5571,28 +5571,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>7.72</v>
+        <v>0.505</v>
       </c>
       <c r="E114" s="16" t="n">
-        <v>-0.0013</v>
+        <v>-0.0098</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>2018100</v>
+        <v>2128800</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.17</v>
+        <v>0.35</v>
       </c>
       <c r="H114" t="n">
-        <v>47.62</v>
+        <v>44.35</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>7.768</v>
+        <v>0.518</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>7.755</v>
+        <v>0.531</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5616,28 +5616,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>1.17</v>
+        <v>7.71</v>
       </c>
       <c r="E115" s="16" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0026</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1985300</v>
+        <v>2065200</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="H115" t="n">
-        <v>53.44</v>
+        <v>47.13</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>1.158</v>
+        <v>7.767</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>1.113</v>
+        <v>7.755</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5661,39 +5661,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.635</v>
+        <v>3.12</v>
       </c>
       <c r="E116" s="16" t="n">
-        <v>-0.0379</v>
+        <v>-0.0095</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1966800</v>
+        <v>2027400</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="H116" t="n">
-        <v>52.18</v>
-      </c>
-      <c r="I116" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.91</v>
+      </c>
+      <c r="I116" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.638</v>
+        <v>2.97</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.606</v>
+        <v>2.784</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5706,39 +5706,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>MALAKOF</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.615</v>
+        <v>0.79</v>
       </c>
       <c r="E117" s="10" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.0464</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1966400</v>
+        <v>1983100</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="H117" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="I117" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.32</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.612</v>
+        <v>0.792</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.596</v>
+        <v>0.806</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5751,28 +5751,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.865</v>
+        <v>0.635</v>
       </c>
       <c r="E118" s="16" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0379</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1953800</v>
+        <v>1966800</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H118" t="n">
-        <v>53.73</v>
+        <v>52.18</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.863</v>
+        <v>0.638</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.857</v>
+        <v>0.606</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5796,39 +5796,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>4.29</v>
+        <v>0.615</v>
       </c>
       <c r="E119" s="10" t="n">
-        <v>0.0387</v>
+        <v>0.008199999999999999</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1952400</v>
+        <v>1966400</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.25</v>
+        <v>0.65</v>
       </c>
       <c r="H119" t="n">
-        <v>44.83</v>
-      </c>
-      <c r="I119" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.38</v>
+      </c>
+      <c r="I119" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>4.412</v>
+        <v>0.612</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>4.478</v>
+        <v>0.596</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5841,28 +5841,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MALAKOF</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.79</v>
+        <v>4.3</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>0.0464</v>
+        <v>0.0412</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1907800</v>
+        <v>1959400</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.47</v>
+        <v>0.25</v>
       </c>
       <c r="H120" t="n">
-        <v>48.32</v>
+        <v>45.19</v>
       </c>
       <c r="I120" s="13" t="inlineStr">
         <is>
@@ -5870,10 +5870,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.792</v>
+        <v>4.413</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.806</v>
+        <v>4.478</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5886,39 +5886,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>0.0148</v>
+        <v>0.865</v>
+      </c>
+      <c r="E121" s="16" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1849600</v>
+        <v>1953800</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H121" t="n">
-        <v>78.03</v>
-      </c>
-      <c r="I121" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.73</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>1.186</v>
+        <v>0.863</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.971</v>
+        <v>0.857</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5931,39 +5931,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="E122" s="16" t="n">
-        <v>-0.0013</v>
+        <v>1.37</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>0.0148</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1835500</v>
+        <v>1874300</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.2</v>
+        <v>0.63</v>
       </c>
       <c r="H122" t="n">
-        <v>26.21</v>
-      </c>
-      <c r="I122" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.03</v>
+      </c>
+      <c r="I122" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>7.748</v>
+        <v>1.186</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>8.164999999999999</v>
+        <v>0.971</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5991,7 +5991,7 @@
         <v>0</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1803000</v>
+        <v>1833000</v>
       </c>
       <c r="G123" s="12" t="n">
         <v>0.17</v>
@@ -6021,28 +6021,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E124" s="10" t="n">
-        <v>0.02</v>
+        <v>13</v>
+      </c>
+      <c r="E124" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1767200</v>
+        <v>1814500</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="H124" t="n">
-        <v>49.14</v>
+        <v>41.6</v>
       </c>
       <c r="I124" s="17" t="inlineStr">
         <is>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.254</v>
+        <v>13.086</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.264</v>
+        <v>13.646</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6066,28 +6066,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E125" s="15" t="n">
-        <v>0</v>
+        <v>4.68</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>0.0174</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1753900</v>
+        <v>1808800</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.54</v>
+        <v>0.19</v>
       </c>
       <c r="H125" t="n">
-        <v>61.26</v>
+        <v>48.48</v>
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.46</v>
+        <v>4.71</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.417</v>
+        <v>4.618</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6111,39 +6111,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E126" s="16" t="n">
-        <v>-0.0172</v>
+        <v>0.255</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>0.02</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1660300</v>
+        <v>1774800</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.25</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H126" t="n">
-        <v>37.25</v>
-      </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.14</v>
+      </c>
+      <c r="I126" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.294</v>
+        <v>0.254</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.309</v>
+        <v>0.264</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>13</v>
+        <v>0.475</v>
       </c>
       <c r="E127" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1624600</v>
+        <v>1757100</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.19</v>
+        <v>0.54</v>
       </c>
       <c r="H127" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="I127" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.26</v>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>13.086</v>
+        <v>0.46</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>13.646</v>
+        <v>0.417</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6201,28 +6201,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="E128" s="10" t="n">
-        <v>0.0152</v>
+        <v>0.285</v>
+      </c>
+      <c r="E128" s="16" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1623400</v>
+        <v>1660300</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H128" t="n">
-        <v>47.6</v>
+        <v>37.25</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>4.709</v>
+        <v>0.294</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>4.618</v>
+        <v>0.309</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6246,28 +6246,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0396</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ADNEX</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.45</v>
+        <v>0.305</v>
       </c>
       <c r="E129" s="10" t="n">
-        <v>0.0345</v>
+        <v>0.0167</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1577200</v>
+        <v>1608900</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>3.45</v>
+        <v>0.25</v>
       </c>
       <c r="H129" t="n">
-        <v>63.94</v>
+        <v>71.64</v>
       </c>
       <c r="I129" s="17" t="inlineStr">
         <is>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.425</v>
+        <v>0.286</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.418</v>
+        <v>0.273</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6291,28 +6291,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0396</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>ADNEX</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E130" s="15" t="n">
-        <v>0</v>
+        <v>0.45</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1565100</v>
+        <v>1603600</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.24</v>
+        <v>3.5</v>
       </c>
       <c r="H130" t="n">
-        <v>68.88</v>
+        <v>63.94</v>
       </c>
       <c r="I130" s="17" t="inlineStr">
         <is>
@@ -6320,10 +6320,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.286</v>
+        <v>0.425</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.273</v>
+        <v>0.418</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6336,28 +6336,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E131" s="10" t="n">
-        <v>0.009899999999999999</v>
+        <v>1.23</v>
+      </c>
+      <c r="E131" s="16" t="n">
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1548700</v>
+        <v>1602900</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>2.54</v>
+        <v>0.27</v>
       </c>
       <c r="H131" t="n">
-        <v>62.9</v>
+        <v>43.69</v>
       </c>
       <c r="I131" s="17" t="inlineStr">
         <is>
@@ -6365,10 +6365,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.992</v>
+        <v>1.252</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.978</v>
+        <v>1.291</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6381,40 +6381,33 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="E132" s="15" t="n">
-        <v>0</v>
+        <v>0.305</v>
+      </c>
+      <c r="E132" s="16" t="n">
+        <v>-0.0317</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1484400</v>
+        <v>1581000</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="H132" t="n">
-        <v>56.62</v>
+        <v>0.15</v>
       </c>
       <c r="I132" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J132" s="9" t="n">
-        <v>5.266</v>
-      </c>
-      <c r="K132" s="9" t="n">
-        <v>5.296</v>
-      </c>
+      <c r="J132" s="9" t="n"/>
+      <c r="K132" s="9" t="n"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
     </row>
@@ -6426,39 +6419,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E133" s="16" t="n">
-        <v>-0.0196</v>
+        <v>5.44</v>
+      </c>
+      <c r="E133" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1478800</v>
+        <v>1551400</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.18</v>
+        <v>0.61</v>
       </c>
       <c r="H133" t="n">
-        <v>61.37</v>
-      </c>
-      <c r="I133" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.62</v>
+      </c>
+      <c r="I133" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.955</v>
+        <v>5.266</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.802</v>
+        <v>5.296</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6471,28 +6464,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E134" s="15" t="n">
-        <v>0</v>
+        <v>1.02</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1458300</v>
+        <v>1548700</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.24</v>
+        <v>2.54</v>
       </c>
       <c r="H134" t="n">
-        <v>68.36</v>
+        <v>62.9</v>
       </c>
       <c r="I134" s="17" t="inlineStr">
         <is>
@@ -6500,10 +6493,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.778</v>
+        <v>0.992</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.76</v>
+        <v>0.978</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6516,28 +6509,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>0.012</v>
+        <v>1.01</v>
+      </c>
+      <c r="E135" s="16" t="n">
+        <v>-0.0098</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1455400</v>
+        <v>1483800</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>1.25</v>
+        <v>0.18</v>
       </c>
       <c r="H135" t="n">
-        <v>43.2</v>
+        <v>63.04</v>
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
@@ -6545,10 +6538,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.425</v>
+        <v>0.956</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.444</v>
+        <v>0.803</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6561,28 +6554,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="E136" s="10" t="n">
-        <v>0.0031</v>
+        <v>0.8</v>
+      </c>
+      <c r="E136" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1451600</v>
+        <v>1482400</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.48</v>
+        <v>0.24</v>
       </c>
       <c r="H136" t="n">
-        <v>70.94</v>
+        <v>68.36</v>
       </c>
       <c r="I136" s="17" t="inlineStr">
         <is>
@@ -6590,10 +6583,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>2.905</v>
+        <v>0.778</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>2.76</v>
+        <v>0.76</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6606,33 +6599,40 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E137" s="16" t="n">
-        <v>-0.0317</v>
+        <v>3.27</v>
+      </c>
+      <c r="E137" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>1449400</v>
+        <v>1471100</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.13</v>
+        <v>0.49</v>
+      </c>
+      <c r="H137" t="n">
+        <v>70.67</v>
       </c>
       <c r="I137" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J137" s="9" t="n"/>
-      <c r="K137" s="9" t="n"/>
+      <c r="J137" s="9" t="n">
+        <v>2.904</v>
+      </c>
+      <c r="K137" s="9" t="n">
+        <v>2.76</v>
+      </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
     </row>
@@ -6644,28 +6644,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>1.21</v>
+        <v>0.415</v>
       </c>
       <c r="E138" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1442000</v>
+        <v>1466400</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.57</v>
+        <v>1.26</v>
       </c>
       <c r="H138" t="n">
-        <v>30.34</v>
+        <v>39.02</v>
       </c>
       <c r="I138" s="13" t="inlineStr">
         <is>
@@ -6673,10 +6673,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>1.322</v>
+        <v>0.425</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>1.316</v>
+        <v>0.444</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6689,39 +6689,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ECOFIRS</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>0.32</v>
+        <v>1.21</v>
       </c>
       <c r="E139" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>1417800</v>
+        <v>1444400</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="H139" t="n">
-        <v>41.35</v>
-      </c>
-      <c r="I139" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.34</v>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>0.331</v>
+        <v>1.322</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>0.34</v>
+        <v>1.316</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6734,39 +6734,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E140" s="15" t="n">
-        <v>0</v>
+        <v>1.37</v>
+      </c>
+      <c r="E140" s="16" t="n">
+        <v>-0.0072</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1411300</v>
+        <v>1430900</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="H140" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="I140" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.73</v>
+      </c>
+      <c r="I140" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>0.452</v>
+        <v>1.272</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>0.421</v>
+        <v>1.176</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6779,39 +6779,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>1.24</v>
+        <v>0.46</v>
       </c>
       <c r="E141" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>1408400</v>
+        <v>1421500</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="H141" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="I141" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.3</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>1.253</v>
+        <v>0.452</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>1.291</v>
+        <v>0.421</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6824,28 +6824,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>ECOFIRS</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.485</v>
+        <v>0.32</v>
       </c>
       <c r="E142" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1406900</v>
+        <v>1417800</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.72</v>
+        <v>0.63</v>
       </c>
       <c r="H142" t="n">
-        <v>61.65</v>
+        <v>41.35</v>
       </c>
       <c r="I142" s="17" t="inlineStr">
         <is>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.456</v>
+        <v>0.331</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.46</v>
+        <v>0.34</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6869,39 +6869,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0219</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.305</v>
+        <v>0.485</v>
       </c>
       <c r="E143" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1387200</v>
+        <v>1409800</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="H143" t="n">
-        <v>50.55</v>
-      </c>
-      <c r="I143" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.65</v>
+      </c>
+      <c r="I143" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.306</v>
+        <v>0.456</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>0.298</v>
+        <v>0.46</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6914,39 +6914,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0219</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>1.38</v>
+        <v>0.305</v>
       </c>
       <c r="E144" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1382500</v>
+        <v>1387200</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="H144" t="n">
-        <v>62.88</v>
-      </c>
-      <c r="I144" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.55</v>
+      </c>
+      <c r="I144" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>1.273</v>
+        <v>0.306</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>1.176</v>
+        <v>0.298</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6959,39 +6959,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E145" s="15" t="n">
-        <v>0</v>
+        <v>1.7</v>
+      </c>
+      <c r="E145" s="16" t="n">
+        <v>-0.023</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1359600</v>
+        <v>1373900</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.43</v>
+        <v>0.97</v>
       </c>
       <c r="H145" t="n">
-        <v>59.45</v>
-      </c>
-      <c r="I145" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.47</v>
+      </c>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>0.581</v>
+        <v>1.837</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>0.578</v>
+        <v>1.94</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7004,36 +7004,40 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.26</v>
+        <v>0.61</v>
       </c>
       <c r="E146" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1328200</v>
+        <v>1359600</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.11</v>
+        <v>0.43</v>
       </c>
       <c r="H146" t="n">
-        <v>25.13</v>
+        <v>59.45</v>
       </c>
       <c r="I146" s="17" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J146" s="9" t="n"/>
-      <c r="K146" s="9" t="n"/>
+      <c r="J146" s="9" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="K146" s="9" t="n">
+        <v>0.578</v>
+      </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
     </row>
@@ -7045,28 +7049,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0272</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>TTVHB</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E147" s="10" t="n">
-        <v>0.0196</v>
+        <v>7.84</v>
+      </c>
+      <c r="E147" s="16" t="n">
+        <v>-0.0051</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>1324800</v>
+        <v>1349000</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.46</v>
+        <v>0.34</v>
       </c>
       <c r="H147" t="n">
-        <v>55.44</v>
+        <v>72.38</v>
       </c>
       <c r="I147" s="17" t="inlineStr">
         <is>
@@ -7074,10 +7078,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>0.247</v>
+        <v>6.968</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>0.252</v>
+        <v>6.655</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7090,39 +7094,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="E148" s="16" t="n">
-        <v>-0.0025</v>
+        <v>2.04</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>0.0049</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>1295000</v>
+        <v>1346300</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.33</v>
+        <v>0.45</v>
       </c>
       <c r="H148" t="n">
-        <v>73</v>
-      </c>
-      <c r="I148" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.23</v>
+      </c>
+      <c r="I148" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>6.97</v>
+        <v>2.052</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>6.656</v>
+        <v>2.09</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7135,40 +7139,36 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="E149" s="10" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.26</v>
+      </c>
+      <c r="E149" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>1248900</v>
+        <v>1328200</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.42</v>
+        <v>0.11</v>
       </c>
       <c r="H149" t="n">
-        <v>47.52</v>
-      </c>
-      <c r="I149" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J149" s="9" t="n">
-        <v>2.053</v>
-      </c>
-      <c r="K149" s="9" t="n">
-        <v>2.09</v>
-      </c>
+        <v>25.13</v>
+      </c>
+      <c r="I149" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="n"/>
+      <c r="K149" s="9" t="n"/>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
     </row>
@@ -7180,28 +7180,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0272</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>TTVHB</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>1.12</v>
+        <v>0.255</v>
       </c>
       <c r="E150" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>1245800</v>
+        <v>1327300</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.26</v>
+        <v>0.46</v>
       </c>
       <c r="H150" t="n">
-        <v>76.33</v>
+        <v>53.38</v>
       </c>
       <c r="I150" s="17" t="inlineStr">
         <is>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>1.029</v>
+        <v>0.247</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>0.863</v>
+        <v>0.252</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7225,28 +7225,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0466</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SRKKAI</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E151" s="16" t="n">
-        <v>-0.0182</v>
+        <v>1.12</v>
+      </c>
+      <c r="E151" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>1194600</v>
+        <v>1258800</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>1.14</v>
+        <v>0.26</v>
       </c>
       <c r="H151" t="n">
-        <v>54.08</v>
+        <v>76.33</v>
       </c>
       <c r="I151" s="17" t="inlineStr">
         <is>
@@ -7254,10 +7254,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>0.526</v>
+        <v>1.029</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>0.533</v>
+        <v>0.863</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7270,28 +7270,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="E152" s="15" t="n">
-        <v>0</v>
+        <v>10.94</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>1180300</v>
+        <v>1253300</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.55</v>
+        <v>0.39</v>
       </c>
       <c r="H152" t="n">
-        <v>68.72</v>
+        <v>78.61</v>
       </c>
       <c r="I152" s="17" t="inlineStr">
         <is>
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>3.101</v>
+        <v>9.929</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>2.677</v>
+        <v>9.356999999999999</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7315,28 +7315,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>2.67</v>
+        <v>0.79</v>
       </c>
       <c r="E153" s="10" t="n">
-        <v>0.0389</v>
+        <v>0.0194</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>1179800</v>
+        <v>1250000</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.78</v>
+        <v>0.19</v>
       </c>
       <c r="H153" t="n">
-        <v>76.06999999999999</v>
+        <v>69.86</v>
       </c>
       <c r="I153" s="17" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>2.34</v>
+        <v>0.719</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>2.101</v>
+        <v>0.647</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7360,28 +7360,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E154" s="15" t="n">
-        <v>0</v>
+        <v>1.83</v>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>0.011</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>1178300</v>
+        <v>1217500</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>1.24</v>
+        <v>0.43</v>
       </c>
       <c r="H154" t="n">
-        <v>45.51</v>
+        <v>30.39</v>
       </c>
       <c r="I154" s="13" t="inlineStr">
         <is>
@@ -7389,10 +7389,10 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>0.261</v>
+        <v>1.919</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>0.265</v>
+        <v>2.041</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7405,39 +7405,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="E155" s="10" t="n">
-        <v>0.005500000000000001</v>
+        <v>3.31</v>
+      </c>
+      <c r="E155" s="16" t="n">
+        <v>-0.003</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>1155100</v>
+        <v>1217400</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H155" t="n">
-        <v>28.11</v>
-      </c>
-      <c r="I155" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.95999999999999</v>
+      </c>
+      <c r="I155" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>1.918</v>
+        <v>3.1</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>2.041</v>
+        <v>2.677</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7450,39 +7450,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0466</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>SRKKAI</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E156" s="15" t="n">
-        <v>0</v>
+        <v>0.54</v>
+      </c>
+      <c r="E156" s="16" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>1146700</v>
+        <v>1208000</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.16</v>
       </c>
       <c r="H156" t="n">
-        <v>33.44</v>
-      </c>
-      <c r="I156" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.08</v>
+      </c>
+      <c r="I156" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>0.975</v>
+        <v>0.526</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>1</v>
+        <v>0.533</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7495,39 +7495,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E157" s="16" t="n">
-        <v>-0.023</v>
+        <v>2.67</v>
+      </c>
+      <c r="E157" s="10" t="n">
+        <v>0.0389</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>1146400</v>
+        <v>1188200</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="H157" t="n">
-        <v>24.47</v>
-      </c>
-      <c r="I157" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.06999999999999</v>
+      </c>
+      <c r="I157" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>1.837</v>
+        <v>2.34</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>1.94</v>
+        <v>2.101</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7540,39 +7540,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E158" s="10" t="n">
-        <v>0.012</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E158" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>1132300</v>
+        <v>1180100</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H158" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="I158" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.44</v>
+      </c>
+      <c r="I158" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>0.86</v>
+        <v>0.975</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>0.931</v>
+        <v>1</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7585,39 +7585,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E159" s="10" t="n">
-        <v>0.0194</v>
+        <v>0.26</v>
+      </c>
+      <c r="E159" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>1107200</v>
+        <v>1178300</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.17</v>
+        <v>1.24</v>
       </c>
       <c r="H159" t="n">
-        <v>69.86</v>
-      </c>
-      <c r="I159" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.51</v>
+      </c>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>0.719</v>
+        <v>0.261</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>0.647</v>
+        <v>0.265</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7630,28 +7630,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>10.98</v>
+        <v>0.84</v>
       </c>
       <c r="E160" s="10" t="n">
-        <v>0.0204</v>
+        <v>0.012</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>1094800</v>
+        <v>1153600</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.34</v>
+        <v>0.65</v>
       </c>
       <c r="H160" t="n">
-        <v>78.98999999999999</v>
+        <v>37.3</v>
       </c>
       <c r="I160" s="17" t="inlineStr">
         <is>
@@ -7659,10 +7659,10 @@
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>9.933</v>
+        <v>0.86</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>9.358000000000001</v>
+        <v>0.931</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7690,10 +7690,10 @@
         <v>0.015</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>1089000</v>
+        <v>1153500</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H161" t="n">
         <v>41.27</v>
@@ -7729,19 +7729,19 @@
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>7.98</v>
+        <v>8</v>
       </c>
       <c r="E162" s="10" t="n">
-        <v>0.0101</v>
+        <v>0.0127</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>1047900</v>
+        <v>1146000</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="H162" t="n">
-        <v>55.99</v>
+        <v>56.89</v>
       </c>
       <c r="I162" s="17" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>7.889</v>
+        <v>7.891</v>
       </c>
       <c r="K162" s="9" t="n">
         <v>7.837</v>
@@ -7765,28 +7765,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>1.14</v>
+        <v>3.37</v>
       </c>
       <c r="E163" s="10" t="n">
-        <v>0.027</v>
+        <v>0.003</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>1029400</v>
+        <v>1085400</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="H163" t="n">
-        <v>47.85</v>
+        <v>33.28</v>
       </c>
       <c r="I163" s="13" t="inlineStr">
         <is>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>1.151</v>
+        <v>3.516</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>1.161</v>
+        <v>3.675</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7810,39 +7810,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>IFCAMSC</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>0.2</v>
+        <v>1.23</v>
       </c>
       <c r="E164" s="16" t="n">
-        <v>-0.0244</v>
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>1022500</v>
+        <v>1055400</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>1.93</v>
+        <v>0.14</v>
       </c>
       <c r="H164" t="n">
-        <v>42.22</v>
-      </c>
-      <c r="I164" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.43000000000001</v>
+      </c>
+      <c r="I164" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>0.204</v>
+        <v>1.035</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>0.215</v>
+        <v>0.798</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7855,28 +7855,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>3.37</v>
+        <v>1.14</v>
       </c>
       <c r="E165" s="10" t="n">
-        <v>0.003</v>
+        <v>0.027</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>1022100</v>
+        <v>1030400</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="H165" t="n">
-        <v>33.28</v>
+        <v>47.85</v>
       </c>
       <c r="I165" s="13" t="inlineStr">
         <is>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>3.516</v>
+        <v>1.151</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>3.675</v>
+        <v>1.161</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7900,28 +7900,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>IFCAMSC</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="E166" s="16" t="n">
-        <v>-0.0108</v>
+        <v>-0.0244</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>926700</v>
+        <v>1022500</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.4</v>
+        <v>1.93</v>
       </c>
       <c r="H166" t="n">
-        <v>45.4</v>
+        <v>42.22</v>
       </c>
       <c r="I166" s="13" t="inlineStr">
         <is>
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>0.926</v>
+        <v>0.204</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.215</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7945,39 +7945,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E167" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.925</v>
+      </c>
+      <c r="E167" s="16" t="n">
+        <v>-0.0054</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>920500</v>
+        <v>973100</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="H167" t="n">
-        <v>57.53</v>
-      </c>
-      <c r="I167" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.63</v>
+      </c>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>0.629</v>
+        <v>0.927</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>0.595</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -7990,28 +7990,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>4.01</v>
+        <v>0.645</v>
       </c>
       <c r="E168" s="10" t="n">
-        <v>0.005</v>
+        <v>0.0157</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>899600</v>
+        <v>973000</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.29</v>
+        <v>0.84</v>
       </c>
       <c r="H168" t="n">
-        <v>62.23</v>
+        <v>88.87</v>
       </c>
       <c r="I168" s="17" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>3.837</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>3.519</v>
+        <v>0.535</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8035,39 +8035,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E169" s="16" t="n">
-        <v>-0.0068</v>
+        <v>4.02</v>
+      </c>
+      <c r="E169" s="10" t="n">
+        <v>0.0075</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>890100</v>
+        <v>935200</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="H169" t="n">
-        <v>29.67</v>
-      </c>
-      <c r="I169" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.58</v>
+      </c>
+      <c r="I169" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>1.521</v>
+        <v>3.838</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>1.637</v>
+        <v>3.519</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8080,28 +8080,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E170" s="16" t="n">
-        <v>-0.0161</v>
+        <v>0.645</v>
+      </c>
+      <c r="E170" s="10" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>859600</v>
+        <v>920500</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="H170" t="n">
-        <v>73.12</v>
+        <v>57.53</v>
       </c>
       <c r="I170" s="17" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>1.034</v>
+        <v>0.629</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>0.798</v>
+        <v>0.595</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8125,28 +8125,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="E171" s="10" t="n">
-        <v>0.0216</v>
+        <v>1.47</v>
+      </c>
+      <c r="E171" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>848800</v>
+        <v>897300</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="H171" t="n">
-        <v>41.18</v>
+        <v>31.03</v>
       </c>
       <c r="I171" s="13" t="inlineStr">
         <is>
@@ -8154,10 +8154,10 @@
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>1.94</v>
+        <v>1.522</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>1.962</v>
+        <v>1.637</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8170,28 +8170,28 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="E172" s="15" t="n">
-        <v>0</v>
+        <v>1.89</v>
+      </c>
+      <c r="E172" s="10" t="n">
+        <v>0.0216</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>837100</v>
+        <v>867200</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="H172" t="n">
-        <v>35.75</v>
+        <v>41.18</v>
       </c>
       <c r="I172" s="13" t="inlineStr">
         <is>
@@ -8199,10 +8199,10 @@
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>3.212</v>
+        <v>1.94</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>3.415</v>
+        <v>1.962</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8215,39 +8215,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>WELLCAL</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>1.13</v>
+        <v>3.12</v>
       </c>
       <c r="E173" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>806100</v>
+        <v>848200</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>2.7</v>
+        <v>0.21</v>
       </c>
       <c r="H173" t="n">
-        <v>57.43</v>
-      </c>
-      <c r="I173" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.75</v>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>1.119</v>
+        <v>3.212</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>1.114</v>
+        <v>3.415</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8269,19 +8269,19 @@
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>9.08</v>
+        <v>9.02</v>
       </c>
       <c r="E174" s="16" t="n">
-        <v>-0.0044</v>
+        <v>-0.011</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>802400</v>
+        <v>834400</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H174" t="n">
-        <v>59.95</v>
+        <v>58.22</v>
       </c>
       <c r="I174" s="17" t="inlineStr">
         <is>
@@ -8289,10 +8289,10 @@
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>8.742000000000001</v>
+        <v>8.736000000000001</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>8.651</v>
+        <v>8.65</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8314,19 +8314,19 @@
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>4.3</v>
+        <v>4.32</v>
       </c>
       <c r="E175" s="10" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0117</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>786900</v>
+        <v>828400</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="H175" t="n">
-        <v>48.19</v>
+        <v>49.01</v>
       </c>
       <c r="I175" s="13" t="inlineStr">
         <is>
@@ -8334,10 +8334,10 @@
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>4.332</v>
+        <v>4.334</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>4.373</v>
+        <v>4.374</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8350,28 +8350,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E176" s="15" t="n">
-        <v>0</v>
+        <v>6.59</v>
+      </c>
+      <c r="E176" s="10" t="n">
+        <v>0.0138</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>777100</v>
+        <v>818200</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.53</v>
+        <v>0.21</v>
       </c>
       <c r="H176" t="n">
-        <v>60.43</v>
+        <v>45.48</v>
       </c>
       <c r="I176" s="17" t="inlineStr">
         <is>
@@ -8379,10 +8379,10 @@
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>0.482</v>
+        <v>6.607</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>0.475</v>
+        <v>6.871</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8395,28 +8395,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0325</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>1.16</v>
+        <v>0.505</v>
       </c>
       <c r="E177" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>764400</v>
+        <v>810200</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>0.49</v>
+        <v>0.55</v>
       </c>
       <c r="H177" t="n">
-        <v>60.29</v>
+        <v>60.43</v>
       </c>
       <c r="I177" s="17" t="inlineStr">
         <is>
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>1.111</v>
+        <v>0.482</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>1.077</v>
+        <v>0.475</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8440,28 +8440,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>WELLCAL</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E178" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>1.13</v>
+      </c>
+      <c r="E178" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>756000</v>
+        <v>806100</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.65</v>
+        <v>2.7</v>
       </c>
       <c r="H178" t="n">
-        <v>88.41</v>
+        <v>57.43</v>
       </c>
       <c r="I178" s="17" t="inlineStr">
         <is>
@@ -8469,10 +8469,10 @@
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.119</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>0.535</v>
+        <v>1.114</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8485,39 +8485,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>0325</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E179" s="16" t="n">
-        <v>-0.0139</v>
+        <v>1.16</v>
+      </c>
+      <c r="E179" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>755400</v>
+        <v>802800</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>0.82</v>
+        <v>0.52</v>
       </c>
       <c r="H179" t="n">
-        <v>39.37</v>
-      </c>
-      <c r="I179" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.29</v>
+      </c>
+      <c r="I179" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>2.259</v>
+        <v>1.111</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>2.324</v>
+        <v>1.077</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8530,39 +8530,39 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D180" s="9" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="E180" s="16" t="n">
-        <v>-0.0205</v>
+        <v>1.36</v>
+      </c>
+      <c r="E180" s="10" t="n">
+        <v>0.0149</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>749600</v>
+        <v>758000</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="H180" t="n">
-        <v>58.42</v>
-      </c>
-      <c r="I180" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.12</v>
+      </c>
+      <c r="I180" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J180" s="9" t="n">
-        <v>0.921</v>
+        <v>1.353</v>
       </c>
       <c r="K180" s="9" t="n">
-        <v>0.838</v>
+        <v>1.211</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="14" t="inlineStr"/>
@@ -8575,39 +8575,39 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D181" s="9" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="E181" s="10" t="n">
-        <v>0.0123</v>
+        <v>2.13</v>
+      </c>
+      <c r="E181" s="16" t="n">
+        <v>-0.0139</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>733600</v>
+        <v>757500</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>0.18</v>
+        <v>0.82</v>
       </c>
       <c r="H181" t="n">
-        <v>44.73</v>
-      </c>
-      <c r="I181" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.37</v>
+      </c>
+      <c r="I181" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J181" s="9" t="n">
-        <v>6.606</v>
+        <v>2.259</v>
       </c>
       <c r="K181" s="9" t="n">
-        <v>6.87</v>
+        <v>2.324</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="14" t="inlineStr"/>
@@ -8620,39 +8620,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D182" s="9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E182" s="10" t="n">
-        <v>0.0224</v>
+        <v>0.955</v>
+      </c>
+      <c r="E182" s="16" t="n">
+        <v>-0.0205</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>725100</v>
+        <v>753300</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>0.26</v>
+        <v>0.41</v>
       </c>
       <c r="H182" t="n">
-        <v>55.19</v>
-      </c>
-      <c r="I182" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.42</v>
+      </c>
+      <c r="I182" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J182" s="9" t="n">
-        <v>1.354</v>
+        <v>0.921</v>
       </c>
       <c r="K182" s="9" t="n">
-        <v>1.211</v>
+        <v>0.838</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="14" t="inlineStr"/>
@@ -8665,28 +8665,28 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1.31</v>
+        <v>6.86</v>
       </c>
       <c r="E183" s="16" t="n">
-        <v>-0.0368</v>
+        <v>-0.0058</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>701800</v>
+        <v>727100</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>0.24</v>
+        <v>0.16</v>
       </c>
       <c r="H183" t="n">
-        <v>68.75</v>
+        <v>55.95</v>
       </c>
       <c r="I183" s="17" t="inlineStr">
         <is>
@@ -8694,10 +8694,10 @@
         </is>
       </c>
       <c r="J183" s="9" t="n">
-        <v>1.142</v>
+        <v>6.779</v>
       </c>
       <c r="K183" s="9" t="n">
-        <v>1.13</v>
+        <v>6.847</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="14" t="inlineStr"/>
@@ -8710,39 +8710,39 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D184" s="9" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E184" s="15" t="n">
-        <v>0</v>
+        <v>4.28</v>
+      </c>
+      <c r="E184" s="16" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>701200</v>
+        <v>719600</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>0.53</v>
+        <v>0.14</v>
       </c>
       <c r="H184" t="n">
-        <v>64.66</v>
-      </c>
-      <c r="I184" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.03</v>
+      </c>
+      <c r="I184" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J184" s="9" t="n">
-        <v>0.641</v>
+        <v>4.546</v>
       </c>
       <c r="K184" s="9" t="n">
-        <v>0.61</v>
+        <v>4.888</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="14" t="inlineStr"/>
@@ -8755,28 +8755,28 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D185" s="9" t="n">
-        <v>0.63</v>
+        <v>0.675</v>
       </c>
       <c r="E185" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>680000</v>
+        <v>716600</v>
       </c>
       <c r="G185" s="12" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="H185" t="n">
-        <v>44.84</v>
+        <v>64.66</v>
       </c>
       <c r="I185" s="17" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         </is>
       </c>
       <c r="J185" s="9" t="n">
-        <v>0.634</v>
+        <v>0.641</v>
       </c>
       <c r="K185" s="9" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="14" t="inlineStr"/>
@@ -8800,39 +8800,39 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D186" s="9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E186" s="10" t="n">
-        <v>0.009300000000000001</v>
+        <v>1.31</v>
+      </c>
+      <c r="E186" s="16" t="n">
+        <v>-0.0368</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>674300</v>
+        <v>701800</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="H186" t="n">
-        <v>48</v>
-      </c>
-      <c r="I186" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.75</v>
+      </c>
+      <c r="I186" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J186" s="9" t="n">
-        <v>2.192</v>
+        <v>1.142</v>
       </c>
       <c r="K186" s="9" t="n">
-        <v>2.115</v>
+        <v>1.13</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" s="14" t="inlineStr"/>
@@ -8845,28 +8845,28 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D187" s="9" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="E187" s="16" t="n">
-        <v>-0.0058</v>
+        <v>0.63</v>
+      </c>
+      <c r="E187" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>662300</v>
+        <v>680000</v>
       </c>
       <c r="G187" s="12" t="n">
-        <v>0.15</v>
+        <v>0.51</v>
       </c>
       <c r="H187" t="n">
-        <v>55.95</v>
+        <v>44.84</v>
       </c>
       <c r="I187" s="17" t="inlineStr">
         <is>
@@ -8874,10 +8874,10 @@
         </is>
       </c>
       <c r="J187" s="9" t="n">
-        <v>6.779</v>
+        <v>0.634</v>
       </c>
       <c r="K187" s="9" t="n">
-        <v>6.847</v>
+        <v>0.63</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" s="14" t="inlineStr"/>
@@ -8890,39 +8890,39 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D188" s="9" t="n">
-        <v>0.765</v>
+        <v>2.16</v>
       </c>
       <c r="E188" s="10" t="n">
-        <v>0.02</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>655300</v>
+        <v>677000</v>
       </c>
       <c r="G188" s="12" t="n">
-        <v>0.38</v>
+        <v>0.12</v>
       </c>
       <c r="H188" t="n">
-        <v>59.87</v>
-      </c>
-      <c r="I188" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48</v>
+      </c>
+      <c r="I188" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J188" s="9" t="n">
-        <v>0.736</v>
+        <v>2.192</v>
       </c>
       <c r="K188" s="9" t="n">
-        <v>0.75</v>
+        <v>2.115</v>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" s="14" t="inlineStr"/>
@@ -8935,39 +8935,39 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D189" s="9" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="E189" s="16" t="n">
-        <v>-0.004699999999999999</v>
+        <v>0.765</v>
+      </c>
+      <c r="E189" s="10" t="n">
+        <v>0.02</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>645600</v>
+        <v>660800</v>
       </c>
       <c r="G189" s="12" t="n">
-        <v>0.12</v>
+        <v>0.38</v>
       </c>
       <c r="H189" t="n">
-        <v>26.03</v>
-      </c>
-      <c r="I189" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.87</v>
+      </c>
+      <c r="I189" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J189" s="9" t="n">
-        <v>4.546</v>
+        <v>0.736</v>
       </c>
       <c r="K189" s="9" t="n">
-        <v>4.888</v>
+        <v>0.75</v>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" s="14" t="inlineStr"/>
@@ -8980,28 +8980,28 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D190" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E190" s="10" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.995</v>
+      </c>
+      <c r="E190" s="16" t="n">
+        <v>-0.034</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>628800</v>
+        <v>658700</v>
       </c>
       <c r="G190" s="12" t="n">
         <v>0.29</v>
       </c>
       <c r="H190" t="n">
-        <v>32.88</v>
+        <v>28.32</v>
       </c>
       <c r="I190" s="13" t="inlineStr">
         <is>
@@ -9009,10 +9009,10 @@
         </is>
       </c>
       <c r="J190" s="9" t="n">
-        <v>0.988</v>
+        <v>1.072</v>
       </c>
       <c r="K190" s="9" t="n">
-        <v>1.019</v>
+        <v>1.133</v>
       </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" s="14" t="inlineStr"/>
@@ -9025,39 +9025,39 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D191" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E191" s="15" t="n">
-        <v>0</v>
+        <v>0.92</v>
+      </c>
+      <c r="E191" s="10" t="n">
+        <v>0.011</v>
       </c>
       <c r="F191" s="11" t="n">
-        <v>618100</v>
+        <v>653300</v>
       </c>
       <c r="G191" s="12" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="H191" t="n">
-        <v>39.05</v>
-      </c>
-      <c r="I191" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.14</v>
+      </c>
+      <c r="I191" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J191" s="9" t="n">
-        <v>0.916</v>
+        <v>0.988</v>
       </c>
       <c r="K191" s="9" t="n">
-        <v>0.968</v>
+        <v>1.019</v>
       </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" s="14" t="inlineStr"/>
@@ -9070,39 +9070,39 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D192" s="9" t="n">
-        <v>2.65</v>
+        <v>0.895</v>
       </c>
       <c r="E192" s="16" t="n">
-        <v>-0.0038</v>
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>607100</v>
+        <v>620100</v>
       </c>
       <c r="G192" s="12" t="n">
-        <v>0.45</v>
+        <v>0.22</v>
       </c>
       <c r="H192" t="n">
-        <v>34.17</v>
-      </c>
-      <c r="I192" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.53</v>
+      </c>
+      <c r="I192" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J192" s="9" t="n">
-        <v>2.879</v>
+        <v>0.916</v>
       </c>
       <c r="K192" s="9" t="n">
-        <v>2.842</v>
+        <v>0.968</v>
       </c>
       <c r="L192" t="inlineStr"/>
       <c r="M192" s="14" t="inlineStr"/>
@@ -9115,39 +9115,39 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D193" s="9" t="n">
-        <v>4.24</v>
+        <v>7.83</v>
       </c>
       <c r="E193" s="10" t="n">
-        <v>0.0266</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F193" s="11" t="n">
-        <v>567900</v>
+        <v>613400</v>
       </c>
       <c r="G193" s="12" t="n">
-        <v>0.65</v>
+        <v>0.15</v>
       </c>
       <c r="H193" t="n">
-        <v>54.07</v>
-      </c>
-      <c r="I193" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.17</v>
+      </c>
+      <c r="I193" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J193" s="9" t="n">
-        <v>4.109</v>
+        <v>7.85</v>
       </c>
       <c r="K193" s="9" t="n">
-        <v>4.258</v>
+        <v>8.028</v>
       </c>
       <c r="L193" t="inlineStr"/>
       <c r="M193" s="14" t="inlineStr"/>
@@ -9160,28 +9160,28 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>TMK</t>
         </is>
       </c>
       <c r="D194" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E194" s="15" t="n">
-        <v>0</v>
+        <v>2.65</v>
+      </c>
+      <c r="E194" s="16" t="n">
+        <v>-0.0038</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>558500</v>
+        <v>607100</v>
       </c>
       <c r="G194" s="12" t="n">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
       <c r="H194" t="n">
-        <v>35.62</v>
+        <v>34.17</v>
       </c>
       <c r="I194" s="13" t="inlineStr">
         <is>
@@ -9189,10 +9189,10 @@
         </is>
       </c>
       <c r="J194" s="9" t="n">
-        <v>0.5590000000000001</v>
+        <v>2.879</v>
       </c>
       <c r="K194" s="9" t="n">
-        <v>0.587</v>
+        <v>2.842</v>
       </c>
       <c r="L194" t="inlineStr"/>
       <c r="M194" s="14" t="inlineStr"/>
@@ -9205,28 +9205,28 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>GESHEN</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D195" s="9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E195" s="15" t="n">
-        <v>0</v>
+        <v>3.48</v>
+      </c>
+      <c r="E195" s="10" t="n">
+        <v>0.0029</v>
       </c>
       <c r="F195" s="11" t="n">
-        <v>557500</v>
+        <v>582100</v>
       </c>
       <c r="G195" s="12" t="n">
-        <v>1.11</v>
+        <v>0.19</v>
       </c>
       <c r="H195" t="n">
-        <v>37.25</v>
+        <v>59.33</v>
       </c>
       <c r="I195" s="13" t="inlineStr">
         <is>
@@ -9234,10 +9234,10 @@
         </is>
       </c>
       <c r="J195" s="9" t="n">
-        <v>1.151</v>
+        <v>3.42</v>
       </c>
       <c r="K195" s="9" t="n">
-        <v>1.25</v>
+        <v>3.024</v>
       </c>
       <c r="L195" t="inlineStr"/>
       <c r="M195" s="14" t="inlineStr"/>
@@ -9250,28 +9250,28 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>0366</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>ICENTS</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="D196" s="9" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E196" s="15" t="n">
-        <v>0</v>
+        <v>4.19</v>
+      </c>
+      <c r="E196" s="10" t="n">
+        <v>0.0145</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>551100</v>
+        <v>574400</v>
       </c>
       <c r="G196" s="12" t="n">
-        <v>0.31</v>
+        <v>0.66</v>
       </c>
       <c r="H196" t="n">
-        <v>57.38</v>
+        <v>52.09</v>
       </c>
       <c r="I196" s="13" t="inlineStr">
         <is>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="J196" s="9" t="n">
-        <v>0.83</v>
+        <v>4.104</v>
       </c>
       <c r="K196" s="9" t="n">
-        <v>0.756</v>
+        <v>4.257</v>
       </c>
       <c r="L196" t="inlineStr"/>
       <c r="M196" s="14" t="inlineStr"/>
@@ -9295,28 +9295,28 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D197" s="9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E197" s="10" t="n">
-        <v>0.0252</v>
+        <v>0.54</v>
+      </c>
+      <c r="E197" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F197" s="11" t="n">
-        <v>540300</v>
+        <v>558500</v>
       </c>
       <c r="G197" s="12" t="n">
-        <v>0.58</v>
+        <v>0.15</v>
       </c>
       <c r="H197" t="n">
-        <v>49.47</v>
+        <v>35.62</v>
       </c>
       <c r="I197" s="13" t="inlineStr">
         <is>
@@ -9324,10 +9324,10 @@
         </is>
       </c>
       <c r="J197" s="9" t="n">
-        <v>1.623</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K197" s="9" t="n">
-        <v>1.692</v>
+        <v>0.587</v>
       </c>
       <c r="L197" t="inlineStr"/>
       <c r="M197" s="14" t="inlineStr"/>
@@ -9340,39 +9340,39 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>PJBUMI</t>
+          <t>GESHEN</t>
         </is>
       </c>
       <c r="D198" s="9" t="n">
-        <v>4.12</v>
+        <v>1.12</v>
       </c>
       <c r="E198" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>535700</v>
+        <v>557500</v>
       </c>
       <c r="G198" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="H198" t="n">
-        <v>67.45999999999999</v>
-      </c>
-      <c r="I198" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.25</v>
+      </c>
+      <c r="I198" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J198" s="9" t="n">
-        <v>4.03</v>
+        <v>1.151</v>
       </c>
       <c r="K198" s="9" t="n">
-        <v>3.902</v>
+        <v>1.25</v>
       </c>
       <c r="L198" t="inlineStr"/>
       <c r="M198" s="14" t="inlineStr"/>
@@ -9385,39 +9385,39 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D199" s="9" t="n">
-        <v>0.645</v>
+        <v>7.56</v>
       </c>
       <c r="E199" s="16" t="n">
-        <v>-0.0373</v>
+        <v>-0.0066</v>
       </c>
       <c r="F199" s="11" t="n">
-        <v>532000</v>
+        <v>552000</v>
       </c>
       <c r="G199" s="12" t="n">
-        <v>1.26</v>
+        <v>0.15</v>
       </c>
       <c r="H199" t="n">
-        <v>49.78</v>
-      </c>
-      <c r="I199" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.9</v>
+      </c>
+      <c r="I199" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J199" s="9" t="n">
-        <v>0.643</v>
+        <v>7.641</v>
       </c>
       <c r="K199" s="9" t="n">
-        <v>0.655</v>
+        <v>7.817</v>
       </c>
       <c r="L199" t="inlineStr"/>
       <c r="M199" s="14" t="inlineStr"/>
@@ -9430,28 +9430,28 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>0366</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>ICENTS</t>
         </is>
       </c>
       <c r="D200" s="9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E200" s="10" t="n">
-        <v>0.0131</v>
+        <v>0.85</v>
+      </c>
+      <c r="E200" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>516100</v>
+        <v>551100</v>
       </c>
       <c r="G200" s="12" t="n">
-        <v>0.12</v>
+        <v>0.31</v>
       </c>
       <c r="H200" t="n">
-        <v>44.1</v>
+        <v>57.38</v>
       </c>
       <c r="I200" s="13" t="inlineStr">
         <is>
@@ -9459,10 +9459,10 @@
         </is>
       </c>
       <c r="J200" s="9" t="n">
-        <v>1.564</v>
+        <v>0.83</v>
       </c>
       <c r="K200" s="9" t="n">
-        <v>1.629</v>
+        <v>0.756</v>
       </c>
       <c r="L200" t="inlineStr"/>
       <c r="M200" s="14" t="inlineStr"/>
@@ -9475,39 +9475,39 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D201" s="9" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="E201" s="16" t="n">
-        <v>-0.0066</v>
+        <v>1.55</v>
+      </c>
+      <c r="E201" s="10" t="n">
+        <v>0.0131</v>
       </c>
       <c r="F201" s="11" t="n">
-        <v>514500</v>
+        <v>541700</v>
       </c>
       <c r="G201" s="12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="H201" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="I201" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.1</v>
+      </c>
+      <c r="I201" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J201" s="9" t="n">
-        <v>7.641</v>
+        <v>1.564</v>
       </c>
       <c r="K201" s="9" t="n">
-        <v>7.817</v>
+        <v>1.629</v>
       </c>
       <c r="L201" t="inlineStr"/>
       <c r="M201" s="14" t="inlineStr"/>
@@ -9520,28 +9520,28 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>THETA</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D202" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E202" s="16" t="n">
-        <v>-0.0236</v>
+        <v>1.63</v>
+      </c>
+      <c r="E202" s="10" t="n">
+        <v>0.0252</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>510200</v>
+        <v>540300</v>
       </c>
       <c r="G202" s="12" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="H202" t="n">
-        <v>43.59</v>
+        <v>49.47</v>
       </c>
       <c r="I202" s="13" t="inlineStr">
         <is>
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="J202" s="9" t="n">
-        <v>0.642</v>
+        <v>1.623</v>
       </c>
       <c r="K202" s="9" t="n">
-        <v>0.662</v>
+        <v>1.692</v>
       </c>
       <c r="L202" t="inlineStr"/>
       <c r="M202" s="14" t="inlineStr"/>
@@ -9565,45 +9565,180 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="D203" s="9" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="E203" s="10" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.645</v>
+      </c>
+      <c r="E203" s="16" t="n">
+        <v>-0.0373</v>
       </c>
       <c r="F203" s="11" t="n">
-        <v>507700</v>
+        <v>536200</v>
       </c>
       <c r="G203" s="12" t="n">
-        <v>0.12</v>
+        <v>1.27</v>
       </c>
       <c r="H203" t="n">
-        <v>47.17</v>
-      </c>
-      <c r="I203" s="17" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.78</v>
+      </c>
+      <c r="I203" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J203" s="9" t="n">
-        <v>7.85</v>
+        <v>0.643</v>
       </c>
       <c r="K203" s="9" t="n">
-        <v>8.028</v>
+        <v>0.655</v>
       </c>
       <c r="L203" t="inlineStr"/>
       <c r="M203" s="14" t="inlineStr"/>
     </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>7163</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>PJBUMI</t>
+        </is>
+      </c>
+      <c r="D204" s="9" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="E204" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" s="11" t="n">
+        <v>535700</v>
+      </c>
+      <c r="G204" s="12" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H204" t="n">
+        <v>67.45999999999999</v>
+      </c>
+      <c r="I204" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J204" s="9" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="K204" s="9" t="n">
+        <v>3.902</v>
+      </c>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" s="14" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>1562</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>SPTOTO</t>
+        </is>
+      </c>
+      <c r="D205" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E205" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" s="11" t="n">
+        <v>523900</v>
+      </c>
+      <c r="G205" s="12" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H205" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="I205" s="17" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J205" s="9" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="K205" s="9" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" s="14" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>9075</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>THETA</t>
+        </is>
+      </c>
+      <c r="D206" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E206" s="16" t="n">
+        <v>-0.0236</v>
+      </c>
+      <c r="F206" s="11" t="n">
+        <v>512200</v>
+      </c>
+      <c r="G206" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H206" t="n">
+        <v>43.59</v>
+      </c>
+      <c r="I206" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J206" s="9" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="K206" s="9" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M203"/>
+  <autoFilter ref="A1:M206"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-06/bursa-report-2026-10-06.xlsx
+++ b/docs/downloads/2026-10-06/bursa-report-2026-10-06.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多，但RSI达71.64已超买，现价3.07远高于50日均线1.952，偏离较大，信号可靠性偏弱。</t>
+          <t>SAR转多，但RSI达71.64已超买，现价3.07远高于50日均线1.952，偏离较大，信号可靠性存疑。</t>
         </is>
       </c>
     </row>
